--- a/Excel Files IPEDS/Trimmed/c2009_trimmed_file.xlsx
+++ b/Excel Files IPEDS/Trimmed/c2009_trimmed_file.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E299"/>
+  <dimension ref="A1:O299"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,6 +451,56 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>CTOTALM</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>CRACE20</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>CRACE21</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>CRACE22</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>CUNKNT</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>CBKAAT</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>CASIAT</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>CNHPIT</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>CHISPT</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>CWHITT</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>Year</t>
         </is>
       </c>
@@ -469,6 +519,26 @@
         <v>7</v>
       </c>
       <c r="E2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -486,6 +556,26 @@
         <v>7</v>
       </c>
       <c r="E3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -503,6 +593,26 @@
         <v>7</v>
       </c>
       <c r="E4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -520,6 +630,26 @@
         <v>7</v>
       </c>
       <c r="E5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -537,6 +667,26 @@
         <v>7</v>
       </c>
       <c r="E6" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -554,6 +704,26 @@
         <v>7</v>
       </c>
       <c r="E7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -571,6 +741,26 @@
         <v>7</v>
       </c>
       <c r="E8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>5</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -588,6 +778,26 @@
         <v>17</v>
       </c>
       <c r="E9" t="n">
+        <v>11</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" t="n">
+        <v>5</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -605,6 +815,30 @@
         <v>7</v>
       </c>
       <c r="E10" t="n">
+        <v>9</v>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>5</v>
+      </c>
+      <c r="O10" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -622,6 +856,30 @@
         <v>17</v>
       </c>
       <c r="E11" t="n">
+        <v>8</v>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>5</v>
+      </c>
+      <c r="O11" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -639,6 +897,30 @@
         <v>7</v>
       </c>
       <c r="E12" t="n">
+        <v>5</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>2</v>
+      </c>
+      <c r="N12" t="n">
+        <v>5</v>
+      </c>
+      <c r="O12" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -656,6 +938,26 @@
         <v>7</v>
       </c>
       <c r="E13" t="n">
+        <v>4</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>4</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -673,6 +975,26 @@
         <v>7</v>
       </c>
       <c r="E14" t="n">
+        <v>14</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>5</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -690,6 +1012,26 @@
         <v>7</v>
       </c>
       <c r="E15" t="n">
+        <v>3</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -707,6 +1049,26 @@
         <v>7</v>
       </c>
       <c r="E16" t="n">
+        <v>4</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -724,6 +1086,26 @@
         <v>7</v>
       </c>
       <c r="E17" t="n">
+        <v>9</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I17" t="n">
+        <v>6</v>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -741,6 +1123,26 @@
         <v>7</v>
       </c>
       <c r="E18" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -758,6 +1160,26 @@
         <v>7</v>
       </c>
       <c r="E19" t="n">
+        <v>4</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -775,6 +1197,26 @@
         <v>7</v>
       </c>
       <c r="E20" t="n">
+        <v>20</v>
+      </c>
+      <c r="F20" t="n">
+        <v>5</v>
+      </c>
+      <c r="G20" t="n">
+        <v>4</v>
+      </c>
+      <c r="H20" t="n">
+        <v>10</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -792,6 +1234,26 @@
         <v>7</v>
       </c>
       <c r="E21" t="n">
+        <v>9</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" t="n">
+        <v>10</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -809,6 +1271,26 @@
         <v>7</v>
       </c>
       <c r="E22" t="n">
+        <v>15</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>8</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2</v>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -826,6 +1308,26 @@
         <v>7</v>
       </c>
       <c r="E23" t="n">
+        <v>10</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>6</v>
+      </c>
+      <c r="I23" t="n">
+        <v>2</v>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -843,6 +1345,26 @@
         <v>7</v>
       </c>
       <c r="E24" t="n">
+        <v>10</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" t="n">
+        <v>5</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -860,6 +1382,26 @@
         <v>7</v>
       </c>
       <c r="E25" t="n">
+        <v>29</v>
+      </c>
+      <c r="F25" t="n">
+        <v>3</v>
+      </c>
+      <c r="G25" t="n">
+        <v>2</v>
+      </c>
+      <c r="H25" t="n">
+        <v>19</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -877,6 +1419,26 @@
         <v>7</v>
       </c>
       <c r="E26" t="n">
+        <v>22</v>
+      </c>
+      <c r="F26" t="n">
+        <v>3</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2</v>
+      </c>
+      <c r="H26" t="n">
+        <v>12</v>
+      </c>
+      <c r="I26" t="n">
+        <v>3</v>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -894,6 +1456,26 @@
         <v>7</v>
       </c>
       <c r="E27" t="n">
+        <v>8</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>6</v>
+      </c>
+      <c r="I27" t="n">
+        <v>4</v>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -911,6 +1493,26 @@
         <v>7</v>
       </c>
       <c r="E28" t="n">
+        <v>33</v>
+      </c>
+      <c r="F28" t="n">
+        <v>3</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" t="n">
+        <v>17</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -928,6 +1530,26 @@
         <v>7</v>
       </c>
       <c r="E29" t="n">
+        <v>8</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" t="n">
+        <v>3</v>
+      </c>
+      <c r="I29" t="n">
+        <v>4</v>
+      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -945,6 +1567,26 @@
         <v>7</v>
       </c>
       <c r="E30" t="n">
+        <v>7</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>3</v>
+      </c>
+      <c r="H30" t="n">
+        <v>6</v>
+      </c>
+      <c r="I30" t="n">
+        <v>3</v>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -962,6 +1604,26 @@
         <v>7</v>
       </c>
       <c r="E31" t="n">
+        <v>8</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>6</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -979,6 +1641,26 @@
         <v>7</v>
       </c>
       <c r="E32" t="n">
+        <v>4</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -996,6 +1678,26 @@
         <v>7</v>
       </c>
       <c r="E33" t="n">
+        <v>14</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>7</v>
+      </c>
+      <c r="I33" t="n">
+        <v>2</v>
+      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -1013,6 +1715,26 @@
         <v>7</v>
       </c>
       <c r="E34" t="n">
+        <v>6</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>6</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -1030,6 +1752,26 @@
         <v>7</v>
       </c>
       <c r="E35" t="n">
+        <v>6</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>5</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -1047,6 +1789,30 @@
         <v>7</v>
       </c>
       <c r="E36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -1064,6 +1830,26 @@
         <v>7</v>
       </c>
       <c r="E37" t="n">
+        <v>12</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>4</v>
+      </c>
+      <c r="I37" t="n">
+        <v>3</v>
+      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -1081,6 +1867,26 @@
         <v>17</v>
       </c>
       <c r="E38" t="n">
+        <v>4</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1</v>
+      </c>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -1098,6 +1904,26 @@
         <v>7</v>
       </c>
       <c r="E39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="n">
+        <v>2</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -1115,6 +1941,26 @@
         <v>17</v>
       </c>
       <c r="E40" t="n">
+        <v>2</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>2</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -1132,6 +1978,26 @@
         <v>7</v>
       </c>
       <c r="E41" t="n">
+        <v>13</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>11</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1</v>
+      </c>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -1149,6 +2015,26 @@
         <v>17</v>
       </c>
       <c r="E42" t="n">
+        <v>4</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>2</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1</v>
+      </c>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -1166,6 +2052,26 @@
         <v>7</v>
       </c>
       <c r="E43" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -1183,6 +2089,26 @@
         <v>7</v>
       </c>
       <c r="E44" t="n">
+        <v>2</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -1200,6 +2126,26 @@
         <v>7</v>
       </c>
       <c r="E45" t="n">
+        <v>3</v>
+      </c>
+      <c r="F45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>4</v>
+      </c>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -1217,6 +2163,26 @@
         <v>7</v>
       </c>
       <c r="E46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>1</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -1234,6 +2200,26 @@
         <v>7</v>
       </c>
       <c r="E47" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>2</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -1251,6 +2237,26 @@
         <v>17</v>
       </c>
       <c r="E48" t="n">
+        <v>2</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>2</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -1268,6 +2274,26 @@
         <v>7</v>
       </c>
       <c r="E49" t="n">
+        <v>1</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -1285,6 +2311,26 @@
         <v>7</v>
       </c>
       <c r="E50" t="n">
+        <v>4</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>2</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -1302,6 +2348,26 @@
         <v>7</v>
       </c>
       <c r="E51" t="n">
+        <v>1</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -1319,6 +2385,26 @@
         <v>7</v>
       </c>
       <c r="E52" t="n">
+        <v>1</v>
+      </c>
+      <c r="F52" t="n">
+        <v>1</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -1336,6 +2422,26 @@
         <v>7</v>
       </c>
       <c r="E53" t="n">
+        <v>3</v>
+      </c>
+      <c r="F53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" t="n">
+        <v>1</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -1353,6 +2459,26 @@
         <v>7</v>
       </c>
       <c r="E54" t="n">
+        <v>15</v>
+      </c>
+      <c r="F54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>12</v>
+      </c>
+      <c r="I54" t="n">
+        <v>1</v>
+      </c>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -1370,6 +2496,26 @@
         <v>7</v>
       </c>
       <c r="E55" t="n">
+        <v>9</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
+        <v>6</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -1387,6 +2533,26 @@
         <v>7</v>
       </c>
       <c r="E56" t="n">
+        <v>3</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" t="n">
+        <v>1</v>
+      </c>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -1404,6 +2570,26 @@
         <v>17</v>
       </c>
       <c r="E57" t="n">
+        <v>1</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -1421,6 +2607,26 @@
         <v>7</v>
       </c>
       <c r="E58" t="n">
+        <v>6</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" t="n">
+        <v>1</v>
+      </c>
+      <c r="H58" t="n">
+        <v>6</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -1438,6 +2644,30 @@
         <v>7</v>
       </c>
       <c r="E59" t="n">
+        <v>1</v>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="n">
+        <v>1</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -1455,6 +2685,26 @@
         <v>7</v>
       </c>
       <c r="E60" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -1472,6 +2722,30 @@
         <v>7</v>
       </c>
       <c r="E61" t="n">
+        <v>10</v>
+      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" t="n">
+        <v>5</v>
+      </c>
+      <c r="O61" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -1489,6 +2763,30 @@
         <v>17</v>
       </c>
       <c r="E62" t="n">
+        <v>13</v>
+      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" t="n">
+        <v>1</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" t="n">
+        <v>7</v>
+      </c>
+      <c r="O62" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -1506,6 +2804,26 @@
         <v>7</v>
       </c>
       <c r="E63" t="n">
+        <v>5</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" t="n">
+        <v>3</v>
+      </c>
+      <c r="I63" t="n">
+        <v>2</v>
+      </c>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -1523,6 +2841,26 @@
         <v>7</v>
       </c>
       <c r="E64" t="n">
+        <v>5</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="n">
+        <v>4</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -1540,6 +2878,26 @@
         <v>7</v>
       </c>
       <c r="E65" t="n">
+        <v>3</v>
+      </c>
+      <c r="F65" t="n">
+        <v>1</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" t="n">
+        <v>3</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -1557,6 +2915,26 @@
         <v>7</v>
       </c>
       <c r="E66" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" t="n">
+        <v>1</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -1574,6 +2952,26 @@
         <v>7</v>
       </c>
       <c r="E67" t="n">
+        <v>4</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" t="n">
+        <v>3</v>
+      </c>
+      <c r="I67" t="n">
+        <v>1</v>
+      </c>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -1591,6 +2989,26 @@
         <v>7</v>
       </c>
       <c r="E68" t="n">
+        <v>18</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0</v>
+      </c>
+      <c r="G68" t="n">
+        <v>1</v>
+      </c>
+      <c r="H68" t="n">
+        <v>10</v>
+      </c>
+      <c r="I68" t="n">
+        <v>3</v>
+      </c>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -1608,6 +3026,26 @@
         <v>17</v>
       </c>
       <c r="E69" t="n">
+        <v>19</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" t="n">
+        <v>10</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -1625,6 +3063,30 @@
         <v>7</v>
       </c>
       <c r="E70" t="n">
+        <v>4</v>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" t="n">
+        <v>1</v>
+      </c>
+      <c r="N70" t="n">
+        <v>1</v>
+      </c>
+      <c r="O70" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -1642,6 +3104,30 @@
         <v>7</v>
       </c>
       <c r="E71" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0</v>
+      </c>
+      <c r="N71" t="n">
+        <v>0</v>
+      </c>
+      <c r="O71" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -1659,6 +3145,26 @@
         <v>7</v>
       </c>
       <c r="E72" t="n">
+        <v>8</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" t="n">
+        <v>2</v>
+      </c>
+      <c r="I72" t="n">
+        <v>1</v>
+      </c>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -1676,6 +3182,26 @@
         <v>17</v>
       </c>
       <c r="E73" t="n">
+        <v>4</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" t="n">
+        <v>3</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -1693,6 +3219,26 @@
         <v>7</v>
       </c>
       <c r="E74" t="n">
+        <v>16</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" t="n">
+        <v>5</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -1710,6 +3256,26 @@
         <v>17</v>
       </c>
       <c r="E75" t="n">
+        <v>28</v>
+      </c>
+      <c r="F75" t="n">
+        <v>2</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" t="n">
+        <v>17</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -1727,6 +3293,26 @@
         <v>7</v>
       </c>
       <c r="E76" t="n">
+        <v>3</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0</v>
+      </c>
+      <c r="I76" t="n">
+        <v>1</v>
+      </c>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -1744,6 +3330,26 @@
         <v>7</v>
       </c>
       <c r="E77" t="n">
+        <v>3</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" t="n">
+        <v>2</v>
+      </c>
+      <c r="I77" t="n">
+        <v>1</v>
+      </c>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -1761,6 +3367,26 @@
         <v>17</v>
       </c>
       <c r="E78" t="n">
+        <v>2</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" t="n">
+        <v>1</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -1778,6 +3404,26 @@
         <v>7</v>
       </c>
       <c r="E79" t="n">
+        <v>7</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" t="n">
+        <v>3</v>
+      </c>
+      <c r="I79" t="n">
+        <v>1</v>
+      </c>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -1795,6 +3441,26 @@
         <v>17</v>
       </c>
       <c r="E80" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -1812,6 +3478,26 @@
         <v>7</v>
       </c>
       <c r="E81" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -1829,6 +3515,26 @@
         <v>17</v>
       </c>
       <c r="E82" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -1846,6 +3552,26 @@
         <v>7</v>
       </c>
       <c r="E83" t="n">
+        <v>2</v>
+      </c>
+      <c r="F83" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -1863,6 +3589,26 @@
         <v>7</v>
       </c>
       <c r="E84" t="n">
+        <v>9</v>
+      </c>
+      <c r="F84" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" t="n">
+        <v>1</v>
+      </c>
+      <c r="H84" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" t="n">
+        <v>1</v>
+      </c>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -1880,6 +3626,26 @@
         <v>7</v>
       </c>
       <c r="E85" t="n">
+        <v>8</v>
+      </c>
+      <c r="F85" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" t="n">
+        <v>9</v>
+      </c>
+      <c r="I85" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
+      <c r="O85" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -1897,6 +3663,26 @@
         <v>7</v>
       </c>
       <c r="E86" t="n">
+        <v>3</v>
+      </c>
+      <c r="F86" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
+      <c r="O86" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -1914,6 +3700,26 @@
         <v>7</v>
       </c>
       <c r="E87" t="n">
+        <v>10</v>
+      </c>
+      <c r="F87" t="n">
+        <v>1</v>
+      </c>
+      <c r="G87" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" t="n">
+        <v>7</v>
+      </c>
+      <c r="I87" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
+      <c r="O87" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -1931,6 +3737,26 @@
         <v>7</v>
       </c>
       <c r="E88" t="n">
+        <v>11</v>
+      </c>
+      <c r="F88" t="n">
+        <v>1</v>
+      </c>
+      <c r="G88" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" t="n">
+        <v>6</v>
+      </c>
+      <c r="I88" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
+      <c r="O88" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -1948,6 +3774,26 @@
         <v>7</v>
       </c>
       <c r="E89" t="n">
+        <v>4</v>
+      </c>
+      <c r="F89" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" t="n">
+        <v>0</v>
+      </c>
+      <c r="H89" t="n">
+        <v>5</v>
+      </c>
+      <c r="I89" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
+      <c r="O89" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -1965,6 +3811,26 @@
         <v>7</v>
       </c>
       <c r="E90" t="n">
+        <v>7</v>
+      </c>
+      <c r="F90" t="n">
+        <v>0</v>
+      </c>
+      <c r="G90" t="n">
+        <v>1</v>
+      </c>
+      <c r="H90" t="n">
+        <v>5</v>
+      </c>
+      <c r="I90" t="n">
+        <v>1</v>
+      </c>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
+      <c r="O90" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -1982,6 +3848,26 @@
         <v>17</v>
       </c>
       <c r="E91" t="n">
+        <v>5</v>
+      </c>
+      <c r="F91" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
+      <c r="O91" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -1999,6 +3885,26 @@
         <v>7</v>
       </c>
       <c r="E92" t="n">
+        <v>2</v>
+      </c>
+      <c r="F92" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" t="n">
+        <v>2</v>
+      </c>
+      <c r="I92" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
+      <c r="O92" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -2016,6 +3922,26 @@
         <v>17</v>
       </c>
       <c r="E93" t="n">
+        <v>6</v>
+      </c>
+      <c r="F93" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" t="n">
+        <v>4</v>
+      </c>
+      <c r="I93" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
+      <c r="O93" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -2033,6 +3959,26 @@
         <v>7</v>
       </c>
       <c r="E94" t="n">
+        <v>3</v>
+      </c>
+      <c r="F94" t="n">
+        <v>0</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
+      <c r="O94" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -2050,6 +3996,26 @@
         <v>7</v>
       </c>
       <c r="E95" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
+      <c r="O95" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -2067,6 +4033,26 @@
         <v>7</v>
       </c>
       <c r="E96" t="n">
+        <v>5</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>2</v>
+      </c>
+      <c r="I96" t="n">
+        <v>1</v>
+      </c>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
+      <c r="O96" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -2084,6 +4070,26 @@
         <v>7</v>
       </c>
       <c r="E97" t="n">
+        <v>5</v>
+      </c>
+      <c r="F97" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
+        <v>2</v>
+      </c>
+      <c r="I97" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
+      <c r="O97" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -2101,6 +4107,26 @@
         <v>7</v>
       </c>
       <c r="E98" t="n">
+        <v>5</v>
+      </c>
+      <c r="F98" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" t="n">
+        <v>5</v>
+      </c>
+      <c r="I98" t="n">
+        <v>1</v>
+      </c>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
+      <c r="O98" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -2118,6 +4144,26 @@
         <v>7</v>
       </c>
       <c r="E99" t="n">
+        <v>3</v>
+      </c>
+      <c r="F99" t="n">
+        <v>0</v>
+      </c>
+      <c r="G99" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" t="n">
+        <v>2</v>
+      </c>
+      <c r="I99" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
+      <c r="O99" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -2135,6 +4181,26 @@
         <v>7</v>
       </c>
       <c r="E100" t="n">
+        <v>2</v>
+      </c>
+      <c r="F100" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" t="n">
+        <v>1</v>
+      </c>
+      <c r="I100" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
+      <c r="O100" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -2152,6 +4218,26 @@
         <v>7</v>
       </c>
       <c r="E101" t="n">
+        <v>1</v>
+      </c>
+      <c r="F101" t="n">
+        <v>0</v>
+      </c>
+      <c r="G101" t="n">
+        <v>0</v>
+      </c>
+      <c r="H101" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
+      <c r="O101" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -2169,6 +4255,26 @@
         <v>7</v>
       </c>
       <c r="E102" t="n">
+        <v>3</v>
+      </c>
+      <c r="F102" t="n">
+        <v>0</v>
+      </c>
+      <c r="G102" t="n">
+        <v>0</v>
+      </c>
+      <c r="H102" t="n">
+        <v>1</v>
+      </c>
+      <c r="I102" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
+      <c r="O102" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -2186,6 +4292,26 @@
         <v>7</v>
       </c>
       <c r="E103" t="n">
+        <v>0</v>
+      </c>
+      <c r="F103" t="n">
+        <v>0</v>
+      </c>
+      <c r="G103" t="n">
+        <v>0</v>
+      </c>
+      <c r="H103" t="n">
+        <v>0</v>
+      </c>
+      <c r="I103" t="n">
+        <v>0</v>
+      </c>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
+      <c r="O103" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -2203,6 +4329,26 @@
         <v>7</v>
       </c>
       <c r="E104" t="n">
+        <v>3</v>
+      </c>
+      <c r="F104" t="n">
+        <v>0</v>
+      </c>
+      <c r="G104" t="n">
+        <v>0</v>
+      </c>
+      <c r="H104" t="n">
+        <v>2</v>
+      </c>
+      <c r="I104" t="n">
+        <v>0</v>
+      </c>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
+      <c r="O104" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -2220,6 +4366,26 @@
         <v>7</v>
       </c>
       <c r="E105" t="n">
+        <v>7</v>
+      </c>
+      <c r="F105" t="n">
+        <v>0</v>
+      </c>
+      <c r="G105" t="n">
+        <v>1</v>
+      </c>
+      <c r="H105" t="n">
+        <v>6</v>
+      </c>
+      <c r="I105" t="n">
+        <v>0</v>
+      </c>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
+      <c r="O105" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -2237,6 +4403,26 @@
         <v>17</v>
       </c>
       <c r="E106" t="n">
+        <v>12</v>
+      </c>
+      <c r="F106" t="n">
+        <v>1</v>
+      </c>
+      <c r="G106" t="n">
+        <v>0</v>
+      </c>
+      <c r="H106" t="n">
+        <v>5</v>
+      </c>
+      <c r="I106" t="n">
+        <v>0</v>
+      </c>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
+      <c r="O106" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -2254,6 +4440,26 @@
         <v>7</v>
       </c>
       <c r="E107" t="n">
+        <v>6</v>
+      </c>
+      <c r="F107" t="n">
+        <v>0</v>
+      </c>
+      <c r="G107" t="n">
+        <v>1</v>
+      </c>
+      <c r="H107" t="n">
+        <v>3</v>
+      </c>
+      <c r="I107" t="n">
+        <v>0</v>
+      </c>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
+      <c r="O107" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -2271,6 +4477,26 @@
         <v>17</v>
       </c>
       <c r="E108" t="n">
+        <v>4</v>
+      </c>
+      <c r="F108" t="n">
+        <v>0</v>
+      </c>
+      <c r="G108" t="n">
+        <v>0</v>
+      </c>
+      <c r="H108" t="n">
+        <v>4</v>
+      </c>
+      <c r="I108" t="n">
+        <v>0</v>
+      </c>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
+      <c r="O108" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -2288,6 +4514,26 @@
         <v>7</v>
       </c>
       <c r="E109" t="n">
+        <v>3</v>
+      </c>
+      <c r="F109" t="n">
+        <v>0</v>
+      </c>
+      <c r="G109" t="n">
+        <v>0</v>
+      </c>
+      <c r="H109" t="n">
+        <v>1</v>
+      </c>
+      <c r="I109" t="n">
+        <v>0</v>
+      </c>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
+      <c r="O109" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -2305,6 +4551,26 @@
         <v>17</v>
       </c>
       <c r="E110" t="n">
+        <v>23</v>
+      </c>
+      <c r="F110" t="n">
+        <v>0</v>
+      </c>
+      <c r="G110" t="n">
+        <v>0</v>
+      </c>
+      <c r="H110" t="n">
+        <v>9</v>
+      </c>
+      <c r="I110" t="n">
+        <v>5</v>
+      </c>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
+      <c r="O110" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -2322,6 +4588,26 @@
         <v>7</v>
       </c>
       <c r="E111" t="n">
+        <v>0</v>
+      </c>
+      <c r="F111" t="n">
+        <v>0</v>
+      </c>
+      <c r="G111" t="n">
+        <v>0</v>
+      </c>
+      <c r="H111" t="n">
+        <v>0</v>
+      </c>
+      <c r="I111" t="n">
+        <v>0</v>
+      </c>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
+      <c r="O111" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -2339,6 +4625,26 @@
         <v>7</v>
       </c>
       <c r="E112" t="n">
+        <v>5</v>
+      </c>
+      <c r="F112" t="n">
+        <v>1</v>
+      </c>
+      <c r="G112" t="n">
+        <v>0</v>
+      </c>
+      <c r="H112" t="n">
+        <v>2</v>
+      </c>
+      <c r="I112" t="n">
+        <v>1</v>
+      </c>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr"/>
+      <c r="N112" t="inlineStr"/>
+      <c r="O112" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -2356,6 +4662,26 @@
         <v>17</v>
       </c>
       <c r="E113" t="n">
+        <v>14</v>
+      </c>
+      <c r="F113" t="n">
+        <v>2</v>
+      </c>
+      <c r="G113" t="n">
+        <v>0</v>
+      </c>
+      <c r="H113" t="n">
+        <v>0</v>
+      </c>
+      <c r="I113" t="n">
+        <v>4</v>
+      </c>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
+      <c r="O113" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -2373,6 +4699,26 @@
         <v>7</v>
       </c>
       <c r="E114" t="n">
+        <v>5</v>
+      </c>
+      <c r="F114" t="n">
+        <v>0</v>
+      </c>
+      <c r="G114" t="n">
+        <v>0</v>
+      </c>
+      <c r="H114" t="n">
+        <v>2</v>
+      </c>
+      <c r="I114" t="n">
+        <v>0</v>
+      </c>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
+      <c r="O114" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -2390,6 +4736,26 @@
         <v>17</v>
       </c>
       <c r="E115" t="n">
+        <v>2</v>
+      </c>
+      <c r="F115" t="n">
+        <v>0</v>
+      </c>
+      <c r="G115" t="n">
+        <v>0</v>
+      </c>
+      <c r="H115" t="n">
+        <v>0</v>
+      </c>
+      <c r="I115" t="n">
+        <v>0</v>
+      </c>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
+      <c r="O115" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -2407,6 +4773,26 @@
         <v>7</v>
       </c>
       <c r="E116" t="n">
+        <v>0</v>
+      </c>
+      <c r="F116" t="n">
+        <v>0</v>
+      </c>
+      <c r="G116" t="n">
+        <v>0</v>
+      </c>
+      <c r="H116" t="n">
+        <v>0</v>
+      </c>
+      <c r="I116" t="n">
+        <v>1</v>
+      </c>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
+      <c r="O116" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -2424,6 +4810,26 @@
         <v>17</v>
       </c>
       <c r="E117" t="n">
+        <v>0</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0</v>
+      </c>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr"/>
+      <c r="N117" t="inlineStr"/>
+      <c r="O117" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -2441,6 +4847,26 @@
         <v>7</v>
       </c>
       <c r="E118" t="n">
+        <v>17</v>
+      </c>
+      <c r="F118" t="n">
+        <v>3</v>
+      </c>
+      <c r="G118" t="n">
+        <v>2</v>
+      </c>
+      <c r="H118" t="n">
+        <v>12</v>
+      </c>
+      <c r="I118" t="n">
+        <v>1</v>
+      </c>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
+      <c r="O118" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -2458,6 +4884,26 @@
         <v>17</v>
       </c>
       <c r="E119" t="n">
+        <v>32</v>
+      </c>
+      <c r="F119" t="n">
+        <v>2</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0</v>
+      </c>
+      <c r="H119" t="n">
+        <v>13</v>
+      </c>
+      <c r="I119" t="n">
+        <v>9</v>
+      </c>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
+      <c r="O119" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -2475,6 +4921,26 @@
         <v>7</v>
       </c>
       <c r="E120" t="n">
+        <v>6</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0</v>
+      </c>
+      <c r="H120" t="n">
+        <v>3</v>
+      </c>
+      <c r="I120" t="n">
+        <v>2</v>
+      </c>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
+      <c r="O120" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -2492,6 +4958,26 @@
         <v>17</v>
       </c>
       <c r="E121" t="n">
+        <v>1</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0</v>
+      </c>
+      <c r="H121" t="n">
+        <v>1</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0</v>
+      </c>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
+      <c r="O121" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -2509,6 +4995,26 @@
         <v>7</v>
       </c>
       <c r="E122" t="n">
+        <v>4</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0</v>
+      </c>
+      <c r="H122" t="n">
+        <v>2</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0</v>
+      </c>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
+      <c r="O122" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -2526,6 +5032,26 @@
         <v>17</v>
       </c>
       <c r="E123" t="n">
+        <v>3</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0</v>
+      </c>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr"/>
+      <c r="N123" t="inlineStr"/>
+      <c r="O123" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -2543,6 +5069,26 @@
         <v>7</v>
       </c>
       <c r="E124" t="n">
+        <v>6</v>
+      </c>
+      <c r="F124" t="n">
+        <v>2</v>
+      </c>
+      <c r="G124" t="n">
+        <v>1</v>
+      </c>
+      <c r="H124" t="n">
+        <v>3</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0</v>
+      </c>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
+      <c r="O124" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -2560,6 +5106,26 @@
         <v>7</v>
       </c>
       <c r="E125" t="n">
+        <v>4</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0</v>
+      </c>
+      <c r="H125" t="n">
+        <v>2</v>
+      </c>
+      <c r="I125" t="n">
+        <v>1</v>
+      </c>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
+      <c r="O125" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -2577,6 +5143,26 @@
         <v>17</v>
       </c>
       <c r="E126" t="n">
+        <v>31</v>
+      </c>
+      <c r="F126" t="n">
+        <v>1</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0</v>
+      </c>
+      <c r="H126" t="n">
+        <v>13</v>
+      </c>
+      <c r="I126" t="n">
+        <v>5</v>
+      </c>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
+      <c r="O126" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -2594,6 +5180,26 @@
         <v>7</v>
       </c>
       <c r="E127" t="n">
+        <v>9</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0</v>
+      </c>
+      <c r="G127" t="n">
+        <v>1</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0</v>
+      </c>
+      <c r="I127" t="n">
+        <v>1</v>
+      </c>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr"/>
+      <c r="N127" t="inlineStr"/>
+      <c r="O127" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -2611,6 +5217,26 @@
         <v>7</v>
       </c>
       <c r="E128" t="n">
+        <v>4</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0</v>
+      </c>
+      <c r="H128" t="n">
+        <v>1</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0</v>
+      </c>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
+      <c r="O128" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -2628,6 +5254,30 @@
         <v>7</v>
       </c>
       <c r="E129" t="n">
+        <v>2</v>
+      </c>
+      <c r="F129" t="inlineStr"/>
+      <c r="G129" t="inlineStr"/>
+      <c r="H129" t="inlineStr"/>
+      <c r="I129" t="n">
+        <v>0</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0</v>
+      </c>
+      <c r="O129" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -2645,6 +5295,30 @@
         <v>17</v>
       </c>
       <c r="E130" t="n">
+        <v>4</v>
+      </c>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="inlineStr"/>
+      <c r="H130" t="inlineStr"/>
+      <c r="I130" t="n">
+        <v>0</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0</v>
+      </c>
+      <c r="N130" t="n">
+        <v>2</v>
+      </c>
+      <c r="O130" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -2662,6 +5336,26 @@
         <v>7</v>
       </c>
       <c r="E131" t="n">
+        <v>1</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0</v>
+      </c>
+      <c r="H131" t="n">
+        <v>1</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0</v>
+      </c>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="inlineStr"/>
+      <c r="N131" t="inlineStr"/>
+      <c r="O131" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -2679,6 +5373,26 @@
         <v>7</v>
       </c>
       <c r="E132" t="n">
+        <v>3</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0</v>
+      </c>
+      <c r="H132" t="n">
+        <v>1</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0</v>
+      </c>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr"/>
+      <c r="N132" t="inlineStr"/>
+      <c r="O132" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -2696,6 +5410,26 @@
         <v>7</v>
       </c>
       <c r="E133" t="n">
+        <v>2</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0</v>
+      </c>
+      <c r="H133" t="n">
+        <v>2</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0</v>
+      </c>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr"/>
+      <c r="N133" t="inlineStr"/>
+      <c r="O133" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -2713,6 +5447,26 @@
         <v>7</v>
       </c>
       <c r="E134" t="n">
+        <v>5</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0</v>
+      </c>
+      <c r="G134" t="n">
+        <v>1</v>
+      </c>
+      <c r="H134" t="n">
+        <v>8</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0</v>
+      </c>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" t="inlineStr"/>
+      <c r="N134" t="inlineStr"/>
+      <c r="O134" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -2730,6 +5484,26 @@
         <v>17</v>
       </c>
       <c r="E135" t="n">
+        <v>15</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0</v>
+      </c>
+      <c r="H135" t="n">
+        <v>11</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0</v>
+      </c>
+      <c r="J135" t="inlineStr"/>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr"/>
+      <c r="N135" t="inlineStr"/>
+      <c r="O135" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -2747,6 +5521,26 @@
         <v>7</v>
       </c>
       <c r="E136" t="n">
+        <v>13</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0</v>
+      </c>
+      <c r="H136" t="n">
+        <v>4</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0</v>
+      </c>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
+      <c r="O136" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -2764,6 +5558,30 @@
         <v>7</v>
       </c>
       <c r="E137" t="n">
+        <v>2</v>
+      </c>
+      <c r="F137" t="inlineStr"/>
+      <c r="G137" t="inlineStr"/>
+      <c r="H137" t="inlineStr"/>
+      <c r="I137" t="n">
+        <v>0</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0</v>
+      </c>
+      <c r="N137" t="n">
+        <v>1</v>
+      </c>
+      <c r="O137" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -2781,6 +5599,30 @@
         <v>17</v>
       </c>
       <c r="E138" t="n">
+        <v>2</v>
+      </c>
+      <c r="F138" t="inlineStr"/>
+      <c r="G138" t="inlineStr"/>
+      <c r="H138" t="inlineStr"/>
+      <c r="I138" t="n">
+        <v>0</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0</v>
+      </c>
+      <c r="O138" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -2798,6 +5640,26 @@
         <v>7</v>
       </c>
       <c r="E139" t="n">
+        <v>1</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0</v>
+      </c>
+      <c r="H139" t="n">
+        <v>1</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0</v>
+      </c>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr"/>
+      <c r="N139" t="inlineStr"/>
+      <c r="O139" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -2815,6 +5677,26 @@
         <v>7</v>
       </c>
       <c r="E140" t="n">
+        <v>9</v>
+      </c>
+      <c r="F140" t="n">
+        <v>5</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0</v>
+      </c>
+      <c r="H140" t="n">
+        <v>3</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0</v>
+      </c>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="inlineStr"/>
+      <c r="N140" t="inlineStr"/>
+      <c r="O140" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -2832,6 +5714,26 @@
         <v>7</v>
       </c>
       <c r="E141" t="n">
+        <v>6</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0</v>
+      </c>
+      <c r="G141" t="n">
+        <v>1</v>
+      </c>
+      <c r="H141" t="n">
+        <v>3</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0</v>
+      </c>
+      <c r="J141" t="inlineStr"/>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" t="inlineStr"/>
+      <c r="N141" t="inlineStr"/>
+      <c r="O141" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -2849,6 +5751,26 @@
         <v>17</v>
       </c>
       <c r="E142" t="n">
+        <v>3</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0</v>
+      </c>
+      <c r="J142" t="inlineStr"/>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" t="inlineStr"/>
+      <c r="N142" t="inlineStr"/>
+      <c r="O142" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -2866,6 +5788,26 @@
         <v>7</v>
       </c>
       <c r="E143" t="n">
+        <v>3</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0</v>
+      </c>
+      <c r="H143" t="n">
+        <v>2</v>
+      </c>
+      <c r="I143" t="n">
+        <v>1</v>
+      </c>
+      <c r="J143" t="inlineStr"/>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" t="inlineStr"/>
+      <c r="N143" t="inlineStr"/>
+      <c r="O143" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -2883,6 +5825,30 @@
         <v>7</v>
       </c>
       <c r="E144" t="n">
+        <v>3</v>
+      </c>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="inlineStr"/>
+      <c r="H144" t="inlineStr"/>
+      <c r="I144" t="n">
+        <v>0</v>
+      </c>
+      <c r="J144" t="n">
+        <v>0</v>
+      </c>
+      <c r="K144" t="n">
+        <v>0</v>
+      </c>
+      <c r="L144" t="n">
+        <v>0</v>
+      </c>
+      <c r="M144" t="n">
+        <v>0</v>
+      </c>
+      <c r="N144" t="n">
+        <v>1</v>
+      </c>
+      <c r="O144" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -2900,6 +5866,30 @@
         <v>17</v>
       </c>
       <c r="E145" t="n">
+        <v>8</v>
+      </c>
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" t="inlineStr"/>
+      <c r="H145" t="inlineStr"/>
+      <c r="I145" t="n">
+        <v>1</v>
+      </c>
+      <c r="J145" t="n">
+        <v>0</v>
+      </c>
+      <c r="K145" t="n">
+        <v>0</v>
+      </c>
+      <c r="L145" t="n">
+        <v>0</v>
+      </c>
+      <c r="M145" t="n">
+        <v>0</v>
+      </c>
+      <c r="N145" t="n">
+        <v>6</v>
+      </c>
+      <c r="O145" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -2917,6 +5907,30 @@
         <v>7</v>
       </c>
       <c r="E146" t="n">
+        <v>2</v>
+      </c>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr"/>
+      <c r="H146" t="inlineStr"/>
+      <c r="I146" t="n">
+        <v>0</v>
+      </c>
+      <c r="J146" t="n">
+        <v>0</v>
+      </c>
+      <c r="K146" t="n">
+        <v>0</v>
+      </c>
+      <c r="L146" t="n">
+        <v>0</v>
+      </c>
+      <c r="M146" t="n">
+        <v>0</v>
+      </c>
+      <c r="N146" t="n">
+        <v>1</v>
+      </c>
+      <c r="O146" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -2934,6 +5948,26 @@
         <v>7</v>
       </c>
       <c r="E147" t="n">
+        <v>3</v>
+      </c>
+      <c r="F147" t="n">
+        <v>0</v>
+      </c>
+      <c r="G147" t="n">
+        <v>0</v>
+      </c>
+      <c r="H147" t="n">
+        <v>2</v>
+      </c>
+      <c r="I147" t="n">
+        <v>0</v>
+      </c>
+      <c r="J147" t="inlineStr"/>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" t="inlineStr"/>
+      <c r="N147" t="inlineStr"/>
+      <c r="O147" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -2951,6 +5985,26 @@
         <v>17</v>
       </c>
       <c r="E148" t="n">
+        <v>2</v>
+      </c>
+      <c r="F148" t="n">
+        <v>0</v>
+      </c>
+      <c r="G148" t="n">
+        <v>0</v>
+      </c>
+      <c r="H148" t="n">
+        <v>1</v>
+      </c>
+      <c r="I148" t="n">
+        <v>0</v>
+      </c>
+      <c r="J148" t="inlineStr"/>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" t="inlineStr"/>
+      <c r="N148" t="inlineStr"/>
+      <c r="O148" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -2968,6 +6022,26 @@
         <v>7</v>
       </c>
       <c r="E149" t="n">
+        <v>4</v>
+      </c>
+      <c r="F149" t="n">
+        <v>0</v>
+      </c>
+      <c r="G149" t="n">
+        <v>0</v>
+      </c>
+      <c r="H149" t="n">
+        <v>0</v>
+      </c>
+      <c r="I149" t="n">
+        <v>0</v>
+      </c>
+      <c r="J149" t="inlineStr"/>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" t="inlineStr"/>
+      <c r="N149" t="inlineStr"/>
+      <c r="O149" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -2985,6 +6059,30 @@
         <v>7</v>
       </c>
       <c r="E150" t="n">
+        <v>5</v>
+      </c>
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="inlineStr"/>
+      <c r="H150" t="inlineStr"/>
+      <c r="I150" t="n">
+        <v>0</v>
+      </c>
+      <c r="J150" t="n">
+        <v>0</v>
+      </c>
+      <c r="K150" t="n">
+        <v>0</v>
+      </c>
+      <c r="L150" t="n">
+        <v>0</v>
+      </c>
+      <c r="M150" t="n">
+        <v>0</v>
+      </c>
+      <c r="N150" t="n">
+        <v>2</v>
+      </c>
+      <c r="O150" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -3002,6 +6100,26 @@
         <v>7</v>
       </c>
       <c r="E151" t="n">
+        <v>7</v>
+      </c>
+      <c r="F151" t="n">
+        <v>0</v>
+      </c>
+      <c r="G151" t="n">
+        <v>0</v>
+      </c>
+      <c r="H151" t="n">
+        <v>4</v>
+      </c>
+      <c r="I151" t="n">
+        <v>0</v>
+      </c>
+      <c r="J151" t="inlineStr"/>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" t="inlineStr"/>
+      <c r="N151" t="inlineStr"/>
+      <c r="O151" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -3019,6 +6137,26 @@
         <v>17</v>
       </c>
       <c r="E152" t="n">
+        <v>4</v>
+      </c>
+      <c r="F152" t="n">
+        <v>0</v>
+      </c>
+      <c r="G152" t="n">
+        <v>0</v>
+      </c>
+      <c r="H152" t="n">
+        <v>1</v>
+      </c>
+      <c r="I152" t="n">
+        <v>0</v>
+      </c>
+      <c r="J152" t="inlineStr"/>
+      <c r="K152" t="inlineStr"/>
+      <c r="L152" t="inlineStr"/>
+      <c r="M152" t="inlineStr"/>
+      <c r="N152" t="inlineStr"/>
+      <c r="O152" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -3036,6 +6174,26 @@
         <v>7</v>
       </c>
       <c r="E153" t="n">
+        <v>3</v>
+      </c>
+      <c r="F153" t="n">
+        <v>0</v>
+      </c>
+      <c r="G153" t="n">
+        <v>0</v>
+      </c>
+      <c r="H153" t="n">
+        <v>3</v>
+      </c>
+      <c r="I153" t="n">
+        <v>0</v>
+      </c>
+      <c r="J153" t="inlineStr"/>
+      <c r="K153" t="inlineStr"/>
+      <c r="L153" t="inlineStr"/>
+      <c r="M153" t="inlineStr"/>
+      <c r="N153" t="inlineStr"/>
+      <c r="O153" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -3053,6 +6211,26 @@
         <v>7</v>
       </c>
       <c r="E154" t="n">
+        <v>7</v>
+      </c>
+      <c r="F154" t="n">
+        <v>0</v>
+      </c>
+      <c r="G154" t="n">
+        <v>0</v>
+      </c>
+      <c r="H154" t="n">
+        <v>5</v>
+      </c>
+      <c r="I154" t="n">
+        <v>0</v>
+      </c>
+      <c r="J154" t="inlineStr"/>
+      <c r="K154" t="inlineStr"/>
+      <c r="L154" t="inlineStr"/>
+      <c r="M154" t="inlineStr"/>
+      <c r="N154" t="inlineStr"/>
+      <c r="O154" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -3070,6 +6248,26 @@
         <v>17</v>
       </c>
       <c r="E155" t="n">
+        <v>4</v>
+      </c>
+      <c r="F155" t="n">
+        <v>0</v>
+      </c>
+      <c r="G155" t="n">
+        <v>0</v>
+      </c>
+      <c r="H155" t="n">
+        <v>3</v>
+      </c>
+      <c r="I155" t="n">
+        <v>0</v>
+      </c>
+      <c r="J155" t="inlineStr"/>
+      <c r="K155" t="inlineStr"/>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" t="inlineStr"/>
+      <c r="N155" t="inlineStr"/>
+      <c r="O155" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -3087,6 +6285,26 @@
         <v>7</v>
       </c>
       <c r="E156" t="n">
+        <v>3</v>
+      </c>
+      <c r="F156" t="n">
+        <v>0</v>
+      </c>
+      <c r="G156" t="n">
+        <v>0</v>
+      </c>
+      <c r="H156" t="n">
+        <v>2</v>
+      </c>
+      <c r="I156" t="n">
+        <v>0</v>
+      </c>
+      <c r="J156" t="inlineStr"/>
+      <c r="K156" t="inlineStr"/>
+      <c r="L156" t="inlineStr"/>
+      <c r="M156" t="inlineStr"/>
+      <c r="N156" t="inlineStr"/>
+      <c r="O156" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -3104,6 +6322,26 @@
         <v>17</v>
       </c>
       <c r="E157" t="n">
+        <v>2</v>
+      </c>
+      <c r="F157" t="n">
+        <v>0</v>
+      </c>
+      <c r="G157" t="n">
+        <v>0</v>
+      </c>
+      <c r="H157" t="n">
+        <v>1</v>
+      </c>
+      <c r="I157" t="n">
+        <v>0</v>
+      </c>
+      <c r="J157" t="inlineStr"/>
+      <c r="K157" t="inlineStr"/>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" t="inlineStr"/>
+      <c r="N157" t="inlineStr"/>
+      <c r="O157" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -3121,6 +6359,26 @@
         <v>7</v>
       </c>
       <c r="E158" t="n">
+        <v>6</v>
+      </c>
+      <c r="F158" t="n">
+        <v>0</v>
+      </c>
+      <c r="G158" t="n">
+        <v>0</v>
+      </c>
+      <c r="H158" t="n">
+        <v>4</v>
+      </c>
+      <c r="I158" t="n">
+        <v>0</v>
+      </c>
+      <c r="J158" t="inlineStr"/>
+      <c r="K158" t="inlineStr"/>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" t="inlineStr"/>
+      <c r="N158" t="inlineStr"/>
+      <c r="O158" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -3138,6 +6396,26 @@
         <v>17</v>
       </c>
       <c r="E159" t="n">
+        <v>8</v>
+      </c>
+      <c r="F159" t="n">
+        <v>0</v>
+      </c>
+      <c r="G159" t="n">
+        <v>0</v>
+      </c>
+      <c r="H159" t="n">
+        <v>7</v>
+      </c>
+      <c r="I159" t="n">
+        <v>0</v>
+      </c>
+      <c r="J159" t="inlineStr"/>
+      <c r="K159" t="inlineStr"/>
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" t="inlineStr"/>
+      <c r="N159" t="inlineStr"/>
+      <c r="O159" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -3155,6 +6433,26 @@
         <v>7</v>
       </c>
       <c r="E160" t="n">
+        <v>8</v>
+      </c>
+      <c r="F160" t="n">
+        <v>0</v>
+      </c>
+      <c r="G160" t="n">
+        <v>0</v>
+      </c>
+      <c r="H160" t="n">
+        <v>1</v>
+      </c>
+      <c r="I160" t="n">
+        <v>6</v>
+      </c>
+      <c r="J160" t="inlineStr"/>
+      <c r="K160" t="inlineStr"/>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" t="inlineStr"/>
+      <c r="N160" t="inlineStr"/>
+      <c r="O160" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -3172,6 +6470,26 @@
         <v>7</v>
       </c>
       <c r="E161" t="n">
+        <v>0</v>
+      </c>
+      <c r="F161" t="n">
+        <v>0</v>
+      </c>
+      <c r="G161" t="n">
+        <v>0</v>
+      </c>
+      <c r="H161" t="n">
+        <v>0</v>
+      </c>
+      <c r="I161" t="n">
+        <v>0</v>
+      </c>
+      <c r="J161" t="inlineStr"/>
+      <c r="K161" t="inlineStr"/>
+      <c r="L161" t="inlineStr"/>
+      <c r="M161" t="inlineStr"/>
+      <c r="N161" t="inlineStr"/>
+      <c r="O161" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -3189,6 +6507,26 @@
         <v>7</v>
       </c>
       <c r="E162" t="n">
+        <v>4</v>
+      </c>
+      <c r="F162" t="n">
+        <v>0</v>
+      </c>
+      <c r="G162" t="n">
+        <v>0</v>
+      </c>
+      <c r="H162" t="n">
+        <v>5</v>
+      </c>
+      <c r="I162" t="n">
+        <v>1</v>
+      </c>
+      <c r="J162" t="inlineStr"/>
+      <c r="K162" t="inlineStr"/>
+      <c r="L162" t="inlineStr"/>
+      <c r="M162" t="inlineStr"/>
+      <c r="N162" t="inlineStr"/>
+      <c r="O162" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -3206,6 +6544,26 @@
         <v>7</v>
       </c>
       <c r="E163" t="n">
+        <v>1</v>
+      </c>
+      <c r="F163" t="n">
+        <v>1</v>
+      </c>
+      <c r="G163" t="n">
+        <v>0</v>
+      </c>
+      <c r="H163" t="n">
+        <v>1</v>
+      </c>
+      <c r="I163" t="n">
+        <v>0</v>
+      </c>
+      <c r="J163" t="inlineStr"/>
+      <c r="K163" t="inlineStr"/>
+      <c r="L163" t="inlineStr"/>
+      <c r="M163" t="inlineStr"/>
+      <c r="N163" t="inlineStr"/>
+      <c r="O163" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -3223,6 +6581,26 @@
         <v>17</v>
       </c>
       <c r="E164" t="n">
+        <v>4</v>
+      </c>
+      <c r="F164" t="n">
+        <v>0</v>
+      </c>
+      <c r="G164" t="n">
+        <v>0</v>
+      </c>
+      <c r="H164" t="n">
+        <v>3</v>
+      </c>
+      <c r="I164" t="n">
+        <v>1</v>
+      </c>
+      <c r="J164" t="inlineStr"/>
+      <c r="K164" t="inlineStr"/>
+      <c r="L164" t="inlineStr"/>
+      <c r="M164" t="inlineStr"/>
+      <c r="N164" t="inlineStr"/>
+      <c r="O164" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -3240,6 +6618,30 @@
         <v>7</v>
       </c>
       <c r="E165" t="n">
+        <v>0</v>
+      </c>
+      <c r="F165" t="inlineStr"/>
+      <c r="G165" t="inlineStr"/>
+      <c r="H165" t="inlineStr"/>
+      <c r="I165" t="n">
+        <v>0</v>
+      </c>
+      <c r="J165" t="n">
+        <v>0</v>
+      </c>
+      <c r="K165" t="n">
+        <v>0</v>
+      </c>
+      <c r="L165" t="n">
+        <v>0</v>
+      </c>
+      <c r="M165" t="n">
+        <v>0</v>
+      </c>
+      <c r="N165" t="n">
+        <v>0</v>
+      </c>
+      <c r="O165" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -3257,6 +6659,30 @@
         <v>17</v>
       </c>
       <c r="E166" t="n">
+        <v>1</v>
+      </c>
+      <c r="F166" t="inlineStr"/>
+      <c r="G166" t="inlineStr"/>
+      <c r="H166" t="inlineStr"/>
+      <c r="I166" t="n">
+        <v>0</v>
+      </c>
+      <c r="J166" t="n">
+        <v>0</v>
+      </c>
+      <c r="K166" t="n">
+        <v>0</v>
+      </c>
+      <c r="L166" t="n">
+        <v>0</v>
+      </c>
+      <c r="M166" t="n">
+        <v>0</v>
+      </c>
+      <c r="N166" t="n">
+        <v>1</v>
+      </c>
+      <c r="O166" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -3274,6 +6700,30 @@
         <v>7</v>
       </c>
       <c r="E167" t="n">
+        <v>0</v>
+      </c>
+      <c r="F167" t="inlineStr"/>
+      <c r="G167" t="inlineStr"/>
+      <c r="H167" t="inlineStr"/>
+      <c r="I167" t="n">
+        <v>0</v>
+      </c>
+      <c r="J167" t="n">
+        <v>0</v>
+      </c>
+      <c r="K167" t="n">
+        <v>0</v>
+      </c>
+      <c r="L167" t="n">
+        <v>0</v>
+      </c>
+      <c r="M167" t="n">
+        <v>0</v>
+      </c>
+      <c r="N167" t="n">
+        <v>1</v>
+      </c>
+      <c r="O167" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -3291,6 +6741,26 @@
         <v>7</v>
       </c>
       <c r="E168" t="n">
+        <v>0</v>
+      </c>
+      <c r="F168" t="n">
+        <v>0</v>
+      </c>
+      <c r="G168" t="n">
+        <v>0</v>
+      </c>
+      <c r="H168" t="n">
+        <v>1</v>
+      </c>
+      <c r="I168" t="n">
+        <v>0</v>
+      </c>
+      <c r="J168" t="inlineStr"/>
+      <c r="K168" t="inlineStr"/>
+      <c r="L168" t="inlineStr"/>
+      <c r="M168" t="inlineStr"/>
+      <c r="N168" t="inlineStr"/>
+      <c r="O168" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -3308,6 +6778,26 @@
         <v>7</v>
       </c>
       <c r="E169" t="n">
+        <v>5</v>
+      </c>
+      <c r="F169" t="n">
+        <v>0</v>
+      </c>
+      <c r="G169" t="n">
+        <v>0</v>
+      </c>
+      <c r="H169" t="n">
+        <v>3</v>
+      </c>
+      <c r="I169" t="n">
+        <v>0</v>
+      </c>
+      <c r="J169" t="inlineStr"/>
+      <c r="K169" t="inlineStr"/>
+      <c r="L169" t="inlineStr"/>
+      <c r="M169" t="inlineStr"/>
+      <c r="N169" t="inlineStr"/>
+      <c r="O169" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -3325,6 +6815,26 @@
         <v>7</v>
       </c>
       <c r="E170" t="n">
+        <v>6</v>
+      </c>
+      <c r="F170" t="n">
+        <v>0</v>
+      </c>
+      <c r="G170" t="n">
+        <v>1</v>
+      </c>
+      <c r="H170" t="n">
+        <v>4</v>
+      </c>
+      <c r="I170" t="n">
+        <v>1</v>
+      </c>
+      <c r="J170" t="inlineStr"/>
+      <c r="K170" t="inlineStr"/>
+      <c r="L170" t="inlineStr"/>
+      <c r="M170" t="inlineStr"/>
+      <c r="N170" t="inlineStr"/>
+      <c r="O170" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -3342,6 +6852,30 @@
         <v>7</v>
       </c>
       <c r="E171" t="n">
+        <v>4</v>
+      </c>
+      <c r="F171" t="inlineStr"/>
+      <c r="G171" t="inlineStr"/>
+      <c r="H171" t="inlineStr"/>
+      <c r="I171" t="n">
+        <v>0</v>
+      </c>
+      <c r="J171" t="n">
+        <v>0</v>
+      </c>
+      <c r="K171" t="n">
+        <v>0</v>
+      </c>
+      <c r="L171" t="n">
+        <v>0</v>
+      </c>
+      <c r="M171" t="n">
+        <v>1</v>
+      </c>
+      <c r="N171" t="n">
+        <v>3</v>
+      </c>
+      <c r="O171" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -3359,6 +6893,26 @@
         <v>7</v>
       </c>
       <c r="E172" t="n">
+        <v>4</v>
+      </c>
+      <c r="F172" t="n">
+        <v>1</v>
+      </c>
+      <c r="G172" t="n">
+        <v>1</v>
+      </c>
+      <c r="H172" t="n">
+        <v>3</v>
+      </c>
+      <c r="I172" t="n">
+        <v>0</v>
+      </c>
+      <c r="J172" t="inlineStr"/>
+      <c r="K172" t="inlineStr"/>
+      <c r="L172" t="inlineStr"/>
+      <c r="M172" t="inlineStr"/>
+      <c r="N172" t="inlineStr"/>
+      <c r="O172" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -3376,6 +6930,26 @@
         <v>7</v>
       </c>
       <c r="E173" t="n">
+        <v>5</v>
+      </c>
+      <c r="F173" t="n">
+        <v>0</v>
+      </c>
+      <c r="G173" t="n">
+        <v>0</v>
+      </c>
+      <c r="H173" t="n">
+        <v>1</v>
+      </c>
+      <c r="I173" t="n">
+        <v>0</v>
+      </c>
+      <c r="J173" t="inlineStr"/>
+      <c r="K173" t="inlineStr"/>
+      <c r="L173" t="inlineStr"/>
+      <c r="M173" t="inlineStr"/>
+      <c r="N173" t="inlineStr"/>
+      <c r="O173" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -3393,6 +6967,26 @@
         <v>17</v>
       </c>
       <c r="E174" t="n">
+        <v>5</v>
+      </c>
+      <c r="F174" t="n">
+        <v>0</v>
+      </c>
+      <c r="G174" t="n">
+        <v>0</v>
+      </c>
+      <c r="H174" t="n">
+        <v>3</v>
+      </c>
+      <c r="I174" t="n">
+        <v>0</v>
+      </c>
+      <c r="J174" t="inlineStr"/>
+      <c r="K174" t="inlineStr"/>
+      <c r="L174" t="inlineStr"/>
+      <c r="M174" t="inlineStr"/>
+      <c r="N174" t="inlineStr"/>
+      <c r="O174" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -3410,6 +7004,26 @@
         <v>7</v>
       </c>
       <c r="E175" t="n">
+        <v>6</v>
+      </c>
+      <c r="F175" t="n">
+        <v>0</v>
+      </c>
+      <c r="G175" t="n">
+        <v>0</v>
+      </c>
+      <c r="H175" t="n">
+        <v>2</v>
+      </c>
+      <c r="I175" t="n">
+        <v>0</v>
+      </c>
+      <c r="J175" t="inlineStr"/>
+      <c r="K175" t="inlineStr"/>
+      <c r="L175" t="inlineStr"/>
+      <c r="M175" t="inlineStr"/>
+      <c r="N175" t="inlineStr"/>
+      <c r="O175" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -3427,6 +7041,26 @@
         <v>7</v>
       </c>
       <c r="E176" t="n">
+        <v>2</v>
+      </c>
+      <c r="F176" t="n">
+        <v>0</v>
+      </c>
+      <c r="G176" t="n">
+        <v>0</v>
+      </c>
+      <c r="H176" t="n">
+        <v>2</v>
+      </c>
+      <c r="I176" t="n">
+        <v>0</v>
+      </c>
+      <c r="J176" t="inlineStr"/>
+      <c r="K176" t="inlineStr"/>
+      <c r="L176" t="inlineStr"/>
+      <c r="M176" t="inlineStr"/>
+      <c r="N176" t="inlineStr"/>
+      <c r="O176" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -3444,6 +7078,26 @@
         <v>17</v>
       </c>
       <c r="E177" t="n">
+        <v>2</v>
+      </c>
+      <c r="F177" t="n">
+        <v>0</v>
+      </c>
+      <c r="G177" t="n">
+        <v>0</v>
+      </c>
+      <c r="H177" t="n">
+        <v>1</v>
+      </c>
+      <c r="I177" t="n">
+        <v>0</v>
+      </c>
+      <c r="J177" t="inlineStr"/>
+      <c r="K177" t="inlineStr"/>
+      <c r="L177" t="inlineStr"/>
+      <c r="M177" t="inlineStr"/>
+      <c r="N177" t="inlineStr"/>
+      <c r="O177" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -3461,6 +7115,26 @@
         <v>7</v>
       </c>
       <c r="E178" t="n">
+        <v>3</v>
+      </c>
+      <c r="F178" t="n">
+        <v>0</v>
+      </c>
+      <c r="G178" t="n">
+        <v>0</v>
+      </c>
+      <c r="H178" t="n">
+        <v>3</v>
+      </c>
+      <c r="I178" t="n">
+        <v>0</v>
+      </c>
+      <c r="J178" t="inlineStr"/>
+      <c r="K178" t="inlineStr"/>
+      <c r="L178" t="inlineStr"/>
+      <c r="M178" t="inlineStr"/>
+      <c r="N178" t="inlineStr"/>
+      <c r="O178" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -3478,6 +7152,26 @@
         <v>7</v>
       </c>
       <c r="E179" t="n">
+        <v>18</v>
+      </c>
+      <c r="F179" t="n">
+        <v>0</v>
+      </c>
+      <c r="G179" t="n">
+        <v>0</v>
+      </c>
+      <c r="H179" t="n">
+        <v>6</v>
+      </c>
+      <c r="I179" t="n">
+        <v>1</v>
+      </c>
+      <c r="J179" t="inlineStr"/>
+      <c r="K179" t="inlineStr"/>
+      <c r="L179" t="inlineStr"/>
+      <c r="M179" t="inlineStr"/>
+      <c r="N179" t="inlineStr"/>
+      <c r="O179" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -3495,6 +7189,26 @@
         <v>7</v>
       </c>
       <c r="E180" t="n">
+        <v>4</v>
+      </c>
+      <c r="F180" t="n">
+        <v>1</v>
+      </c>
+      <c r="G180" t="n">
+        <v>1</v>
+      </c>
+      <c r="H180" t="n">
+        <v>2</v>
+      </c>
+      <c r="I180" t="n">
+        <v>0</v>
+      </c>
+      <c r="J180" t="inlineStr"/>
+      <c r="K180" t="inlineStr"/>
+      <c r="L180" t="inlineStr"/>
+      <c r="M180" t="inlineStr"/>
+      <c r="N180" t="inlineStr"/>
+      <c r="O180" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -3512,6 +7226,26 @@
         <v>7</v>
       </c>
       <c r="E181" t="n">
+        <v>3</v>
+      </c>
+      <c r="F181" t="n">
+        <v>0</v>
+      </c>
+      <c r="G181" t="n">
+        <v>0</v>
+      </c>
+      <c r="H181" t="n">
+        <v>1</v>
+      </c>
+      <c r="I181" t="n">
+        <v>0</v>
+      </c>
+      <c r="J181" t="inlineStr"/>
+      <c r="K181" t="inlineStr"/>
+      <c r="L181" t="inlineStr"/>
+      <c r="M181" t="inlineStr"/>
+      <c r="N181" t="inlineStr"/>
+      <c r="O181" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -3529,6 +7263,26 @@
         <v>7</v>
       </c>
       <c r="E182" t="n">
+        <v>1</v>
+      </c>
+      <c r="F182" t="n">
+        <v>1</v>
+      </c>
+      <c r="G182" t="n">
+        <v>0</v>
+      </c>
+      <c r="H182" t="n">
+        <v>1</v>
+      </c>
+      <c r="I182" t="n">
+        <v>0</v>
+      </c>
+      <c r="J182" t="inlineStr"/>
+      <c r="K182" t="inlineStr"/>
+      <c r="L182" t="inlineStr"/>
+      <c r="M182" t="inlineStr"/>
+      <c r="N182" t="inlineStr"/>
+      <c r="O182" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -3546,6 +7300,26 @@
         <v>7</v>
       </c>
       <c r="E183" t="n">
+        <v>5</v>
+      </c>
+      <c r="F183" t="n">
+        <v>1</v>
+      </c>
+      <c r="G183" t="n">
+        <v>0</v>
+      </c>
+      <c r="H183" t="n">
+        <v>2</v>
+      </c>
+      <c r="I183" t="n">
+        <v>0</v>
+      </c>
+      <c r="J183" t="inlineStr"/>
+      <c r="K183" t="inlineStr"/>
+      <c r="L183" t="inlineStr"/>
+      <c r="M183" t="inlineStr"/>
+      <c r="N183" t="inlineStr"/>
+      <c r="O183" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -3563,6 +7337,26 @@
         <v>7</v>
       </c>
       <c r="E184" t="n">
+        <v>7</v>
+      </c>
+      <c r="F184" t="n">
+        <v>0</v>
+      </c>
+      <c r="G184" t="n">
+        <v>1</v>
+      </c>
+      <c r="H184" t="n">
+        <v>2</v>
+      </c>
+      <c r="I184" t="n">
+        <v>0</v>
+      </c>
+      <c r="J184" t="inlineStr"/>
+      <c r="K184" t="inlineStr"/>
+      <c r="L184" t="inlineStr"/>
+      <c r="M184" t="inlineStr"/>
+      <c r="N184" t="inlineStr"/>
+      <c r="O184" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -3580,6 +7374,26 @@
         <v>7</v>
       </c>
       <c r="E185" t="n">
+        <v>10</v>
+      </c>
+      <c r="F185" t="n">
+        <v>0</v>
+      </c>
+      <c r="G185" t="n">
+        <v>0</v>
+      </c>
+      <c r="H185" t="n">
+        <v>7</v>
+      </c>
+      <c r="I185" t="n">
+        <v>1</v>
+      </c>
+      <c r="J185" t="inlineStr"/>
+      <c r="K185" t="inlineStr"/>
+      <c r="L185" t="inlineStr"/>
+      <c r="M185" t="inlineStr"/>
+      <c r="N185" t="inlineStr"/>
+      <c r="O185" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -3597,6 +7411,26 @@
         <v>17</v>
       </c>
       <c r="E186" t="n">
+        <v>11</v>
+      </c>
+      <c r="F186" t="n">
+        <v>1</v>
+      </c>
+      <c r="G186" t="n">
+        <v>1</v>
+      </c>
+      <c r="H186" t="n">
+        <v>4</v>
+      </c>
+      <c r="I186" t="n">
+        <v>1</v>
+      </c>
+      <c r="J186" t="inlineStr"/>
+      <c r="K186" t="inlineStr"/>
+      <c r="L186" t="inlineStr"/>
+      <c r="M186" t="inlineStr"/>
+      <c r="N186" t="inlineStr"/>
+      <c r="O186" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -3614,6 +7448,26 @@
         <v>17</v>
       </c>
       <c r="E187" t="n">
+        <v>1</v>
+      </c>
+      <c r="F187" t="n">
+        <v>0</v>
+      </c>
+      <c r="G187" t="n">
+        <v>0</v>
+      </c>
+      <c r="H187" t="n">
+        <v>1</v>
+      </c>
+      <c r="I187" t="n">
+        <v>0</v>
+      </c>
+      <c r="J187" t="inlineStr"/>
+      <c r="K187" t="inlineStr"/>
+      <c r="L187" t="inlineStr"/>
+      <c r="M187" t="inlineStr"/>
+      <c r="N187" t="inlineStr"/>
+      <c r="O187" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -3631,6 +7485,26 @@
         <v>7</v>
       </c>
       <c r="E188" t="n">
+        <v>5</v>
+      </c>
+      <c r="F188" t="n">
+        <v>0</v>
+      </c>
+      <c r="G188" t="n">
+        <v>1</v>
+      </c>
+      <c r="H188" t="n">
+        <v>2</v>
+      </c>
+      <c r="I188" t="n">
+        <v>2</v>
+      </c>
+      <c r="J188" t="inlineStr"/>
+      <c r="K188" t="inlineStr"/>
+      <c r="L188" t="inlineStr"/>
+      <c r="M188" t="inlineStr"/>
+      <c r="N188" t="inlineStr"/>
+      <c r="O188" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -3648,6 +7522,26 @@
         <v>7</v>
       </c>
       <c r="E189" t="n">
+        <v>1</v>
+      </c>
+      <c r="F189" t="n">
+        <v>0</v>
+      </c>
+      <c r="G189" t="n">
+        <v>0</v>
+      </c>
+      <c r="H189" t="n">
+        <v>1</v>
+      </c>
+      <c r="I189" t="n">
+        <v>0</v>
+      </c>
+      <c r="J189" t="inlineStr"/>
+      <c r="K189" t="inlineStr"/>
+      <c r="L189" t="inlineStr"/>
+      <c r="M189" t="inlineStr"/>
+      <c r="N189" t="inlineStr"/>
+      <c r="O189" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -3665,6 +7559,26 @@
         <v>7</v>
       </c>
       <c r="E190" t="n">
+        <v>8</v>
+      </c>
+      <c r="F190" t="n">
+        <v>0</v>
+      </c>
+      <c r="G190" t="n">
+        <v>0</v>
+      </c>
+      <c r="H190" t="n">
+        <v>3</v>
+      </c>
+      <c r="I190" t="n">
+        <v>1</v>
+      </c>
+      <c r="J190" t="inlineStr"/>
+      <c r="K190" t="inlineStr"/>
+      <c r="L190" t="inlineStr"/>
+      <c r="M190" t="inlineStr"/>
+      <c r="N190" t="inlineStr"/>
+      <c r="O190" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -3682,6 +7596,26 @@
         <v>7</v>
       </c>
       <c r="E191" t="n">
+        <v>17</v>
+      </c>
+      <c r="F191" t="n">
+        <v>0</v>
+      </c>
+      <c r="G191" t="n">
+        <v>1</v>
+      </c>
+      <c r="H191" t="n">
+        <v>10</v>
+      </c>
+      <c r="I191" t="n">
+        <v>0</v>
+      </c>
+      <c r="J191" t="inlineStr"/>
+      <c r="K191" t="inlineStr"/>
+      <c r="L191" t="inlineStr"/>
+      <c r="M191" t="inlineStr"/>
+      <c r="N191" t="inlineStr"/>
+      <c r="O191" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -3699,6 +7633,30 @@
         <v>7</v>
       </c>
       <c r="E192" t="n">
+        <v>4</v>
+      </c>
+      <c r="F192" t="inlineStr"/>
+      <c r="G192" t="inlineStr"/>
+      <c r="H192" t="inlineStr"/>
+      <c r="I192" t="n">
+        <v>0</v>
+      </c>
+      <c r="J192" t="n">
+        <v>1</v>
+      </c>
+      <c r="K192" t="n">
+        <v>0</v>
+      </c>
+      <c r="L192" t="n">
+        <v>0</v>
+      </c>
+      <c r="M192" t="n">
+        <v>0</v>
+      </c>
+      <c r="N192" t="n">
+        <v>3</v>
+      </c>
+      <c r="O192" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -3716,6 +7674,30 @@
         <v>17</v>
       </c>
       <c r="E193" t="n">
+        <v>4</v>
+      </c>
+      <c r="F193" t="inlineStr"/>
+      <c r="G193" t="inlineStr"/>
+      <c r="H193" t="inlineStr"/>
+      <c r="I193" t="n">
+        <v>0</v>
+      </c>
+      <c r="J193" t="n">
+        <v>0</v>
+      </c>
+      <c r="K193" t="n">
+        <v>0</v>
+      </c>
+      <c r="L193" t="n">
+        <v>0</v>
+      </c>
+      <c r="M193" t="n">
+        <v>0</v>
+      </c>
+      <c r="N193" t="n">
+        <v>0</v>
+      </c>
+      <c r="O193" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -3733,6 +7715,26 @@
         <v>7</v>
       </c>
       <c r="E194" t="n">
+        <v>8</v>
+      </c>
+      <c r="F194" t="n">
+        <v>0</v>
+      </c>
+      <c r="G194" t="n">
+        <v>0</v>
+      </c>
+      <c r="H194" t="n">
+        <v>10</v>
+      </c>
+      <c r="I194" t="n">
+        <v>0</v>
+      </c>
+      <c r="J194" t="inlineStr"/>
+      <c r="K194" t="inlineStr"/>
+      <c r="L194" t="inlineStr"/>
+      <c r="M194" t="inlineStr"/>
+      <c r="N194" t="inlineStr"/>
+      <c r="O194" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -3750,6 +7752,26 @@
         <v>7</v>
       </c>
       <c r="E195" t="n">
+        <v>2</v>
+      </c>
+      <c r="F195" t="n">
+        <v>1</v>
+      </c>
+      <c r="G195" t="n">
+        <v>0</v>
+      </c>
+      <c r="H195" t="n">
+        <v>2</v>
+      </c>
+      <c r="I195" t="n">
+        <v>0</v>
+      </c>
+      <c r="J195" t="inlineStr"/>
+      <c r="K195" t="inlineStr"/>
+      <c r="L195" t="inlineStr"/>
+      <c r="M195" t="inlineStr"/>
+      <c r="N195" t="inlineStr"/>
+      <c r="O195" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -3767,6 +7789,26 @@
         <v>7</v>
       </c>
       <c r="E196" t="n">
+        <v>4</v>
+      </c>
+      <c r="F196" t="n">
+        <v>0</v>
+      </c>
+      <c r="G196" t="n">
+        <v>0</v>
+      </c>
+      <c r="H196" t="n">
+        <v>3</v>
+      </c>
+      <c r="I196" t="n">
+        <v>2</v>
+      </c>
+      <c r="J196" t="inlineStr"/>
+      <c r="K196" t="inlineStr"/>
+      <c r="L196" t="inlineStr"/>
+      <c r="M196" t="inlineStr"/>
+      <c r="N196" t="inlineStr"/>
+      <c r="O196" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -3784,6 +7826,26 @@
         <v>7</v>
       </c>
       <c r="E197" t="n">
+        <v>2</v>
+      </c>
+      <c r="F197" t="n">
+        <v>0</v>
+      </c>
+      <c r="G197" t="n">
+        <v>0</v>
+      </c>
+      <c r="H197" t="n">
+        <v>1</v>
+      </c>
+      <c r="I197" t="n">
+        <v>0</v>
+      </c>
+      <c r="J197" t="inlineStr"/>
+      <c r="K197" t="inlineStr"/>
+      <c r="L197" t="inlineStr"/>
+      <c r="M197" t="inlineStr"/>
+      <c r="N197" t="inlineStr"/>
+      <c r="O197" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -3801,6 +7863,26 @@
         <v>7</v>
       </c>
       <c r="E198" t="n">
+        <v>15</v>
+      </c>
+      <c r="F198" t="n">
+        <v>0</v>
+      </c>
+      <c r="G198" t="n">
+        <v>0</v>
+      </c>
+      <c r="H198" t="n">
+        <v>19</v>
+      </c>
+      <c r="I198" t="n">
+        <v>1</v>
+      </c>
+      <c r="J198" t="inlineStr"/>
+      <c r="K198" t="inlineStr"/>
+      <c r="L198" t="inlineStr"/>
+      <c r="M198" t="inlineStr"/>
+      <c r="N198" t="inlineStr"/>
+      <c r="O198" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -3818,6 +7900,26 @@
         <v>7</v>
       </c>
       <c r="E199" t="n">
+        <v>2</v>
+      </c>
+      <c r="F199" t="n">
+        <v>0</v>
+      </c>
+      <c r="G199" t="n">
+        <v>0</v>
+      </c>
+      <c r="H199" t="n">
+        <v>1</v>
+      </c>
+      <c r="I199" t="n">
+        <v>0</v>
+      </c>
+      <c r="J199" t="inlineStr"/>
+      <c r="K199" t="inlineStr"/>
+      <c r="L199" t="inlineStr"/>
+      <c r="M199" t="inlineStr"/>
+      <c r="N199" t="inlineStr"/>
+      <c r="O199" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -3835,6 +7937,26 @@
         <v>7</v>
       </c>
       <c r="E200" t="n">
+        <v>0</v>
+      </c>
+      <c r="F200" t="n">
+        <v>0</v>
+      </c>
+      <c r="G200" t="n">
+        <v>0</v>
+      </c>
+      <c r="H200" t="n">
+        <v>0</v>
+      </c>
+      <c r="I200" t="n">
+        <v>0</v>
+      </c>
+      <c r="J200" t="inlineStr"/>
+      <c r="K200" t="inlineStr"/>
+      <c r="L200" t="inlineStr"/>
+      <c r="M200" t="inlineStr"/>
+      <c r="N200" t="inlineStr"/>
+      <c r="O200" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -3852,6 +7974,26 @@
         <v>7</v>
       </c>
       <c r="E201" t="n">
+        <v>2</v>
+      </c>
+      <c r="F201" t="n">
+        <v>1</v>
+      </c>
+      <c r="G201" t="n">
+        <v>0</v>
+      </c>
+      <c r="H201" t="n">
+        <v>4</v>
+      </c>
+      <c r="I201" t="n">
+        <v>0</v>
+      </c>
+      <c r="J201" t="inlineStr"/>
+      <c r="K201" t="inlineStr"/>
+      <c r="L201" t="inlineStr"/>
+      <c r="M201" t="inlineStr"/>
+      <c r="N201" t="inlineStr"/>
+      <c r="O201" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -3869,6 +8011,26 @@
         <v>7</v>
       </c>
       <c r="E202" t="n">
+        <v>2</v>
+      </c>
+      <c r="F202" t="n">
+        <v>0</v>
+      </c>
+      <c r="G202" t="n">
+        <v>0</v>
+      </c>
+      <c r="H202" t="n">
+        <v>1</v>
+      </c>
+      <c r="I202" t="n">
+        <v>0</v>
+      </c>
+      <c r="J202" t="inlineStr"/>
+      <c r="K202" t="inlineStr"/>
+      <c r="L202" t="inlineStr"/>
+      <c r="M202" t="inlineStr"/>
+      <c r="N202" t="inlineStr"/>
+      <c r="O202" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -3886,6 +8048,26 @@
         <v>7</v>
       </c>
       <c r="E203" t="n">
+        <v>0</v>
+      </c>
+      <c r="F203" t="n">
+        <v>0</v>
+      </c>
+      <c r="G203" t="n">
+        <v>0</v>
+      </c>
+      <c r="H203" t="n">
+        <v>1</v>
+      </c>
+      <c r="I203" t="n">
+        <v>0</v>
+      </c>
+      <c r="J203" t="inlineStr"/>
+      <c r="K203" t="inlineStr"/>
+      <c r="L203" t="inlineStr"/>
+      <c r="M203" t="inlineStr"/>
+      <c r="N203" t="inlineStr"/>
+      <c r="O203" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -3903,6 +8085,26 @@
         <v>7</v>
       </c>
       <c r="E204" t="n">
+        <v>3</v>
+      </c>
+      <c r="F204" t="n">
+        <v>0</v>
+      </c>
+      <c r="G204" t="n">
+        <v>0</v>
+      </c>
+      <c r="H204" t="n">
+        <v>1</v>
+      </c>
+      <c r="I204" t="n">
+        <v>1</v>
+      </c>
+      <c r="J204" t="inlineStr"/>
+      <c r="K204" t="inlineStr"/>
+      <c r="L204" t="inlineStr"/>
+      <c r="M204" t="inlineStr"/>
+      <c r="N204" t="inlineStr"/>
+      <c r="O204" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -3920,6 +8122,26 @@
         <v>7</v>
       </c>
       <c r="E205" t="n">
+        <v>4</v>
+      </c>
+      <c r="F205" t="n">
+        <v>0</v>
+      </c>
+      <c r="G205" t="n">
+        <v>0</v>
+      </c>
+      <c r="H205" t="n">
+        <v>1</v>
+      </c>
+      <c r="I205" t="n">
+        <v>0</v>
+      </c>
+      <c r="J205" t="inlineStr"/>
+      <c r="K205" t="inlineStr"/>
+      <c r="L205" t="inlineStr"/>
+      <c r="M205" t="inlineStr"/>
+      <c r="N205" t="inlineStr"/>
+      <c r="O205" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -3937,6 +8159,26 @@
         <v>7</v>
       </c>
       <c r="E206" t="n">
+        <v>4</v>
+      </c>
+      <c r="F206" t="n">
+        <v>0</v>
+      </c>
+      <c r="G206" t="n">
+        <v>0</v>
+      </c>
+      <c r="H206" t="n">
+        <v>3</v>
+      </c>
+      <c r="I206" t="n">
+        <v>0</v>
+      </c>
+      <c r="J206" t="inlineStr"/>
+      <c r="K206" t="inlineStr"/>
+      <c r="L206" t="inlineStr"/>
+      <c r="M206" t="inlineStr"/>
+      <c r="N206" t="inlineStr"/>
+      <c r="O206" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -3954,6 +8196,26 @@
         <v>7</v>
       </c>
       <c r="E207" t="n">
+        <v>5</v>
+      </c>
+      <c r="F207" t="n">
+        <v>0</v>
+      </c>
+      <c r="G207" t="n">
+        <v>0</v>
+      </c>
+      <c r="H207" t="n">
+        <v>0</v>
+      </c>
+      <c r="I207" t="n">
+        <v>0</v>
+      </c>
+      <c r="J207" t="inlineStr"/>
+      <c r="K207" t="inlineStr"/>
+      <c r="L207" t="inlineStr"/>
+      <c r="M207" t="inlineStr"/>
+      <c r="N207" t="inlineStr"/>
+      <c r="O207" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -3971,6 +8233,26 @@
         <v>7</v>
       </c>
       <c r="E208" t="n">
+        <v>2</v>
+      </c>
+      <c r="F208" t="n">
+        <v>0</v>
+      </c>
+      <c r="G208" t="n">
+        <v>0</v>
+      </c>
+      <c r="H208" t="n">
+        <v>4</v>
+      </c>
+      <c r="I208" t="n">
+        <v>0</v>
+      </c>
+      <c r="J208" t="inlineStr"/>
+      <c r="K208" t="inlineStr"/>
+      <c r="L208" t="inlineStr"/>
+      <c r="M208" t="inlineStr"/>
+      <c r="N208" t="inlineStr"/>
+      <c r="O208" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -3988,6 +8270,26 @@
         <v>7</v>
       </c>
       <c r="E209" t="n">
+        <v>0</v>
+      </c>
+      <c r="F209" t="n">
+        <v>0</v>
+      </c>
+      <c r="G209" t="n">
+        <v>0</v>
+      </c>
+      <c r="H209" t="n">
+        <v>0</v>
+      </c>
+      <c r="I209" t="n">
+        <v>0</v>
+      </c>
+      <c r="J209" t="inlineStr"/>
+      <c r="K209" t="inlineStr"/>
+      <c r="L209" t="inlineStr"/>
+      <c r="M209" t="inlineStr"/>
+      <c r="N209" t="inlineStr"/>
+      <c r="O209" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -4005,6 +8307,26 @@
         <v>7</v>
       </c>
       <c r="E210" t="n">
+        <v>4</v>
+      </c>
+      <c r="F210" t="n">
+        <v>0</v>
+      </c>
+      <c r="G210" t="n">
+        <v>0</v>
+      </c>
+      <c r="H210" t="n">
+        <v>3</v>
+      </c>
+      <c r="I210" t="n">
+        <v>2</v>
+      </c>
+      <c r="J210" t="inlineStr"/>
+      <c r="K210" t="inlineStr"/>
+      <c r="L210" t="inlineStr"/>
+      <c r="M210" t="inlineStr"/>
+      <c r="N210" t="inlineStr"/>
+      <c r="O210" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -4022,6 +8344,26 @@
         <v>7</v>
       </c>
       <c r="E211" t="n">
+        <v>6</v>
+      </c>
+      <c r="F211" t="n">
+        <v>0</v>
+      </c>
+      <c r="G211" t="n">
+        <v>0</v>
+      </c>
+      <c r="H211" t="n">
+        <v>4</v>
+      </c>
+      <c r="I211" t="n">
+        <v>0</v>
+      </c>
+      <c r="J211" t="inlineStr"/>
+      <c r="K211" t="inlineStr"/>
+      <c r="L211" t="inlineStr"/>
+      <c r="M211" t="inlineStr"/>
+      <c r="N211" t="inlineStr"/>
+      <c r="O211" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -4039,6 +8381,26 @@
         <v>7</v>
       </c>
       <c r="E212" t="n">
+        <v>15</v>
+      </c>
+      <c r="F212" t="n">
+        <v>0</v>
+      </c>
+      <c r="G212" t="n">
+        <v>0</v>
+      </c>
+      <c r="H212" t="n">
+        <v>8</v>
+      </c>
+      <c r="I212" t="n">
+        <v>7</v>
+      </c>
+      <c r="J212" t="inlineStr"/>
+      <c r="K212" t="inlineStr"/>
+      <c r="L212" t="inlineStr"/>
+      <c r="M212" t="inlineStr"/>
+      <c r="N212" t="inlineStr"/>
+      <c r="O212" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -4056,6 +8418,26 @@
         <v>17</v>
       </c>
       <c r="E213" t="n">
+        <v>17</v>
+      </c>
+      <c r="F213" t="n">
+        <v>0</v>
+      </c>
+      <c r="G213" t="n">
+        <v>0</v>
+      </c>
+      <c r="H213" t="n">
+        <v>8</v>
+      </c>
+      <c r="I213" t="n">
+        <v>1</v>
+      </c>
+      <c r="J213" t="inlineStr"/>
+      <c r="K213" t="inlineStr"/>
+      <c r="L213" t="inlineStr"/>
+      <c r="M213" t="inlineStr"/>
+      <c r="N213" t="inlineStr"/>
+      <c r="O213" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -4073,6 +8455,26 @@
         <v>7</v>
       </c>
       <c r="E214" t="n">
+        <v>1</v>
+      </c>
+      <c r="F214" t="n">
+        <v>0</v>
+      </c>
+      <c r="G214" t="n">
+        <v>1</v>
+      </c>
+      <c r="H214" t="n">
+        <v>1</v>
+      </c>
+      <c r="I214" t="n">
+        <v>0</v>
+      </c>
+      <c r="J214" t="inlineStr"/>
+      <c r="K214" t="inlineStr"/>
+      <c r="L214" t="inlineStr"/>
+      <c r="M214" t="inlineStr"/>
+      <c r="N214" t="inlineStr"/>
+      <c r="O214" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -4090,6 +8492,26 @@
         <v>17</v>
       </c>
       <c r="E215" t="n">
+        <v>4</v>
+      </c>
+      <c r="F215" t="n">
+        <v>0</v>
+      </c>
+      <c r="G215" t="n">
+        <v>0</v>
+      </c>
+      <c r="H215" t="n">
+        <v>0</v>
+      </c>
+      <c r="I215" t="n">
+        <v>0</v>
+      </c>
+      <c r="J215" t="inlineStr"/>
+      <c r="K215" t="inlineStr"/>
+      <c r="L215" t="inlineStr"/>
+      <c r="M215" t="inlineStr"/>
+      <c r="N215" t="inlineStr"/>
+      <c r="O215" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -4107,6 +8529,26 @@
         <v>7</v>
       </c>
       <c r="E216" t="n">
+        <v>4</v>
+      </c>
+      <c r="F216" t="n">
+        <v>0</v>
+      </c>
+      <c r="G216" t="n">
+        <v>0</v>
+      </c>
+      <c r="H216" t="n">
+        <v>4</v>
+      </c>
+      <c r="I216" t="n">
+        <v>0</v>
+      </c>
+      <c r="J216" t="inlineStr"/>
+      <c r="K216" t="inlineStr"/>
+      <c r="L216" t="inlineStr"/>
+      <c r="M216" t="inlineStr"/>
+      <c r="N216" t="inlineStr"/>
+      <c r="O216" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -4124,6 +8566,26 @@
         <v>7</v>
       </c>
       <c r="E217" t="n">
+        <v>2</v>
+      </c>
+      <c r="F217" t="n">
+        <v>0</v>
+      </c>
+      <c r="G217" t="n">
+        <v>0</v>
+      </c>
+      <c r="H217" t="n">
+        <v>2</v>
+      </c>
+      <c r="I217" t="n">
+        <v>0</v>
+      </c>
+      <c r="J217" t="inlineStr"/>
+      <c r="K217" t="inlineStr"/>
+      <c r="L217" t="inlineStr"/>
+      <c r="M217" t="inlineStr"/>
+      <c r="N217" t="inlineStr"/>
+      <c r="O217" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -4141,6 +8603,26 @@
         <v>7</v>
       </c>
       <c r="E218" t="n">
+        <v>1</v>
+      </c>
+      <c r="F218" t="n">
+        <v>0</v>
+      </c>
+      <c r="G218" t="n">
+        <v>0</v>
+      </c>
+      <c r="H218" t="n">
+        <v>2</v>
+      </c>
+      <c r="I218" t="n">
+        <v>0</v>
+      </c>
+      <c r="J218" t="inlineStr"/>
+      <c r="K218" t="inlineStr"/>
+      <c r="L218" t="inlineStr"/>
+      <c r="M218" t="inlineStr"/>
+      <c r="N218" t="inlineStr"/>
+      <c r="O218" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -4158,6 +8640,36 @@
         <v>7</v>
       </c>
       <c r="E219" t="n">
+        <v>1</v>
+      </c>
+      <c r="F219" t="n">
+        <v>0</v>
+      </c>
+      <c r="G219" t="n">
+        <v>0</v>
+      </c>
+      <c r="H219" t="n">
+        <v>0</v>
+      </c>
+      <c r="I219" t="n">
+        <v>0</v>
+      </c>
+      <c r="J219" t="n">
+        <v>0</v>
+      </c>
+      <c r="K219" t="n">
+        <v>0</v>
+      </c>
+      <c r="L219" t="n">
+        <v>0</v>
+      </c>
+      <c r="M219" t="n">
+        <v>0</v>
+      </c>
+      <c r="N219" t="n">
+        <v>0</v>
+      </c>
+      <c r="O219" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -4175,6 +8687,26 @@
         <v>7</v>
       </c>
       <c r="E220" t="n">
+        <v>2</v>
+      </c>
+      <c r="F220" t="n">
+        <v>0</v>
+      </c>
+      <c r="G220" t="n">
+        <v>0</v>
+      </c>
+      <c r="H220" t="n">
+        <v>1</v>
+      </c>
+      <c r="I220" t="n">
+        <v>0</v>
+      </c>
+      <c r="J220" t="inlineStr"/>
+      <c r="K220" t="inlineStr"/>
+      <c r="L220" t="inlineStr"/>
+      <c r="M220" t="inlineStr"/>
+      <c r="N220" t="inlineStr"/>
+      <c r="O220" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -4192,6 +8724,26 @@
         <v>7</v>
       </c>
       <c r="E221" t="n">
+        <v>2</v>
+      </c>
+      <c r="F221" t="n">
+        <v>1</v>
+      </c>
+      <c r="G221" t="n">
+        <v>0</v>
+      </c>
+      <c r="H221" t="n">
+        <v>1</v>
+      </c>
+      <c r="I221" t="n">
+        <v>0</v>
+      </c>
+      <c r="J221" t="inlineStr"/>
+      <c r="K221" t="inlineStr"/>
+      <c r="L221" t="inlineStr"/>
+      <c r="M221" t="inlineStr"/>
+      <c r="N221" t="inlineStr"/>
+      <c r="O221" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -4209,6 +8761,26 @@
         <v>17</v>
       </c>
       <c r="E222" t="n">
+        <v>2</v>
+      </c>
+      <c r="F222" t="n">
+        <v>0</v>
+      </c>
+      <c r="G222" t="n">
+        <v>0</v>
+      </c>
+      <c r="H222" t="n">
+        <v>3</v>
+      </c>
+      <c r="I222" t="n">
+        <v>0</v>
+      </c>
+      <c r="J222" t="inlineStr"/>
+      <c r="K222" t="inlineStr"/>
+      <c r="L222" t="inlineStr"/>
+      <c r="M222" t="inlineStr"/>
+      <c r="N222" t="inlineStr"/>
+      <c r="O222" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -4226,6 +8798,26 @@
         <v>7</v>
       </c>
       <c r="E223" t="n">
+        <v>3</v>
+      </c>
+      <c r="F223" t="n">
+        <v>0</v>
+      </c>
+      <c r="G223" t="n">
+        <v>0</v>
+      </c>
+      <c r="H223" t="n">
+        <v>2</v>
+      </c>
+      <c r="I223" t="n">
+        <v>1</v>
+      </c>
+      <c r="J223" t="inlineStr"/>
+      <c r="K223" t="inlineStr"/>
+      <c r="L223" t="inlineStr"/>
+      <c r="M223" t="inlineStr"/>
+      <c r="N223" t="inlineStr"/>
+      <c r="O223" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -4243,6 +8835,26 @@
         <v>17</v>
       </c>
       <c r="E224" t="n">
+        <v>11</v>
+      </c>
+      <c r="F224" t="n">
+        <v>0</v>
+      </c>
+      <c r="G224" t="n">
+        <v>0</v>
+      </c>
+      <c r="H224" t="n">
+        <v>6</v>
+      </c>
+      <c r="I224" t="n">
+        <v>0</v>
+      </c>
+      <c r="J224" t="inlineStr"/>
+      <c r="K224" t="inlineStr"/>
+      <c r="L224" t="inlineStr"/>
+      <c r="M224" t="inlineStr"/>
+      <c r="N224" t="inlineStr"/>
+      <c r="O224" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -4260,6 +8872,26 @@
         <v>7</v>
       </c>
       <c r="E225" t="n">
+        <v>4</v>
+      </c>
+      <c r="F225" t="n">
+        <v>0</v>
+      </c>
+      <c r="G225" t="n">
+        <v>0</v>
+      </c>
+      <c r="H225" t="n">
+        <v>2</v>
+      </c>
+      <c r="I225" t="n">
+        <v>0</v>
+      </c>
+      <c r="J225" t="inlineStr"/>
+      <c r="K225" t="inlineStr"/>
+      <c r="L225" t="inlineStr"/>
+      <c r="M225" t="inlineStr"/>
+      <c r="N225" t="inlineStr"/>
+      <c r="O225" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -4277,6 +8909,26 @@
         <v>7</v>
       </c>
       <c r="E226" t="n">
+        <v>1</v>
+      </c>
+      <c r="F226" t="n">
+        <v>0</v>
+      </c>
+      <c r="G226" t="n">
+        <v>0</v>
+      </c>
+      <c r="H226" t="n">
+        <v>1</v>
+      </c>
+      <c r="I226" t="n">
+        <v>0</v>
+      </c>
+      <c r="J226" t="inlineStr"/>
+      <c r="K226" t="inlineStr"/>
+      <c r="L226" t="inlineStr"/>
+      <c r="M226" t="inlineStr"/>
+      <c r="N226" t="inlineStr"/>
+      <c r="O226" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -4294,6 +8946,26 @@
         <v>7</v>
       </c>
       <c r="E227" t="n">
+        <v>2</v>
+      </c>
+      <c r="F227" t="n">
+        <v>0</v>
+      </c>
+      <c r="G227" t="n">
+        <v>0</v>
+      </c>
+      <c r="H227" t="n">
+        <v>3</v>
+      </c>
+      <c r="I227" t="n">
+        <v>0</v>
+      </c>
+      <c r="J227" t="inlineStr"/>
+      <c r="K227" t="inlineStr"/>
+      <c r="L227" t="inlineStr"/>
+      <c r="M227" t="inlineStr"/>
+      <c r="N227" t="inlineStr"/>
+      <c r="O227" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -4311,6 +8983,26 @@
         <v>7</v>
       </c>
       <c r="E228" t="n">
+        <v>10</v>
+      </c>
+      <c r="F228" t="n">
+        <v>0</v>
+      </c>
+      <c r="G228" t="n">
+        <v>0</v>
+      </c>
+      <c r="H228" t="n">
+        <v>2</v>
+      </c>
+      <c r="I228" t="n">
+        <v>3</v>
+      </c>
+      <c r="J228" t="inlineStr"/>
+      <c r="K228" t="inlineStr"/>
+      <c r="L228" t="inlineStr"/>
+      <c r="M228" t="inlineStr"/>
+      <c r="N228" t="inlineStr"/>
+      <c r="O228" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -4328,6 +9020,26 @@
         <v>7</v>
       </c>
       <c r="E229" t="n">
+        <v>3</v>
+      </c>
+      <c r="F229" t="n">
+        <v>0</v>
+      </c>
+      <c r="G229" t="n">
+        <v>0</v>
+      </c>
+      <c r="H229" t="n">
+        <v>3</v>
+      </c>
+      <c r="I229" t="n">
+        <v>0</v>
+      </c>
+      <c r="J229" t="inlineStr"/>
+      <c r="K229" t="inlineStr"/>
+      <c r="L229" t="inlineStr"/>
+      <c r="M229" t="inlineStr"/>
+      <c r="N229" t="inlineStr"/>
+      <c r="O229" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -4345,6 +9057,26 @@
         <v>7</v>
       </c>
       <c r="E230" t="n">
+        <v>0</v>
+      </c>
+      <c r="F230" t="n">
+        <v>0</v>
+      </c>
+      <c r="G230" t="n">
+        <v>0</v>
+      </c>
+      <c r="H230" t="n">
+        <v>0</v>
+      </c>
+      <c r="I230" t="n">
+        <v>0</v>
+      </c>
+      <c r="J230" t="inlineStr"/>
+      <c r="K230" t="inlineStr"/>
+      <c r="L230" t="inlineStr"/>
+      <c r="M230" t="inlineStr"/>
+      <c r="N230" t="inlineStr"/>
+      <c r="O230" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -4362,6 +9094,26 @@
         <v>17</v>
       </c>
       <c r="E231" t="n">
+        <v>4</v>
+      </c>
+      <c r="F231" t="n">
+        <v>0</v>
+      </c>
+      <c r="G231" t="n">
+        <v>0</v>
+      </c>
+      <c r="H231" t="n">
+        <v>1</v>
+      </c>
+      <c r="I231" t="n">
+        <v>2</v>
+      </c>
+      <c r="J231" t="inlineStr"/>
+      <c r="K231" t="inlineStr"/>
+      <c r="L231" t="inlineStr"/>
+      <c r="M231" t="inlineStr"/>
+      <c r="N231" t="inlineStr"/>
+      <c r="O231" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -4379,6 +9131,26 @@
         <v>7</v>
       </c>
       <c r="E232" t="n">
+        <v>1</v>
+      </c>
+      <c r="F232" t="n">
+        <v>0</v>
+      </c>
+      <c r="G232" t="n">
+        <v>0</v>
+      </c>
+      <c r="H232" t="n">
+        <v>0</v>
+      </c>
+      <c r="I232" t="n">
+        <v>0</v>
+      </c>
+      <c r="J232" t="inlineStr"/>
+      <c r="K232" t="inlineStr"/>
+      <c r="L232" t="inlineStr"/>
+      <c r="M232" t="inlineStr"/>
+      <c r="N232" t="inlineStr"/>
+      <c r="O232" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -4396,6 +9168,26 @@
         <v>17</v>
       </c>
       <c r="E233" t="n">
+        <v>19</v>
+      </c>
+      <c r="F233" t="n">
+        <v>1</v>
+      </c>
+      <c r="G233" t="n">
+        <v>0</v>
+      </c>
+      <c r="H233" t="n">
+        <v>3</v>
+      </c>
+      <c r="I233" t="n">
+        <v>0</v>
+      </c>
+      <c r="J233" t="inlineStr"/>
+      <c r="K233" t="inlineStr"/>
+      <c r="L233" t="inlineStr"/>
+      <c r="M233" t="inlineStr"/>
+      <c r="N233" t="inlineStr"/>
+      <c r="O233" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -4413,6 +9205,26 @@
         <v>7</v>
       </c>
       <c r="E234" t="n">
+        <v>2</v>
+      </c>
+      <c r="F234" t="n">
+        <v>0</v>
+      </c>
+      <c r="G234" t="n">
+        <v>0</v>
+      </c>
+      <c r="H234" t="n">
+        <v>3</v>
+      </c>
+      <c r="I234" t="n">
+        <v>0</v>
+      </c>
+      <c r="J234" t="inlineStr"/>
+      <c r="K234" t="inlineStr"/>
+      <c r="L234" t="inlineStr"/>
+      <c r="M234" t="inlineStr"/>
+      <c r="N234" t="inlineStr"/>
+      <c r="O234" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -4430,6 +9242,30 @@
         <v>7</v>
       </c>
       <c r="E235" t="n">
+        <v>5</v>
+      </c>
+      <c r="F235" t="inlineStr"/>
+      <c r="G235" t="inlineStr"/>
+      <c r="H235" t="inlineStr"/>
+      <c r="I235" t="n">
+        <v>0</v>
+      </c>
+      <c r="J235" t="n">
+        <v>0</v>
+      </c>
+      <c r="K235" t="n">
+        <v>0</v>
+      </c>
+      <c r="L235" t="n">
+        <v>0</v>
+      </c>
+      <c r="M235" t="n">
+        <v>0</v>
+      </c>
+      <c r="N235" t="n">
+        <v>3</v>
+      </c>
+      <c r="O235" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -4447,6 +9283,30 @@
         <v>17</v>
       </c>
       <c r="E236" t="n">
+        <v>10</v>
+      </c>
+      <c r="F236" t="inlineStr"/>
+      <c r="G236" t="inlineStr"/>
+      <c r="H236" t="inlineStr"/>
+      <c r="I236" t="n">
+        <v>0</v>
+      </c>
+      <c r="J236" t="n">
+        <v>0</v>
+      </c>
+      <c r="K236" t="n">
+        <v>0</v>
+      </c>
+      <c r="L236" t="n">
+        <v>0</v>
+      </c>
+      <c r="M236" t="n">
+        <v>0</v>
+      </c>
+      <c r="N236" t="n">
+        <v>3</v>
+      </c>
+      <c r="O236" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -4464,6 +9324,26 @@
         <v>7</v>
       </c>
       <c r="E237" t="n">
+        <v>2</v>
+      </c>
+      <c r="F237" t="n">
+        <v>0</v>
+      </c>
+      <c r="G237" t="n">
+        <v>0</v>
+      </c>
+      <c r="H237" t="n">
+        <v>1</v>
+      </c>
+      <c r="I237" t="n">
+        <v>0</v>
+      </c>
+      <c r="J237" t="inlineStr"/>
+      <c r="K237" t="inlineStr"/>
+      <c r="L237" t="inlineStr"/>
+      <c r="M237" t="inlineStr"/>
+      <c r="N237" t="inlineStr"/>
+      <c r="O237" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -4481,6 +9361,30 @@
         <v>7</v>
       </c>
       <c r="E238" t="n">
+        <v>9</v>
+      </c>
+      <c r="F238" t="inlineStr"/>
+      <c r="G238" t="inlineStr"/>
+      <c r="H238" t="inlineStr"/>
+      <c r="I238" t="n">
+        <v>1</v>
+      </c>
+      <c r="J238" t="n">
+        <v>0</v>
+      </c>
+      <c r="K238" t="n">
+        <v>1</v>
+      </c>
+      <c r="L238" t="n">
+        <v>0</v>
+      </c>
+      <c r="M238" t="n">
+        <v>0</v>
+      </c>
+      <c r="N238" t="n">
+        <v>3</v>
+      </c>
+      <c r="O238" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -4498,6 +9402,30 @@
         <v>17</v>
       </c>
       <c r="E239" t="n">
+        <v>14</v>
+      </c>
+      <c r="F239" t="inlineStr"/>
+      <c r="G239" t="inlineStr"/>
+      <c r="H239" t="inlineStr"/>
+      <c r="I239" t="n">
+        <v>0</v>
+      </c>
+      <c r="J239" t="n">
+        <v>0</v>
+      </c>
+      <c r="K239" t="n">
+        <v>1</v>
+      </c>
+      <c r="L239" t="n">
+        <v>0</v>
+      </c>
+      <c r="M239" t="n">
+        <v>0</v>
+      </c>
+      <c r="N239" t="n">
+        <v>1</v>
+      </c>
+      <c r="O239" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -4515,6 +9443,26 @@
         <v>7</v>
       </c>
       <c r="E240" t="n">
+        <v>0</v>
+      </c>
+      <c r="F240" t="n">
+        <v>0</v>
+      </c>
+      <c r="G240" t="n">
+        <v>0</v>
+      </c>
+      <c r="H240" t="n">
+        <v>0</v>
+      </c>
+      <c r="I240" t="n">
+        <v>0</v>
+      </c>
+      <c r="J240" t="inlineStr"/>
+      <c r="K240" t="inlineStr"/>
+      <c r="L240" t="inlineStr"/>
+      <c r="M240" t="inlineStr"/>
+      <c r="N240" t="inlineStr"/>
+      <c r="O240" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -4532,6 +9480,26 @@
         <v>7</v>
       </c>
       <c r="E241" t="n">
+        <v>2</v>
+      </c>
+      <c r="F241" t="n">
+        <v>1</v>
+      </c>
+      <c r="G241" t="n">
+        <v>0</v>
+      </c>
+      <c r="H241" t="n">
+        <v>3</v>
+      </c>
+      <c r="I241" t="n">
+        <v>1</v>
+      </c>
+      <c r="J241" t="inlineStr"/>
+      <c r="K241" t="inlineStr"/>
+      <c r="L241" t="inlineStr"/>
+      <c r="M241" t="inlineStr"/>
+      <c r="N241" t="inlineStr"/>
+      <c r="O241" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -4549,6 +9517,30 @@
         <v>7</v>
       </c>
       <c r="E242" t="n">
+        <v>5</v>
+      </c>
+      <c r="F242" t="inlineStr"/>
+      <c r="G242" t="inlineStr"/>
+      <c r="H242" t="inlineStr"/>
+      <c r="I242" t="n">
+        <v>0</v>
+      </c>
+      <c r="J242" t="n">
+        <v>0</v>
+      </c>
+      <c r="K242" t="n">
+        <v>0</v>
+      </c>
+      <c r="L242" t="n">
+        <v>0</v>
+      </c>
+      <c r="M242" t="n">
+        <v>0</v>
+      </c>
+      <c r="N242" t="n">
+        <v>2</v>
+      </c>
+      <c r="O242" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -4566,6 +9558,30 @@
         <v>7</v>
       </c>
       <c r="E243" t="n">
+        <v>4</v>
+      </c>
+      <c r="F243" t="inlineStr"/>
+      <c r="G243" t="inlineStr"/>
+      <c r="H243" t="inlineStr"/>
+      <c r="I243" t="n">
+        <v>0</v>
+      </c>
+      <c r="J243" t="n">
+        <v>6</v>
+      </c>
+      <c r="K243" t="n">
+        <v>0</v>
+      </c>
+      <c r="L243" t="n">
+        <v>0</v>
+      </c>
+      <c r="M243" t="n">
+        <v>0</v>
+      </c>
+      <c r="N243" t="n">
+        <v>0</v>
+      </c>
+      <c r="O243" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -4583,6 +9599,26 @@
         <v>7</v>
       </c>
       <c r="E244" t="n">
+        <v>3</v>
+      </c>
+      <c r="F244" t="n">
+        <v>0</v>
+      </c>
+      <c r="G244" t="n">
+        <v>0</v>
+      </c>
+      <c r="H244" t="n">
+        <v>1</v>
+      </c>
+      <c r="I244" t="n">
+        <v>0</v>
+      </c>
+      <c r="J244" t="inlineStr"/>
+      <c r="K244" t="inlineStr"/>
+      <c r="L244" t="inlineStr"/>
+      <c r="M244" t="inlineStr"/>
+      <c r="N244" t="inlineStr"/>
+      <c r="O244" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -4600,6 +9636,26 @@
         <v>7</v>
       </c>
       <c r="E245" t="n">
+        <v>6</v>
+      </c>
+      <c r="F245" t="n">
+        <v>0</v>
+      </c>
+      <c r="G245" t="n">
+        <v>0</v>
+      </c>
+      <c r="H245" t="n">
+        <v>8</v>
+      </c>
+      <c r="I245" t="n">
+        <v>1</v>
+      </c>
+      <c r="J245" t="inlineStr"/>
+      <c r="K245" t="inlineStr"/>
+      <c r="L245" t="inlineStr"/>
+      <c r="M245" t="inlineStr"/>
+      <c r="N245" t="inlineStr"/>
+      <c r="O245" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -4617,6 +9673,26 @@
         <v>17</v>
       </c>
       <c r="E246" t="n">
+        <v>10</v>
+      </c>
+      <c r="F246" t="n">
+        <v>0</v>
+      </c>
+      <c r="G246" t="n">
+        <v>0</v>
+      </c>
+      <c r="H246" t="n">
+        <v>5</v>
+      </c>
+      <c r="I246" t="n">
+        <v>1</v>
+      </c>
+      <c r="J246" t="inlineStr"/>
+      <c r="K246" t="inlineStr"/>
+      <c r="L246" t="inlineStr"/>
+      <c r="M246" t="inlineStr"/>
+      <c r="N246" t="inlineStr"/>
+      <c r="O246" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -4634,6 +9710,26 @@
         <v>7</v>
       </c>
       <c r="E247" t="n">
+        <v>7</v>
+      </c>
+      <c r="F247" t="n">
+        <v>0</v>
+      </c>
+      <c r="G247" t="n">
+        <v>0</v>
+      </c>
+      <c r="H247" t="n">
+        <v>4</v>
+      </c>
+      <c r="I247" t="n">
+        <v>2</v>
+      </c>
+      <c r="J247" t="inlineStr"/>
+      <c r="K247" t="inlineStr"/>
+      <c r="L247" t="inlineStr"/>
+      <c r="M247" t="inlineStr"/>
+      <c r="N247" t="inlineStr"/>
+      <c r="O247" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -4651,6 +9747,26 @@
         <v>17</v>
       </c>
       <c r="E248" t="n">
+        <v>14</v>
+      </c>
+      <c r="F248" t="n">
+        <v>0</v>
+      </c>
+      <c r="G248" t="n">
+        <v>2</v>
+      </c>
+      <c r="H248" t="n">
+        <v>7</v>
+      </c>
+      <c r="I248" t="n">
+        <v>1</v>
+      </c>
+      <c r="J248" t="inlineStr"/>
+      <c r="K248" t="inlineStr"/>
+      <c r="L248" t="inlineStr"/>
+      <c r="M248" t="inlineStr"/>
+      <c r="N248" t="inlineStr"/>
+      <c r="O248" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -4668,6 +9784,26 @@
         <v>7</v>
       </c>
       <c r="E249" t="n">
+        <v>0</v>
+      </c>
+      <c r="F249" t="n">
+        <v>0</v>
+      </c>
+      <c r="G249" t="n">
+        <v>0</v>
+      </c>
+      <c r="H249" t="n">
+        <v>0</v>
+      </c>
+      <c r="I249" t="n">
+        <v>0</v>
+      </c>
+      <c r="J249" t="inlineStr"/>
+      <c r="K249" t="inlineStr"/>
+      <c r="L249" t="inlineStr"/>
+      <c r="M249" t="inlineStr"/>
+      <c r="N249" t="inlineStr"/>
+      <c r="O249" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -4685,6 +9821,26 @@
         <v>17</v>
       </c>
       <c r="E250" t="n">
+        <v>0</v>
+      </c>
+      <c r="F250" t="n">
+        <v>0</v>
+      </c>
+      <c r="G250" t="n">
+        <v>0</v>
+      </c>
+      <c r="H250" t="n">
+        <v>0</v>
+      </c>
+      <c r="I250" t="n">
+        <v>0</v>
+      </c>
+      <c r="J250" t="inlineStr"/>
+      <c r="K250" t="inlineStr"/>
+      <c r="L250" t="inlineStr"/>
+      <c r="M250" t="inlineStr"/>
+      <c r="N250" t="inlineStr"/>
+      <c r="O250" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -4702,6 +9858,26 @@
         <v>7</v>
       </c>
       <c r="E251" t="n">
+        <v>2</v>
+      </c>
+      <c r="F251" t="n">
+        <v>0</v>
+      </c>
+      <c r="G251" t="n">
+        <v>0</v>
+      </c>
+      <c r="H251" t="n">
+        <v>1</v>
+      </c>
+      <c r="I251" t="n">
+        <v>0</v>
+      </c>
+      <c r="J251" t="inlineStr"/>
+      <c r="K251" t="inlineStr"/>
+      <c r="L251" t="inlineStr"/>
+      <c r="M251" t="inlineStr"/>
+      <c r="N251" t="inlineStr"/>
+      <c r="O251" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -4719,6 +9895,26 @@
         <v>7</v>
       </c>
       <c r="E252" t="n">
+        <v>1</v>
+      </c>
+      <c r="F252" t="n">
+        <v>0</v>
+      </c>
+      <c r="G252" t="n">
+        <v>0</v>
+      </c>
+      <c r="H252" t="n">
+        <v>1</v>
+      </c>
+      <c r="I252" t="n">
+        <v>0</v>
+      </c>
+      <c r="J252" t="inlineStr"/>
+      <c r="K252" t="inlineStr"/>
+      <c r="L252" t="inlineStr"/>
+      <c r="M252" t="inlineStr"/>
+      <c r="N252" t="inlineStr"/>
+      <c r="O252" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -4736,6 +9932,26 @@
         <v>7</v>
       </c>
       <c r="E253" t="n">
+        <v>3</v>
+      </c>
+      <c r="F253" t="n">
+        <v>1</v>
+      </c>
+      <c r="G253" t="n">
+        <v>0</v>
+      </c>
+      <c r="H253" t="n">
+        <v>3</v>
+      </c>
+      <c r="I253" t="n">
+        <v>0</v>
+      </c>
+      <c r="J253" t="inlineStr"/>
+      <c r="K253" t="inlineStr"/>
+      <c r="L253" t="inlineStr"/>
+      <c r="M253" t="inlineStr"/>
+      <c r="N253" t="inlineStr"/>
+      <c r="O253" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -4753,6 +9969,26 @@
         <v>7</v>
       </c>
       <c r="E254" t="n">
+        <v>5</v>
+      </c>
+      <c r="F254" t="n">
+        <v>0</v>
+      </c>
+      <c r="G254" t="n">
+        <v>1</v>
+      </c>
+      <c r="H254" t="n">
+        <v>1</v>
+      </c>
+      <c r="I254" t="n">
+        <v>0</v>
+      </c>
+      <c r="J254" t="inlineStr"/>
+      <c r="K254" t="inlineStr"/>
+      <c r="L254" t="inlineStr"/>
+      <c r="M254" t="inlineStr"/>
+      <c r="N254" t="inlineStr"/>
+      <c r="O254" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -4770,6 +10006,26 @@
         <v>7</v>
       </c>
       <c r="E255" t="n">
+        <v>4</v>
+      </c>
+      <c r="F255" t="n">
+        <v>0</v>
+      </c>
+      <c r="G255" t="n">
+        <v>0</v>
+      </c>
+      <c r="H255" t="n">
+        <v>5</v>
+      </c>
+      <c r="I255" t="n">
+        <v>0</v>
+      </c>
+      <c r="J255" t="inlineStr"/>
+      <c r="K255" t="inlineStr"/>
+      <c r="L255" t="inlineStr"/>
+      <c r="M255" t="inlineStr"/>
+      <c r="N255" t="inlineStr"/>
+      <c r="O255" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -4787,6 +10043,26 @@
         <v>7</v>
       </c>
       <c r="E256" t="n">
+        <v>2</v>
+      </c>
+      <c r="F256" t="n">
+        <v>0</v>
+      </c>
+      <c r="G256" t="n">
+        <v>0</v>
+      </c>
+      <c r="H256" t="n">
+        <v>1</v>
+      </c>
+      <c r="I256" t="n">
+        <v>0</v>
+      </c>
+      <c r="J256" t="inlineStr"/>
+      <c r="K256" t="inlineStr"/>
+      <c r="L256" t="inlineStr"/>
+      <c r="M256" t="inlineStr"/>
+      <c r="N256" t="inlineStr"/>
+      <c r="O256" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -4804,6 +10080,26 @@
         <v>7</v>
       </c>
       <c r="E257" t="n">
+        <v>12</v>
+      </c>
+      <c r="F257" t="n">
+        <v>0</v>
+      </c>
+      <c r="G257" t="n">
+        <v>1</v>
+      </c>
+      <c r="H257" t="n">
+        <v>3</v>
+      </c>
+      <c r="I257" t="n">
+        <v>0</v>
+      </c>
+      <c r="J257" t="inlineStr"/>
+      <c r="K257" t="inlineStr"/>
+      <c r="L257" t="inlineStr"/>
+      <c r="M257" t="inlineStr"/>
+      <c r="N257" t="inlineStr"/>
+      <c r="O257" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -4821,6 +10117,26 @@
         <v>7</v>
       </c>
       <c r="E258" t="n">
+        <v>1</v>
+      </c>
+      <c r="F258" t="n">
+        <v>0</v>
+      </c>
+      <c r="G258" t="n">
+        <v>1</v>
+      </c>
+      <c r="H258" t="n">
+        <v>0</v>
+      </c>
+      <c r="I258" t="n">
+        <v>0</v>
+      </c>
+      <c r="J258" t="inlineStr"/>
+      <c r="K258" t="inlineStr"/>
+      <c r="L258" t="inlineStr"/>
+      <c r="M258" t="inlineStr"/>
+      <c r="N258" t="inlineStr"/>
+      <c r="O258" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -4838,6 +10154,26 @@
         <v>7</v>
       </c>
       <c r="E259" t="n">
+        <v>2</v>
+      </c>
+      <c r="F259" t="n">
+        <v>0</v>
+      </c>
+      <c r="G259" t="n">
+        <v>1</v>
+      </c>
+      <c r="H259" t="n">
+        <v>1</v>
+      </c>
+      <c r="I259" t="n">
+        <v>0</v>
+      </c>
+      <c r="J259" t="inlineStr"/>
+      <c r="K259" t="inlineStr"/>
+      <c r="L259" t="inlineStr"/>
+      <c r="M259" t="inlineStr"/>
+      <c r="N259" t="inlineStr"/>
+      <c r="O259" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -4855,6 +10191,26 @@
         <v>7</v>
       </c>
       <c r="E260" t="n">
+        <v>5</v>
+      </c>
+      <c r="F260" t="n">
+        <v>0</v>
+      </c>
+      <c r="G260" t="n">
+        <v>0</v>
+      </c>
+      <c r="H260" t="n">
+        <v>3</v>
+      </c>
+      <c r="I260" t="n">
+        <v>0</v>
+      </c>
+      <c r="J260" t="inlineStr"/>
+      <c r="K260" t="inlineStr"/>
+      <c r="L260" t="inlineStr"/>
+      <c r="M260" t="inlineStr"/>
+      <c r="N260" t="inlineStr"/>
+      <c r="O260" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -4872,6 +10228,26 @@
         <v>7</v>
       </c>
       <c r="E261" t="n">
+        <v>3</v>
+      </c>
+      <c r="F261" t="n">
+        <v>0</v>
+      </c>
+      <c r="G261" t="n">
+        <v>1</v>
+      </c>
+      <c r="H261" t="n">
+        <v>1</v>
+      </c>
+      <c r="I261" t="n">
+        <v>0</v>
+      </c>
+      <c r="J261" t="inlineStr"/>
+      <c r="K261" t="inlineStr"/>
+      <c r="L261" t="inlineStr"/>
+      <c r="M261" t="inlineStr"/>
+      <c r="N261" t="inlineStr"/>
+      <c r="O261" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -4889,6 +10265,26 @@
         <v>17</v>
       </c>
       <c r="E262" t="n">
+        <v>15</v>
+      </c>
+      <c r="F262" t="n">
+        <v>0</v>
+      </c>
+      <c r="G262" t="n">
+        <v>1</v>
+      </c>
+      <c r="H262" t="n">
+        <v>1</v>
+      </c>
+      <c r="I262" t="n">
+        <v>0</v>
+      </c>
+      <c r="J262" t="inlineStr"/>
+      <c r="K262" t="inlineStr"/>
+      <c r="L262" t="inlineStr"/>
+      <c r="M262" t="inlineStr"/>
+      <c r="N262" t="inlineStr"/>
+      <c r="O262" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -4906,6 +10302,26 @@
         <v>7</v>
       </c>
       <c r="E263" t="n">
+        <v>7</v>
+      </c>
+      <c r="F263" t="n">
+        <v>0</v>
+      </c>
+      <c r="G263" t="n">
+        <v>1</v>
+      </c>
+      <c r="H263" t="n">
+        <v>4</v>
+      </c>
+      <c r="I263" t="n">
+        <v>0</v>
+      </c>
+      <c r="J263" t="inlineStr"/>
+      <c r="K263" t="inlineStr"/>
+      <c r="L263" t="inlineStr"/>
+      <c r="M263" t="inlineStr"/>
+      <c r="N263" t="inlineStr"/>
+      <c r="O263" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -4923,6 +10339,26 @@
         <v>17</v>
       </c>
       <c r="E264" t="n">
+        <v>2</v>
+      </c>
+      <c r="F264" t="n">
+        <v>0</v>
+      </c>
+      <c r="G264" t="n">
+        <v>0</v>
+      </c>
+      <c r="H264" t="n">
+        <v>1</v>
+      </c>
+      <c r="I264" t="n">
+        <v>0</v>
+      </c>
+      <c r="J264" t="inlineStr"/>
+      <c r="K264" t="inlineStr"/>
+      <c r="L264" t="inlineStr"/>
+      <c r="M264" t="inlineStr"/>
+      <c r="N264" t="inlineStr"/>
+      <c r="O264" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -4940,6 +10376,26 @@
         <v>7</v>
       </c>
       <c r="E265" t="n">
+        <v>10</v>
+      </c>
+      <c r="F265" t="n">
+        <v>1</v>
+      </c>
+      <c r="G265" t="n">
+        <v>0</v>
+      </c>
+      <c r="H265" t="n">
+        <v>1</v>
+      </c>
+      <c r="I265" t="n">
+        <v>0</v>
+      </c>
+      <c r="J265" t="inlineStr"/>
+      <c r="K265" t="inlineStr"/>
+      <c r="L265" t="inlineStr"/>
+      <c r="M265" t="inlineStr"/>
+      <c r="N265" t="inlineStr"/>
+      <c r="O265" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -4957,6 +10413,26 @@
         <v>17</v>
       </c>
       <c r="E266" t="n">
+        <v>35</v>
+      </c>
+      <c r="F266" t="n">
+        <v>1</v>
+      </c>
+      <c r="G266" t="n">
+        <v>0</v>
+      </c>
+      <c r="H266" t="n">
+        <v>10</v>
+      </c>
+      <c r="I266" t="n">
+        <v>1</v>
+      </c>
+      <c r="J266" t="inlineStr"/>
+      <c r="K266" t="inlineStr"/>
+      <c r="L266" t="inlineStr"/>
+      <c r="M266" t="inlineStr"/>
+      <c r="N266" t="inlineStr"/>
+      <c r="O266" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -4974,6 +10450,26 @@
         <v>7</v>
       </c>
       <c r="E267" t="n">
+        <v>6</v>
+      </c>
+      <c r="F267" t="n">
+        <v>0</v>
+      </c>
+      <c r="G267" t="n">
+        <v>1</v>
+      </c>
+      <c r="H267" t="n">
+        <v>0</v>
+      </c>
+      <c r="I267" t="n">
+        <v>0</v>
+      </c>
+      <c r="J267" t="inlineStr"/>
+      <c r="K267" t="inlineStr"/>
+      <c r="L267" t="inlineStr"/>
+      <c r="M267" t="inlineStr"/>
+      <c r="N267" t="inlineStr"/>
+      <c r="O267" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -4991,6 +10487,26 @@
         <v>7</v>
       </c>
       <c r="E268" t="n">
+        <v>4</v>
+      </c>
+      <c r="F268" t="n">
+        <v>0</v>
+      </c>
+      <c r="G268" t="n">
+        <v>0</v>
+      </c>
+      <c r="H268" t="n">
+        <v>0</v>
+      </c>
+      <c r="I268" t="n">
+        <v>0</v>
+      </c>
+      <c r="J268" t="inlineStr"/>
+      <c r="K268" t="inlineStr"/>
+      <c r="L268" t="inlineStr"/>
+      <c r="M268" t="inlineStr"/>
+      <c r="N268" t="inlineStr"/>
+      <c r="O268" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -5008,6 +10524,26 @@
         <v>17</v>
       </c>
       <c r="E269" t="n">
+        <v>2</v>
+      </c>
+      <c r="F269" t="n">
+        <v>0</v>
+      </c>
+      <c r="G269" t="n">
+        <v>0</v>
+      </c>
+      <c r="H269" t="n">
+        <v>1</v>
+      </c>
+      <c r="I269" t="n">
+        <v>0</v>
+      </c>
+      <c r="J269" t="inlineStr"/>
+      <c r="K269" t="inlineStr"/>
+      <c r="L269" t="inlineStr"/>
+      <c r="M269" t="inlineStr"/>
+      <c r="N269" t="inlineStr"/>
+      <c r="O269" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -5025,6 +10561,26 @@
         <v>7</v>
       </c>
       <c r="E270" t="n">
+        <v>2</v>
+      </c>
+      <c r="F270" t="n">
+        <v>0</v>
+      </c>
+      <c r="G270" t="n">
+        <v>1</v>
+      </c>
+      <c r="H270" t="n">
+        <v>2</v>
+      </c>
+      <c r="I270" t="n">
+        <v>0</v>
+      </c>
+      <c r="J270" t="inlineStr"/>
+      <c r="K270" t="inlineStr"/>
+      <c r="L270" t="inlineStr"/>
+      <c r="M270" t="inlineStr"/>
+      <c r="N270" t="inlineStr"/>
+      <c r="O270" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -5042,6 +10598,26 @@
         <v>7</v>
       </c>
       <c r="E271" t="n">
+        <v>3</v>
+      </c>
+      <c r="F271" t="n">
+        <v>0</v>
+      </c>
+      <c r="G271" t="n">
+        <v>0</v>
+      </c>
+      <c r="H271" t="n">
+        <v>4</v>
+      </c>
+      <c r="I271" t="n">
+        <v>1</v>
+      </c>
+      <c r="J271" t="inlineStr"/>
+      <c r="K271" t="inlineStr"/>
+      <c r="L271" t="inlineStr"/>
+      <c r="M271" t="inlineStr"/>
+      <c r="N271" t="inlineStr"/>
+      <c r="O271" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -5059,6 +10635,26 @@
         <v>7</v>
       </c>
       <c r="E272" t="n">
+        <v>3</v>
+      </c>
+      <c r="F272" t="n">
+        <v>0</v>
+      </c>
+      <c r="G272" t="n">
+        <v>0</v>
+      </c>
+      <c r="H272" t="n">
+        <v>3</v>
+      </c>
+      <c r="I272" t="n">
+        <v>0</v>
+      </c>
+      <c r="J272" t="inlineStr"/>
+      <c r="K272" t="inlineStr"/>
+      <c r="L272" t="inlineStr"/>
+      <c r="M272" t="inlineStr"/>
+      <c r="N272" t="inlineStr"/>
+      <c r="O272" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -5076,6 +10672,26 @@
         <v>7</v>
       </c>
       <c r="E273" t="n">
+        <v>1</v>
+      </c>
+      <c r="F273" t="n">
+        <v>0</v>
+      </c>
+      <c r="G273" t="n">
+        <v>0</v>
+      </c>
+      <c r="H273" t="n">
+        <v>1</v>
+      </c>
+      <c r="I273" t="n">
+        <v>0</v>
+      </c>
+      <c r="J273" t="inlineStr"/>
+      <c r="K273" t="inlineStr"/>
+      <c r="L273" t="inlineStr"/>
+      <c r="M273" t="inlineStr"/>
+      <c r="N273" t="inlineStr"/>
+      <c r="O273" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -5093,6 +10709,26 @@
         <v>7</v>
       </c>
       <c r="E274" t="n">
+        <v>4</v>
+      </c>
+      <c r="F274" t="n">
+        <v>0</v>
+      </c>
+      <c r="G274" t="n">
+        <v>0</v>
+      </c>
+      <c r="H274" t="n">
+        <v>3</v>
+      </c>
+      <c r="I274" t="n">
+        <v>0</v>
+      </c>
+      <c r="J274" t="inlineStr"/>
+      <c r="K274" t="inlineStr"/>
+      <c r="L274" t="inlineStr"/>
+      <c r="M274" t="inlineStr"/>
+      <c r="N274" t="inlineStr"/>
+      <c r="O274" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -5110,6 +10746,26 @@
         <v>17</v>
       </c>
       <c r="E275" t="n">
+        <v>11</v>
+      </c>
+      <c r="F275" t="n">
+        <v>0</v>
+      </c>
+      <c r="G275" t="n">
+        <v>1</v>
+      </c>
+      <c r="H275" t="n">
+        <v>7</v>
+      </c>
+      <c r="I275" t="n">
+        <v>1</v>
+      </c>
+      <c r="J275" t="inlineStr"/>
+      <c r="K275" t="inlineStr"/>
+      <c r="L275" t="inlineStr"/>
+      <c r="M275" t="inlineStr"/>
+      <c r="N275" t="inlineStr"/>
+      <c r="O275" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -5127,6 +10783,26 @@
         <v>7</v>
       </c>
       <c r="E276" t="n">
+        <v>0</v>
+      </c>
+      <c r="F276" t="n">
+        <v>0</v>
+      </c>
+      <c r="G276" t="n">
+        <v>0</v>
+      </c>
+      <c r="H276" t="n">
+        <v>0</v>
+      </c>
+      <c r="I276" t="n">
+        <v>0</v>
+      </c>
+      <c r="J276" t="inlineStr"/>
+      <c r="K276" t="inlineStr"/>
+      <c r="L276" t="inlineStr"/>
+      <c r="M276" t="inlineStr"/>
+      <c r="N276" t="inlineStr"/>
+      <c r="O276" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -5144,6 +10820,26 @@
         <v>7</v>
       </c>
       <c r="E277" t="n">
+        <v>10</v>
+      </c>
+      <c r="F277" t="n">
+        <v>0</v>
+      </c>
+      <c r="G277" t="n">
+        <v>0</v>
+      </c>
+      <c r="H277" t="n">
+        <v>6</v>
+      </c>
+      <c r="I277" t="n">
+        <v>0</v>
+      </c>
+      <c r="J277" t="inlineStr"/>
+      <c r="K277" t="inlineStr"/>
+      <c r="L277" t="inlineStr"/>
+      <c r="M277" t="inlineStr"/>
+      <c r="N277" t="inlineStr"/>
+      <c r="O277" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -5161,6 +10857,26 @@
         <v>7</v>
       </c>
       <c r="E278" t="n">
+        <v>0</v>
+      </c>
+      <c r="F278" t="n">
+        <v>0</v>
+      </c>
+      <c r="G278" t="n">
+        <v>0</v>
+      </c>
+      <c r="H278" t="n">
+        <v>0</v>
+      </c>
+      <c r="I278" t="n">
+        <v>0</v>
+      </c>
+      <c r="J278" t="inlineStr"/>
+      <c r="K278" t="inlineStr"/>
+      <c r="L278" t="inlineStr"/>
+      <c r="M278" t="inlineStr"/>
+      <c r="N278" t="inlineStr"/>
+      <c r="O278" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -5178,6 +10894,26 @@
         <v>7</v>
       </c>
       <c r="E279" t="n">
+        <v>5</v>
+      </c>
+      <c r="F279" t="n">
+        <v>0</v>
+      </c>
+      <c r="G279" t="n">
+        <v>0</v>
+      </c>
+      <c r="H279" t="n">
+        <v>4</v>
+      </c>
+      <c r="I279" t="n">
+        <v>0</v>
+      </c>
+      <c r="J279" t="inlineStr"/>
+      <c r="K279" t="inlineStr"/>
+      <c r="L279" t="inlineStr"/>
+      <c r="M279" t="inlineStr"/>
+      <c r="N279" t="inlineStr"/>
+      <c r="O279" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -5195,6 +10931,26 @@
         <v>17</v>
       </c>
       <c r="E280" t="n">
+        <v>1</v>
+      </c>
+      <c r="F280" t="n">
+        <v>0</v>
+      </c>
+      <c r="G280" t="n">
+        <v>0</v>
+      </c>
+      <c r="H280" t="n">
+        <v>2</v>
+      </c>
+      <c r="I280" t="n">
+        <v>0</v>
+      </c>
+      <c r="J280" t="inlineStr"/>
+      <c r="K280" t="inlineStr"/>
+      <c r="L280" t="inlineStr"/>
+      <c r="M280" t="inlineStr"/>
+      <c r="N280" t="inlineStr"/>
+      <c r="O280" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -5212,6 +10968,26 @@
         <v>7</v>
       </c>
       <c r="E281" t="n">
+        <v>6</v>
+      </c>
+      <c r="F281" t="n">
+        <v>0</v>
+      </c>
+      <c r="G281" t="n">
+        <v>1</v>
+      </c>
+      <c r="H281" t="n">
+        <v>5</v>
+      </c>
+      <c r="I281" t="n">
+        <v>0</v>
+      </c>
+      <c r="J281" t="inlineStr"/>
+      <c r="K281" t="inlineStr"/>
+      <c r="L281" t="inlineStr"/>
+      <c r="M281" t="inlineStr"/>
+      <c r="N281" t="inlineStr"/>
+      <c r="O281" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -5229,6 +11005,26 @@
         <v>17</v>
       </c>
       <c r="E282" t="n">
+        <v>3</v>
+      </c>
+      <c r="F282" t="n">
+        <v>0</v>
+      </c>
+      <c r="G282" t="n">
+        <v>0</v>
+      </c>
+      <c r="H282" t="n">
+        <v>2</v>
+      </c>
+      <c r="I282" t="n">
+        <v>0</v>
+      </c>
+      <c r="J282" t="inlineStr"/>
+      <c r="K282" t="inlineStr"/>
+      <c r="L282" t="inlineStr"/>
+      <c r="M282" t="inlineStr"/>
+      <c r="N282" t="inlineStr"/>
+      <c r="O282" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -5246,6 +11042,26 @@
         <v>7</v>
       </c>
       <c r="E283" t="n">
+        <v>1</v>
+      </c>
+      <c r="F283" t="n">
+        <v>0</v>
+      </c>
+      <c r="G283" t="n">
+        <v>0</v>
+      </c>
+      <c r="H283" t="n">
+        <v>2</v>
+      </c>
+      <c r="I283" t="n">
+        <v>0</v>
+      </c>
+      <c r="J283" t="inlineStr"/>
+      <c r="K283" t="inlineStr"/>
+      <c r="L283" t="inlineStr"/>
+      <c r="M283" t="inlineStr"/>
+      <c r="N283" t="inlineStr"/>
+      <c r="O283" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -5263,6 +11079,26 @@
         <v>7</v>
       </c>
       <c r="E284" t="n">
+        <v>11</v>
+      </c>
+      <c r="F284" t="n">
+        <v>0</v>
+      </c>
+      <c r="G284" t="n">
+        <v>0</v>
+      </c>
+      <c r="H284" t="n">
+        <v>13</v>
+      </c>
+      <c r="I284" t="n">
+        <v>0</v>
+      </c>
+      <c r="J284" t="inlineStr"/>
+      <c r="K284" t="inlineStr"/>
+      <c r="L284" t="inlineStr"/>
+      <c r="M284" t="inlineStr"/>
+      <c r="N284" t="inlineStr"/>
+      <c r="O284" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -5280,6 +11116,26 @@
         <v>7</v>
       </c>
       <c r="E285" t="n">
+        <v>0</v>
+      </c>
+      <c r="F285" t="n">
+        <v>0</v>
+      </c>
+      <c r="G285" t="n">
+        <v>0</v>
+      </c>
+      <c r="H285" t="n">
+        <v>0</v>
+      </c>
+      <c r="I285" t="n">
+        <v>0</v>
+      </c>
+      <c r="J285" t="inlineStr"/>
+      <c r="K285" t="inlineStr"/>
+      <c r="L285" t="inlineStr"/>
+      <c r="M285" t="inlineStr"/>
+      <c r="N285" t="inlineStr"/>
+      <c r="O285" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -5297,6 +11153,30 @@
         <v>7</v>
       </c>
       <c r="E286" t="n">
+        <v>3</v>
+      </c>
+      <c r="F286" t="inlineStr"/>
+      <c r="G286" t="inlineStr"/>
+      <c r="H286" t="inlineStr"/>
+      <c r="I286" t="n">
+        <v>0</v>
+      </c>
+      <c r="J286" t="n">
+        <v>0</v>
+      </c>
+      <c r="K286" t="n">
+        <v>0</v>
+      </c>
+      <c r="L286" t="n">
+        <v>0</v>
+      </c>
+      <c r="M286" t="n">
+        <v>0</v>
+      </c>
+      <c r="N286" t="n">
+        <v>0</v>
+      </c>
+      <c r="O286" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -5314,6 +11194,26 @@
         <v>7</v>
       </c>
       <c r="E287" t="n">
+        <v>16</v>
+      </c>
+      <c r="F287" t="n">
+        <v>1</v>
+      </c>
+      <c r="G287" t="n">
+        <v>1</v>
+      </c>
+      <c r="H287" t="n">
+        <v>10</v>
+      </c>
+      <c r="I287" t="n">
+        <v>6</v>
+      </c>
+      <c r="J287" t="inlineStr"/>
+      <c r="K287" t="inlineStr"/>
+      <c r="L287" t="inlineStr"/>
+      <c r="M287" t="inlineStr"/>
+      <c r="N287" t="inlineStr"/>
+      <c r="O287" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -5331,6 +11231,26 @@
         <v>7</v>
       </c>
       <c r="E288" t="n">
+        <v>7</v>
+      </c>
+      <c r="F288" t="n">
+        <v>0</v>
+      </c>
+      <c r="G288" t="n">
+        <v>0</v>
+      </c>
+      <c r="H288" t="n">
+        <v>6</v>
+      </c>
+      <c r="I288" t="n">
+        <v>0</v>
+      </c>
+      <c r="J288" t="inlineStr"/>
+      <c r="K288" t="inlineStr"/>
+      <c r="L288" t="inlineStr"/>
+      <c r="M288" t="inlineStr"/>
+      <c r="N288" t="inlineStr"/>
+      <c r="O288" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -5348,6 +11268,30 @@
         <v>7</v>
       </c>
       <c r="E289" t="n">
+        <v>14</v>
+      </c>
+      <c r="F289" t="inlineStr"/>
+      <c r="G289" t="inlineStr"/>
+      <c r="H289" t="inlineStr"/>
+      <c r="I289" t="n">
+        <v>0</v>
+      </c>
+      <c r="J289" t="n">
+        <v>0</v>
+      </c>
+      <c r="K289" t="n">
+        <v>0</v>
+      </c>
+      <c r="L289" t="n">
+        <v>0</v>
+      </c>
+      <c r="M289" t="n">
+        <v>0</v>
+      </c>
+      <c r="N289" t="n">
+        <v>11</v>
+      </c>
+      <c r="O289" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -5365,6 +11309,30 @@
         <v>17</v>
       </c>
       <c r="E290" t="n">
+        <v>16</v>
+      </c>
+      <c r="F290" t="inlineStr"/>
+      <c r="G290" t="inlineStr"/>
+      <c r="H290" t="inlineStr"/>
+      <c r="I290" t="n">
+        <v>0</v>
+      </c>
+      <c r="J290" t="n">
+        <v>0</v>
+      </c>
+      <c r="K290" t="n">
+        <v>0</v>
+      </c>
+      <c r="L290" t="n">
+        <v>0</v>
+      </c>
+      <c r="M290" t="n">
+        <v>0</v>
+      </c>
+      <c r="N290" t="n">
+        <v>11</v>
+      </c>
+      <c r="O290" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -5382,6 +11350,30 @@
         <v>7</v>
       </c>
       <c r="E291" t="n">
+        <v>2</v>
+      </c>
+      <c r="F291" t="inlineStr"/>
+      <c r="G291" t="inlineStr"/>
+      <c r="H291" t="inlineStr"/>
+      <c r="I291" t="n">
+        <v>0</v>
+      </c>
+      <c r="J291" t="n">
+        <v>0</v>
+      </c>
+      <c r="K291" t="n">
+        <v>0</v>
+      </c>
+      <c r="L291" t="n">
+        <v>0</v>
+      </c>
+      <c r="M291" t="n">
+        <v>0</v>
+      </c>
+      <c r="N291" t="n">
+        <v>0</v>
+      </c>
+      <c r="O291" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -5399,6 +11391,30 @@
         <v>17</v>
       </c>
       <c r="E292" t="n">
+        <v>3</v>
+      </c>
+      <c r="F292" t="inlineStr"/>
+      <c r="G292" t="inlineStr"/>
+      <c r="H292" t="inlineStr"/>
+      <c r="I292" t="n">
+        <v>0</v>
+      </c>
+      <c r="J292" t="n">
+        <v>0</v>
+      </c>
+      <c r="K292" t="n">
+        <v>0</v>
+      </c>
+      <c r="L292" t="n">
+        <v>0</v>
+      </c>
+      <c r="M292" t="n">
+        <v>0</v>
+      </c>
+      <c r="N292" t="n">
+        <v>2</v>
+      </c>
+      <c r="O292" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -5416,6 +11432,26 @@
         <v>7</v>
       </c>
       <c r="E293" t="n">
+        <v>0</v>
+      </c>
+      <c r="F293" t="n">
+        <v>0</v>
+      </c>
+      <c r="G293" t="n">
+        <v>0</v>
+      </c>
+      <c r="H293" t="n">
+        <v>0</v>
+      </c>
+      <c r="I293" t="n">
+        <v>0</v>
+      </c>
+      <c r="J293" t="inlineStr"/>
+      <c r="K293" t="inlineStr"/>
+      <c r="L293" t="inlineStr"/>
+      <c r="M293" t="inlineStr"/>
+      <c r="N293" t="inlineStr"/>
+      <c r="O293" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -5433,6 +11469,26 @@
         <v>17</v>
       </c>
       <c r="E294" t="n">
+        <v>2</v>
+      </c>
+      <c r="F294" t="n">
+        <v>0</v>
+      </c>
+      <c r="G294" t="n">
+        <v>0</v>
+      </c>
+      <c r="H294" t="n">
+        <v>1</v>
+      </c>
+      <c r="I294" t="n">
+        <v>1</v>
+      </c>
+      <c r="J294" t="inlineStr"/>
+      <c r="K294" t="inlineStr"/>
+      <c r="L294" t="inlineStr"/>
+      <c r="M294" t="inlineStr"/>
+      <c r="N294" t="inlineStr"/>
+      <c r="O294" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -5450,6 +11506,30 @@
         <v>7</v>
       </c>
       <c r="E295" t="n">
+        <v>3</v>
+      </c>
+      <c r="F295" t="inlineStr"/>
+      <c r="G295" t="inlineStr"/>
+      <c r="H295" t="inlineStr"/>
+      <c r="I295" t="n">
+        <v>0</v>
+      </c>
+      <c r="J295" t="n">
+        <v>0</v>
+      </c>
+      <c r="K295" t="n">
+        <v>0</v>
+      </c>
+      <c r="L295" t="n">
+        <v>0</v>
+      </c>
+      <c r="M295" t="n">
+        <v>1</v>
+      </c>
+      <c r="N295" t="n">
+        <v>0</v>
+      </c>
+      <c r="O295" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -5467,6 +11547,26 @@
         <v>7</v>
       </c>
       <c r="E296" t="n">
+        <v>1</v>
+      </c>
+      <c r="F296" t="n">
+        <v>0</v>
+      </c>
+      <c r="G296" t="n">
+        <v>1</v>
+      </c>
+      <c r="H296" t="n">
+        <v>0</v>
+      </c>
+      <c r="I296" t="n">
+        <v>0</v>
+      </c>
+      <c r="J296" t="inlineStr"/>
+      <c r="K296" t="inlineStr"/>
+      <c r="L296" t="inlineStr"/>
+      <c r="M296" t="inlineStr"/>
+      <c r="N296" t="inlineStr"/>
+      <c r="O296" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -5484,6 +11584,26 @@
         <v>7</v>
       </c>
       <c r="E297" t="n">
+        <v>4</v>
+      </c>
+      <c r="F297" t="n">
+        <v>2</v>
+      </c>
+      <c r="G297" t="n">
+        <v>0</v>
+      </c>
+      <c r="H297" t="n">
+        <v>1</v>
+      </c>
+      <c r="I297" t="n">
+        <v>0</v>
+      </c>
+      <c r="J297" t="inlineStr"/>
+      <c r="K297" t="inlineStr"/>
+      <c r="L297" t="inlineStr"/>
+      <c r="M297" t="inlineStr"/>
+      <c r="N297" t="inlineStr"/>
+      <c r="O297" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -5501,6 +11621,26 @@
         <v>7</v>
       </c>
       <c r="E298" t="n">
+        <v>4</v>
+      </c>
+      <c r="F298" t="n">
+        <v>1</v>
+      </c>
+      <c r="G298" t="n">
+        <v>0</v>
+      </c>
+      <c r="H298" t="n">
+        <v>1</v>
+      </c>
+      <c r="I298" t="n">
+        <v>0</v>
+      </c>
+      <c r="J298" t="inlineStr"/>
+      <c r="K298" t="inlineStr"/>
+      <c r="L298" t="inlineStr"/>
+      <c r="M298" t="inlineStr"/>
+      <c r="N298" t="inlineStr"/>
+      <c r="O298" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -5518,6 +11658,26 @@
         <v>17</v>
       </c>
       <c r="E299" t="n">
+        <v>14</v>
+      </c>
+      <c r="F299" t="n">
+        <v>0</v>
+      </c>
+      <c r="G299" t="n">
+        <v>0</v>
+      </c>
+      <c r="H299" t="n">
+        <v>2</v>
+      </c>
+      <c r="I299" t="n">
+        <v>1</v>
+      </c>
+      <c r="J299" t="inlineStr"/>
+      <c r="K299" t="inlineStr"/>
+      <c r="L299" t="inlineStr"/>
+      <c r="M299" t="inlineStr"/>
+      <c r="N299" t="inlineStr"/>
+      <c r="O299" t="n">
         <v>2009</v>
       </c>
     </row>

--- a/Excel Files IPEDS/Trimmed/c2009_trimmed_file.xlsx
+++ b/Excel Files IPEDS/Trimmed/c2009_trimmed_file.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q299"/>
+  <dimension ref="A1:T299"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,30 +486,45 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>CRACE19</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>CBKAAT</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>CASIAT</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>CNHPIT</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>CHISPT</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>CWHITT</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>C2MORT</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>CNRALT</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
@@ -549,12 +564,19 @@
       <c r="K2" t="n">
         <v>0</v>
       </c>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="n">
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="n">
+        <v>2</v>
+      </c>
+      <c r="T2" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -592,12 +614,19 @@
       <c r="K3" t="n">
         <v>0</v>
       </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="n">
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="n">
+        <v>7</v>
+      </c>
+      <c r="T3" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -635,12 +664,19 @@
       <c r="K4" t="n">
         <v>0</v>
       </c>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="n">
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="n">
+        <v>4</v>
+      </c>
+      <c r="T4" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -678,12 +714,19 @@
       <c r="K5" t="n">
         <v>0</v>
       </c>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="n">
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="n">
+        <v>3</v>
+      </c>
+      <c r="T5" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -721,12 +764,19 @@
       <c r="K6" t="n">
         <v>0</v>
       </c>
-      <c r="L6" t="inlineStr"/>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="n">
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="n">
+        <v>4</v>
+      </c>
+      <c r="T6" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -764,12 +814,19 @@
       <c r="K7" t="n">
         <v>0</v>
       </c>
-      <c r="L7" t="inlineStr"/>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="n">
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -807,12 +864,19 @@
       <c r="K8" t="n">
         <v>1</v>
       </c>
-      <c r="L8" t="inlineStr"/>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="n">
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -850,12 +914,19 @@
       <c r="K9" t="n">
         <v>1</v>
       </c>
-      <c r="L9" t="inlineStr"/>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="n">
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="n">
+        <v>8</v>
+      </c>
+      <c r="T9" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -885,9 +956,7 @@
       <c r="K10" t="n">
         <v>1</v>
       </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>0</v>
       </c>
@@ -898,9 +967,18 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
         <v>5</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -930,9 +1008,7 @@
       <c r="K11" t="n">
         <v>0</v>
       </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>0</v>
       </c>
@@ -943,9 +1019,18 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
         <v>5</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -975,9 +1060,7 @@
       <c r="K12" t="n">
         <v>0</v>
       </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
         <v>0</v>
       </c>
@@ -985,12 +1068,21 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q12" t="n">
         <v>5</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -1028,12 +1120,19 @@
       <c r="K13" t="n">
         <v>0</v>
       </c>
-      <c r="L13" t="inlineStr"/>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="n">
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="n">
+        <v>2</v>
+      </c>
+      <c r="T13" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -1071,12 +1170,19 @@
       <c r="K14" t="n">
         <v>0</v>
       </c>
-      <c r="L14" t="inlineStr"/>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="n">
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="n">
+        <v>7</v>
+      </c>
+      <c r="T14" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -1114,12 +1220,19 @@
       <c r="K15" t="n">
         <v>0</v>
       </c>
-      <c r="L15" t="inlineStr"/>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="n">
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -1157,12 +1270,19 @@
       <c r="K16" t="n">
         <v>0</v>
       </c>
-      <c r="L16" t="inlineStr"/>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="n">
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -1200,12 +1320,19 @@
       <c r="K17" t="n">
         <v>6</v>
       </c>
-      <c r="L17" t="inlineStr"/>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="n">
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -1243,12 +1370,19 @@
       <c r="K18" t="n">
         <v>1</v>
       </c>
-      <c r="L18" t="inlineStr"/>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="n">
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -1286,12 +1420,19 @@
       <c r="K19" t="n">
         <v>0</v>
       </c>
-      <c r="L19" t="inlineStr"/>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="n">
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="n">
+        <v>2</v>
+      </c>
+      <c r="T19" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -1329,12 +1470,19 @@
       <c r="K20" t="n">
         <v>0</v>
       </c>
-      <c r="L20" t="inlineStr"/>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="n">
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -1372,12 +1520,19 @@
       <c r="K21" t="n">
         <v>1</v>
       </c>
-      <c r="L21" t="inlineStr"/>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="n">
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="n">
+        <v>2</v>
+      </c>
+      <c r="T21" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -1415,12 +1570,19 @@
       <c r="K22" t="n">
         <v>2</v>
       </c>
-      <c r="L22" t="inlineStr"/>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="n">
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -1458,12 +1620,19 @@
       <c r="K23" t="n">
         <v>2</v>
       </c>
-      <c r="L23" t="inlineStr"/>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="n">
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="n">
+        <v>6</v>
+      </c>
+      <c r="T23" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -1501,12 +1670,19 @@
       <c r="K24" t="n">
         <v>1</v>
       </c>
-      <c r="L24" t="inlineStr"/>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="n">
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="n">
+        <v>2</v>
+      </c>
+      <c r="T24" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -1544,12 +1720,19 @@
       <c r="K25" t="n">
         <v>1</v>
       </c>
-      <c r="L25" t="inlineStr"/>
+      <c r="L25" t="n">
+        <v>1</v>
+      </c>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="n">
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="n">
+        <v>11</v>
+      </c>
+      <c r="T25" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -1587,12 +1770,19 @@
       <c r="K26" t="n">
         <v>3</v>
       </c>
-      <c r="L26" t="inlineStr"/>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="n">
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -1630,12 +1820,19 @@
       <c r="K27" t="n">
         <v>4</v>
       </c>
-      <c r="L27" t="inlineStr"/>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="n">
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -1673,12 +1870,19 @@
       <c r="K28" t="n">
         <v>0</v>
       </c>
-      <c r="L28" t="inlineStr"/>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="n">
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="n">
+        <v>14</v>
+      </c>
+      <c r="T28" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -1716,12 +1920,19 @@
       <c r="K29" t="n">
         <v>4</v>
       </c>
-      <c r="L29" t="inlineStr"/>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="n">
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -1759,12 +1970,19 @@
       <c r="K30" t="n">
         <v>3</v>
       </c>
-      <c r="L30" t="inlineStr"/>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="n">
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -1802,12 +2020,19 @@
       <c r="K31" t="n">
         <v>0</v>
       </c>
-      <c r="L31" t="inlineStr"/>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="n">
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="n">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -1845,12 +2070,19 @@
       <c r="K32" t="n">
         <v>0</v>
       </c>
-      <c r="L32" t="inlineStr"/>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="n">
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="n">
+        <v>3</v>
+      </c>
+      <c r="T32" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -1888,12 +2120,19 @@
       <c r="K33" t="n">
         <v>2</v>
       </c>
-      <c r="L33" t="inlineStr"/>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="n">
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="n">
+        <v>9</v>
+      </c>
+      <c r="T33" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -1931,12 +2170,19 @@
       <c r="K34" t="n">
         <v>0</v>
       </c>
-      <c r="L34" t="inlineStr"/>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="n">
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -1974,12 +2220,19 @@
       <c r="K35" t="n">
         <v>1</v>
       </c>
-      <c r="L35" t="inlineStr"/>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="n">
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="n">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -2009,9 +2262,7 @@
       <c r="K36" t="n">
         <v>0</v>
       </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
+      <c r="L36" t="inlineStr"/>
       <c r="M36" t="n">
         <v>0</v>
       </c>
@@ -2025,6 +2276,15 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -2062,12 +2322,19 @@
       <c r="K37" t="n">
         <v>3</v>
       </c>
-      <c r="L37" t="inlineStr"/>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="n">
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="n">
+        <v>7</v>
+      </c>
+      <c r="T37" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -2105,12 +2372,19 @@
       <c r="K38" t="n">
         <v>1</v>
       </c>
-      <c r="L38" t="inlineStr"/>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="n">
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="n">
+        <v>3</v>
+      </c>
+      <c r="T38" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -2148,12 +2422,19 @@
       <c r="K39" t="n">
         <v>0</v>
       </c>
-      <c r="L39" t="inlineStr"/>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="n">
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="n">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -2191,12 +2472,19 @@
       <c r="K40" t="n">
         <v>0</v>
       </c>
-      <c r="L40" t="inlineStr"/>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="n">
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -2234,12 +2522,19 @@
       <c r="K41" t="n">
         <v>1</v>
       </c>
-      <c r="L41" t="inlineStr"/>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="n">
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -2277,12 +2572,19 @@
       <c r="K42" t="n">
         <v>1</v>
       </c>
-      <c r="L42" t="inlineStr"/>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="n">
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="n">
+        <v>3</v>
+      </c>
+      <c r="T42" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -2320,12 +2622,19 @@
       <c r="K43" t="n">
         <v>0</v>
       </c>
-      <c r="L43" t="inlineStr"/>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="n">
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -2363,12 +2672,19 @@
       <c r="K44" t="n">
         <v>0</v>
       </c>
-      <c r="L44" t="inlineStr"/>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="n">
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="n">
+        <v>3</v>
+      </c>
+      <c r="T44" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -2406,12 +2722,19 @@
       <c r="K45" t="n">
         <v>4</v>
       </c>
-      <c r="L45" t="inlineStr"/>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="n">
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -2449,12 +2772,19 @@
       <c r="K46" t="n">
         <v>0</v>
       </c>
-      <c r="L46" t="inlineStr"/>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="n">
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -2492,12 +2822,19 @@
       <c r="K47" t="n">
         <v>0</v>
       </c>
-      <c r="L47" t="inlineStr"/>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="n">
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr"/>
+      <c r="S47" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -2535,12 +2872,19 @@
       <c r="K48" t="n">
         <v>0</v>
       </c>
-      <c r="L48" t="inlineStr"/>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="n">
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr"/>
+      <c r="S48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -2578,12 +2922,19 @@
       <c r="K49" t="n">
         <v>0</v>
       </c>
-      <c r="L49" t="inlineStr"/>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="n">
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr"/>
+      <c r="S49" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -2621,12 +2972,19 @@
       <c r="K50" t="n">
         <v>0</v>
       </c>
-      <c r="L50" t="inlineStr"/>
+      <c r="L50" t="n">
+        <v>0</v>
+      </c>
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="n">
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr"/>
+      <c r="S50" t="n">
+        <v>2</v>
+      </c>
+      <c r="T50" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -2664,12 +3022,19 @@
       <c r="K51" t="n">
         <v>0</v>
       </c>
-      <c r="L51" t="inlineStr"/>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="n">
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr"/>
+      <c r="S51" t="n">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -2707,12 +3072,19 @@
       <c r="K52" t="n">
         <v>0</v>
       </c>
-      <c r="L52" t="inlineStr"/>
+      <c r="L52" t="n">
+        <v>0</v>
+      </c>
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="n">
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr"/>
+      <c r="S52" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -2750,12 +3122,19 @@
       <c r="K53" t="n">
         <v>0</v>
       </c>
-      <c r="L53" t="inlineStr"/>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="n">
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr"/>
+      <c r="S53" t="n">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -2793,12 +3172,19 @@
       <c r="K54" t="n">
         <v>1</v>
       </c>
-      <c r="L54" t="inlineStr"/>
+      <c r="L54" t="n">
+        <v>1</v>
+      </c>
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="n">
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr"/>
+      <c r="S54" t="n">
+        <v>6</v>
+      </c>
+      <c r="T54" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -2836,12 +3222,19 @@
       <c r="K55" t="n">
         <v>0</v>
       </c>
-      <c r="L55" t="inlineStr"/>
+      <c r="L55" t="n">
+        <v>0</v>
+      </c>
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="n">
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr"/>
+      <c r="S55" t="n">
+        <v>4</v>
+      </c>
+      <c r="T55" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -2879,12 +3272,19 @@
       <c r="K56" t="n">
         <v>1</v>
       </c>
-      <c r="L56" t="inlineStr"/>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
       <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="n">
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr"/>
+      <c r="S56" t="n">
+        <v>4</v>
+      </c>
+      <c r="T56" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -2922,12 +3322,19 @@
       <c r="K57" t="n">
         <v>0</v>
       </c>
-      <c r="L57" t="inlineStr"/>
+      <c r="L57" t="n">
+        <v>0</v>
+      </c>
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="n">
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr"/>
+      <c r="S57" t="n">
+        <v>3</v>
+      </c>
+      <c r="T57" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -2965,12 +3372,19 @@
       <c r="K58" t="n">
         <v>0</v>
       </c>
-      <c r="L58" t="inlineStr"/>
+      <c r="L58" t="n">
+        <v>0</v>
+      </c>
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr"/>
-      <c r="Q58" t="n">
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr"/>
+      <c r="S58" t="n">
+        <v>2</v>
+      </c>
+      <c r="T58" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -3000,9 +3414,7 @@
       <c r="K59" t="n">
         <v>1</v>
       </c>
-      <c r="L59" t="n">
-        <v>0</v>
-      </c>
+      <c r="L59" t="inlineStr"/>
       <c r="M59" t="n">
         <v>0</v>
       </c>
@@ -3016,6 +3428,15 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
+        <v>0</v>
+      </c>
+      <c r="R59" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -3053,12 +3474,19 @@
       <c r="K60" t="n">
         <v>0</v>
       </c>
-      <c r="L60" t="inlineStr"/>
+      <c r="L60" t="n">
+        <v>0</v>
+      </c>
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr"/>
-      <c r="Q60" t="n">
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr"/>
+      <c r="S60" t="n">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -3088,9 +3516,7 @@
       <c r="K61" t="n">
         <v>0</v>
       </c>
-      <c r="L61" t="n">
-        <v>0</v>
-      </c>
+      <c r="L61" t="inlineStr"/>
       <c r="M61" t="n">
         <v>0</v>
       </c>
@@ -3101,9 +3527,18 @@
         <v>0</v>
       </c>
       <c r="P61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q61" t="n">
         <v>5</v>
       </c>
-      <c r="Q61" t="n">
+      <c r="R61" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" t="n">
+        <v>5</v>
+      </c>
+      <c r="T61" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -3133,22 +3568,29 @@
       <c r="K62" t="n">
         <v>0</v>
       </c>
-      <c r="L62" t="n">
-        <v>0</v>
-      </c>
+      <c r="L62" t="inlineStr"/>
       <c r="M62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
       </c>
       <c r="P62" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
+        <v>7</v>
+      </c>
+      <c r="R62" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" t="n">
+        <v>11</v>
+      </c>
+      <c r="T62" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -3186,12 +3628,19 @@
       <c r="K63" t="n">
         <v>2</v>
       </c>
-      <c r="L63" t="inlineStr"/>
+      <c r="L63" t="n">
+        <v>0</v>
+      </c>
       <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
       <c r="O63" t="inlineStr"/>
       <c r="P63" t="inlineStr"/>
-      <c r="Q63" t="n">
+      <c r="Q63" t="inlineStr"/>
+      <c r="R63" t="inlineStr"/>
+      <c r="S63" t="n">
+        <v>3</v>
+      </c>
+      <c r="T63" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -3229,12 +3678,19 @@
       <c r="K64" t="n">
         <v>0</v>
       </c>
-      <c r="L64" t="inlineStr"/>
+      <c r="L64" t="n">
+        <v>0</v>
+      </c>
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
       <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr"/>
-      <c r="Q64" t="n">
+      <c r="Q64" t="inlineStr"/>
+      <c r="R64" t="inlineStr"/>
+      <c r="S64" t="n">
+        <v>3</v>
+      </c>
+      <c r="T64" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -3272,12 +3728,19 @@
       <c r="K65" t="n">
         <v>0</v>
       </c>
-      <c r="L65" t="inlineStr"/>
+      <c r="L65" t="n">
+        <v>0</v>
+      </c>
       <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="O65" t="inlineStr"/>
       <c r="P65" t="inlineStr"/>
-      <c r="Q65" t="n">
+      <c r="Q65" t="inlineStr"/>
+      <c r="R65" t="inlineStr"/>
+      <c r="S65" t="n">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -3315,12 +3778,19 @@
       <c r="K66" t="n">
         <v>0</v>
       </c>
-      <c r="L66" t="inlineStr"/>
+      <c r="L66" t="n">
+        <v>0</v>
+      </c>
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="O66" t="inlineStr"/>
       <c r="P66" t="inlineStr"/>
-      <c r="Q66" t="n">
+      <c r="Q66" t="inlineStr"/>
+      <c r="R66" t="inlineStr"/>
+      <c r="S66" t="n">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -3358,12 +3828,19 @@
       <c r="K67" t="n">
         <v>1</v>
       </c>
-      <c r="L67" t="inlineStr"/>
+      <c r="L67" t="n">
+        <v>0</v>
+      </c>
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr"/>
       <c r="P67" t="inlineStr"/>
-      <c r="Q67" t="n">
+      <c r="Q67" t="inlineStr"/>
+      <c r="R67" t="inlineStr"/>
+      <c r="S67" t="n">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -3401,12 +3878,19 @@
       <c r="K68" t="n">
         <v>3</v>
       </c>
-      <c r="L68" t="inlineStr"/>
+      <c r="L68" t="n">
+        <v>0</v>
+      </c>
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr"/>
       <c r="P68" t="inlineStr"/>
-      <c r="Q68" t="n">
+      <c r="Q68" t="inlineStr"/>
+      <c r="R68" t="inlineStr"/>
+      <c r="S68" t="n">
+        <v>7</v>
+      </c>
+      <c r="T68" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -3444,12 +3928,19 @@
       <c r="K69" t="n">
         <v>0</v>
       </c>
-      <c r="L69" t="inlineStr"/>
+      <c r="L69" t="n">
+        <v>0</v>
+      </c>
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr"/>
       <c r="P69" t="inlineStr"/>
-      <c r="Q69" t="n">
+      <c r="Q69" t="inlineStr"/>
+      <c r="R69" t="inlineStr"/>
+      <c r="S69" t="n">
+        <v>12</v>
+      </c>
+      <c r="T69" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -3479,9 +3970,7 @@
       <c r="K70" t="n">
         <v>0</v>
       </c>
-      <c r="L70" t="n">
-        <v>0</v>
-      </c>
+      <c r="L70" t="inlineStr"/>
       <c r="M70" t="n">
         <v>0</v>
       </c>
@@ -3489,12 +3978,21 @@
         <v>0</v>
       </c>
       <c r="O70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P70" t="n">
         <v>1</v>
       </c>
       <c r="Q70" t="n">
+        <v>1</v>
+      </c>
+      <c r="R70" t="n">
+        <v>0</v>
+      </c>
+      <c r="S70" t="n">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -3524,9 +4022,7 @@
       <c r="K71" t="n">
         <v>0</v>
       </c>
-      <c r="L71" t="n">
-        <v>0</v>
-      </c>
+      <c r="L71" t="inlineStr"/>
       <c r="M71" t="n">
         <v>0</v>
       </c>
@@ -3540,6 +4036,15 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
+        <v>0</v>
+      </c>
+      <c r="R71" t="n">
+        <v>0</v>
+      </c>
+      <c r="S71" t="n">
+        <v>0</v>
+      </c>
+      <c r="T71" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -3577,12 +4082,19 @@
       <c r="K72" t="n">
         <v>1</v>
       </c>
-      <c r="L72" t="inlineStr"/>
+      <c r="L72" t="n">
+        <v>0</v>
+      </c>
       <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr"/>
       <c r="P72" t="inlineStr"/>
-      <c r="Q72" t="n">
+      <c r="Q72" t="inlineStr"/>
+      <c r="R72" t="inlineStr"/>
+      <c r="S72" t="n">
+        <v>8</v>
+      </c>
+      <c r="T72" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -3620,12 +4132,19 @@
       <c r="K73" t="n">
         <v>0</v>
       </c>
-      <c r="L73" t="inlineStr"/>
+      <c r="L73" t="n">
+        <v>0</v>
+      </c>
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr"/>
       <c r="P73" t="inlineStr"/>
-      <c r="Q73" t="n">
+      <c r="Q73" t="inlineStr"/>
+      <c r="R73" t="inlineStr"/>
+      <c r="S73" t="n">
+        <v>3</v>
+      </c>
+      <c r="T73" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -3663,12 +4182,19 @@
       <c r="K74" t="n">
         <v>0</v>
       </c>
-      <c r="L74" t="inlineStr"/>
+      <c r="L74" t="n">
+        <v>0</v>
+      </c>
       <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr"/>
       <c r="P74" t="inlineStr"/>
-      <c r="Q74" t="n">
+      <c r="Q74" t="inlineStr"/>
+      <c r="R74" t="inlineStr"/>
+      <c r="S74" t="n">
+        <v>11</v>
+      </c>
+      <c r="T74" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -3706,12 +4232,19 @@
       <c r="K75" t="n">
         <v>0</v>
       </c>
-      <c r="L75" t="inlineStr"/>
+      <c r="L75" t="n">
+        <v>0</v>
+      </c>
       <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr"/>
       <c r="P75" t="inlineStr"/>
-      <c r="Q75" t="n">
+      <c r="Q75" t="inlineStr"/>
+      <c r="R75" t="inlineStr"/>
+      <c r="S75" t="n">
+        <v>14</v>
+      </c>
+      <c r="T75" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -3749,12 +4282,19 @@
       <c r="K76" t="n">
         <v>1</v>
       </c>
-      <c r="L76" t="inlineStr"/>
+      <c r="L76" t="n">
+        <v>0</v>
+      </c>
       <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr"/>
       <c r="P76" t="inlineStr"/>
-      <c r="Q76" t="n">
+      <c r="Q76" t="inlineStr"/>
+      <c r="R76" t="inlineStr"/>
+      <c r="S76" t="n">
+        <v>3</v>
+      </c>
+      <c r="T76" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -3792,12 +4332,19 @@
       <c r="K77" t="n">
         <v>1</v>
       </c>
-      <c r="L77" t="inlineStr"/>
+      <c r="L77" t="n">
+        <v>0</v>
+      </c>
       <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr"/>
       <c r="P77" t="inlineStr"/>
-      <c r="Q77" t="n">
+      <c r="Q77" t="inlineStr"/>
+      <c r="R77" t="inlineStr"/>
+      <c r="S77" t="n">
+        <v>0</v>
+      </c>
+      <c r="T77" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -3835,12 +4382,19 @@
       <c r="K78" t="n">
         <v>0</v>
       </c>
-      <c r="L78" t="inlineStr"/>
+      <c r="L78" t="n">
+        <v>0</v>
+      </c>
       <c r="M78" t="inlineStr"/>
       <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr"/>
       <c r="P78" t="inlineStr"/>
-      <c r="Q78" t="n">
+      <c r="Q78" t="inlineStr"/>
+      <c r="R78" t="inlineStr"/>
+      <c r="S78" t="n">
+        <v>1</v>
+      </c>
+      <c r="T78" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -3878,12 +4432,19 @@
       <c r="K79" t="n">
         <v>1</v>
       </c>
-      <c r="L79" t="inlineStr"/>
+      <c r="L79" t="n">
+        <v>0</v>
+      </c>
       <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr"/>
       <c r="O79" t="inlineStr"/>
       <c r="P79" t="inlineStr"/>
-      <c r="Q79" t="n">
+      <c r="Q79" t="inlineStr"/>
+      <c r="R79" t="inlineStr"/>
+      <c r="S79" t="n">
+        <v>5</v>
+      </c>
+      <c r="T79" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -3921,12 +4482,19 @@
       <c r="K80" t="n">
         <v>0</v>
       </c>
-      <c r="L80" t="inlineStr"/>
+      <c r="L80" t="n">
+        <v>0</v>
+      </c>
       <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr"/>
       <c r="P80" t="inlineStr"/>
-      <c r="Q80" t="n">
+      <c r="Q80" t="inlineStr"/>
+      <c r="R80" t="inlineStr"/>
+      <c r="S80" t="n">
+        <v>0</v>
+      </c>
+      <c r="T80" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -3964,12 +4532,19 @@
       <c r="K81" t="n">
         <v>0</v>
       </c>
-      <c r="L81" t="inlineStr"/>
+      <c r="L81" t="n">
+        <v>0</v>
+      </c>
       <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr"/>
       <c r="O81" t="inlineStr"/>
       <c r="P81" t="inlineStr"/>
-      <c r="Q81" t="n">
+      <c r="Q81" t="inlineStr"/>
+      <c r="R81" t="inlineStr"/>
+      <c r="S81" t="n">
+        <v>0</v>
+      </c>
+      <c r="T81" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -4007,12 +4582,19 @@
       <c r="K82" t="n">
         <v>0</v>
       </c>
-      <c r="L82" t="inlineStr"/>
+      <c r="L82" t="n">
+        <v>0</v>
+      </c>
       <c r="M82" t="inlineStr"/>
       <c r="N82" t="inlineStr"/>
       <c r="O82" t="inlineStr"/>
       <c r="P82" t="inlineStr"/>
-      <c r="Q82" t="n">
+      <c r="Q82" t="inlineStr"/>
+      <c r="R82" t="inlineStr"/>
+      <c r="S82" t="n">
+        <v>0</v>
+      </c>
+      <c r="T82" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -4050,12 +4632,19 @@
       <c r="K83" t="n">
         <v>0</v>
       </c>
-      <c r="L83" t="inlineStr"/>
+      <c r="L83" t="n">
+        <v>0</v>
+      </c>
       <c r="M83" t="inlineStr"/>
       <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr"/>
       <c r="P83" t="inlineStr"/>
-      <c r="Q83" t="n">
+      <c r="Q83" t="inlineStr"/>
+      <c r="R83" t="inlineStr"/>
+      <c r="S83" t="n">
+        <v>2</v>
+      </c>
+      <c r="T83" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -4093,12 +4682,19 @@
       <c r="K84" t="n">
         <v>1</v>
       </c>
-      <c r="L84" t="inlineStr"/>
+      <c r="L84" t="n">
+        <v>0</v>
+      </c>
       <c r="M84" t="inlineStr"/>
       <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr"/>
       <c r="P84" t="inlineStr"/>
-      <c r="Q84" t="n">
+      <c r="Q84" t="inlineStr"/>
+      <c r="R84" t="inlineStr"/>
+      <c r="S84" t="n">
+        <v>8</v>
+      </c>
+      <c r="T84" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -4136,12 +4732,19 @@
       <c r="K85" t="n">
         <v>0</v>
       </c>
-      <c r="L85" t="inlineStr"/>
+      <c r="L85" t="n">
+        <v>0</v>
+      </c>
       <c r="M85" t="inlineStr"/>
       <c r="N85" t="inlineStr"/>
       <c r="O85" t="inlineStr"/>
       <c r="P85" t="inlineStr"/>
-      <c r="Q85" t="n">
+      <c r="Q85" t="inlineStr"/>
+      <c r="R85" t="inlineStr"/>
+      <c r="S85" t="n">
+        <v>2</v>
+      </c>
+      <c r="T85" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -4179,12 +4782,19 @@
       <c r="K86" t="n">
         <v>0</v>
       </c>
-      <c r="L86" t="inlineStr"/>
+      <c r="L86" t="n">
+        <v>0</v>
+      </c>
       <c r="M86" t="inlineStr"/>
       <c r="N86" t="inlineStr"/>
       <c r="O86" t="inlineStr"/>
       <c r="P86" t="inlineStr"/>
-      <c r="Q86" t="n">
+      <c r="Q86" t="inlineStr"/>
+      <c r="R86" t="inlineStr"/>
+      <c r="S86" t="n">
+        <v>3</v>
+      </c>
+      <c r="T86" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -4222,12 +4832,19 @@
       <c r="K87" t="n">
         <v>0</v>
       </c>
-      <c r="L87" t="inlineStr"/>
+      <c r="L87" t="n">
+        <v>0</v>
+      </c>
       <c r="M87" t="inlineStr"/>
       <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr"/>
       <c r="P87" t="inlineStr"/>
-      <c r="Q87" t="n">
+      <c r="Q87" t="inlineStr"/>
+      <c r="R87" t="inlineStr"/>
+      <c r="S87" t="n">
+        <v>5</v>
+      </c>
+      <c r="T87" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -4265,12 +4882,19 @@
       <c r="K88" t="n">
         <v>0</v>
       </c>
-      <c r="L88" t="inlineStr"/>
+      <c r="L88" t="n">
+        <v>0</v>
+      </c>
       <c r="M88" t="inlineStr"/>
       <c r="N88" t="inlineStr"/>
       <c r="O88" t="inlineStr"/>
       <c r="P88" t="inlineStr"/>
-      <c r="Q88" t="n">
+      <c r="Q88" t="inlineStr"/>
+      <c r="R88" t="inlineStr"/>
+      <c r="S88" t="n">
+        <v>8</v>
+      </c>
+      <c r="T88" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -4308,12 +4932,19 @@
       <c r="K89" t="n">
         <v>0</v>
       </c>
-      <c r="L89" t="inlineStr"/>
+      <c r="L89" t="n">
+        <v>0</v>
+      </c>
       <c r="M89" t="inlineStr"/>
       <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr"/>
       <c r="P89" t="inlineStr"/>
-      <c r="Q89" t="n">
+      <c r="Q89" t="inlineStr"/>
+      <c r="R89" t="inlineStr"/>
+      <c r="S89" t="n">
+        <v>1</v>
+      </c>
+      <c r="T89" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -4351,12 +4982,19 @@
       <c r="K90" t="n">
         <v>1</v>
       </c>
-      <c r="L90" t="inlineStr"/>
+      <c r="L90" t="n">
+        <v>0</v>
+      </c>
       <c r="M90" t="inlineStr"/>
       <c r="N90" t="inlineStr"/>
       <c r="O90" t="inlineStr"/>
       <c r="P90" t="inlineStr"/>
-      <c r="Q90" t="n">
+      <c r="Q90" t="inlineStr"/>
+      <c r="R90" t="inlineStr"/>
+      <c r="S90" t="n">
+        <v>5</v>
+      </c>
+      <c r="T90" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -4394,12 +5032,19 @@
       <c r="K91" t="n">
         <v>0</v>
       </c>
-      <c r="L91" t="inlineStr"/>
+      <c r="L91" t="n">
+        <v>0</v>
+      </c>
       <c r="M91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
       <c r="O91" t="inlineStr"/>
       <c r="P91" t="inlineStr"/>
-      <c r="Q91" t="n">
+      <c r="Q91" t="inlineStr"/>
+      <c r="R91" t="inlineStr"/>
+      <c r="S91" t="n">
+        <v>6</v>
+      </c>
+      <c r="T91" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -4437,12 +5082,19 @@
       <c r="K92" t="n">
         <v>0</v>
       </c>
-      <c r="L92" t="inlineStr"/>
+      <c r="L92" t="n">
+        <v>0</v>
+      </c>
       <c r="M92" t="inlineStr"/>
       <c r="N92" t="inlineStr"/>
       <c r="O92" t="inlineStr"/>
       <c r="P92" t="inlineStr"/>
-      <c r="Q92" t="n">
+      <c r="Q92" t="inlineStr"/>
+      <c r="R92" t="inlineStr"/>
+      <c r="S92" t="n">
+        <v>1</v>
+      </c>
+      <c r="T92" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -4480,12 +5132,19 @@
       <c r="K93" t="n">
         <v>0</v>
       </c>
-      <c r="L93" t="inlineStr"/>
+      <c r="L93" t="n">
+        <v>0</v>
+      </c>
       <c r="M93" t="inlineStr"/>
       <c r="N93" t="inlineStr"/>
       <c r="O93" t="inlineStr"/>
       <c r="P93" t="inlineStr"/>
-      <c r="Q93" t="n">
+      <c r="Q93" t="inlineStr"/>
+      <c r="R93" t="inlineStr"/>
+      <c r="S93" t="n">
+        <v>4</v>
+      </c>
+      <c r="T93" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -4523,12 +5182,19 @@
       <c r="K94" t="n">
         <v>0</v>
       </c>
-      <c r="L94" t="inlineStr"/>
+      <c r="L94" t="n">
+        <v>0</v>
+      </c>
       <c r="M94" t="inlineStr"/>
       <c r="N94" t="inlineStr"/>
       <c r="O94" t="inlineStr"/>
       <c r="P94" t="inlineStr"/>
-      <c r="Q94" t="n">
+      <c r="Q94" t="inlineStr"/>
+      <c r="R94" t="inlineStr"/>
+      <c r="S94" t="n">
+        <v>3</v>
+      </c>
+      <c r="T94" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -4566,12 +5232,19 @@
       <c r="K95" t="n">
         <v>0</v>
       </c>
-      <c r="L95" t="inlineStr"/>
+      <c r="L95" t="n">
+        <v>0</v>
+      </c>
       <c r="M95" t="inlineStr"/>
       <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr"/>
       <c r="P95" t="inlineStr"/>
-      <c r="Q95" t="n">
+      <c r="Q95" t="inlineStr"/>
+      <c r="R95" t="inlineStr"/>
+      <c r="S95" t="n">
+        <v>0</v>
+      </c>
+      <c r="T95" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -4609,12 +5282,19 @@
       <c r="K96" t="n">
         <v>1</v>
       </c>
-      <c r="L96" t="inlineStr"/>
+      <c r="L96" t="n">
+        <v>0</v>
+      </c>
       <c r="M96" t="inlineStr"/>
       <c r="N96" t="inlineStr"/>
       <c r="O96" t="inlineStr"/>
       <c r="P96" t="inlineStr"/>
-      <c r="Q96" t="n">
+      <c r="Q96" t="inlineStr"/>
+      <c r="R96" t="inlineStr"/>
+      <c r="S96" t="n">
+        <v>2</v>
+      </c>
+      <c r="T96" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -4652,12 +5332,19 @@
       <c r="K97" t="n">
         <v>0</v>
       </c>
-      <c r="L97" t="inlineStr"/>
+      <c r="L97" t="n">
+        <v>0</v>
+      </c>
       <c r="M97" t="inlineStr"/>
       <c r="N97" t="inlineStr"/>
       <c r="O97" t="inlineStr"/>
       <c r="P97" t="inlineStr"/>
-      <c r="Q97" t="n">
+      <c r="Q97" t="inlineStr"/>
+      <c r="R97" t="inlineStr"/>
+      <c r="S97" t="n">
+        <v>4</v>
+      </c>
+      <c r="T97" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -4695,12 +5382,19 @@
       <c r="K98" t="n">
         <v>1</v>
       </c>
-      <c r="L98" t="inlineStr"/>
+      <c r="L98" t="n">
+        <v>0</v>
+      </c>
       <c r="M98" t="inlineStr"/>
       <c r="N98" t="inlineStr"/>
       <c r="O98" t="inlineStr"/>
       <c r="P98" t="inlineStr"/>
-      <c r="Q98" t="n">
+      <c r="Q98" t="inlineStr"/>
+      <c r="R98" t="inlineStr"/>
+      <c r="S98" t="n">
+        <v>0</v>
+      </c>
+      <c r="T98" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -4738,12 +5432,19 @@
       <c r="K99" t="n">
         <v>0</v>
       </c>
-      <c r="L99" t="inlineStr"/>
+      <c r="L99" t="n">
+        <v>0</v>
+      </c>
       <c r="M99" t="inlineStr"/>
       <c r="N99" t="inlineStr"/>
       <c r="O99" t="inlineStr"/>
       <c r="P99" t="inlineStr"/>
-      <c r="Q99" t="n">
+      <c r="Q99" t="inlineStr"/>
+      <c r="R99" t="inlineStr"/>
+      <c r="S99" t="n">
+        <v>1</v>
+      </c>
+      <c r="T99" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -4781,12 +5482,19 @@
       <c r="K100" t="n">
         <v>0</v>
       </c>
-      <c r="L100" t="inlineStr"/>
+      <c r="L100" t="n">
+        <v>0</v>
+      </c>
       <c r="M100" t="inlineStr"/>
       <c r="N100" t="inlineStr"/>
       <c r="O100" t="inlineStr"/>
       <c r="P100" t="inlineStr"/>
-      <c r="Q100" t="n">
+      <c r="Q100" t="inlineStr"/>
+      <c r="R100" t="inlineStr"/>
+      <c r="S100" t="n">
+        <v>2</v>
+      </c>
+      <c r="T100" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -4824,12 +5532,19 @@
       <c r="K101" t="n">
         <v>0</v>
       </c>
-      <c r="L101" t="inlineStr"/>
+      <c r="L101" t="n">
+        <v>0</v>
+      </c>
       <c r="M101" t="inlineStr"/>
       <c r="N101" t="inlineStr"/>
       <c r="O101" t="inlineStr"/>
       <c r="P101" t="inlineStr"/>
-      <c r="Q101" t="n">
+      <c r="Q101" t="inlineStr"/>
+      <c r="R101" t="inlineStr"/>
+      <c r="S101" t="n">
+        <v>0</v>
+      </c>
+      <c r="T101" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -4867,12 +5582,19 @@
       <c r="K102" t="n">
         <v>0</v>
       </c>
-      <c r="L102" t="inlineStr"/>
+      <c r="L102" t="n">
+        <v>0</v>
+      </c>
       <c r="M102" t="inlineStr"/>
       <c r="N102" t="inlineStr"/>
       <c r="O102" t="inlineStr"/>
       <c r="P102" t="inlineStr"/>
-      <c r="Q102" t="n">
+      <c r="Q102" t="inlineStr"/>
+      <c r="R102" t="inlineStr"/>
+      <c r="S102" t="n">
+        <v>2</v>
+      </c>
+      <c r="T102" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -4910,12 +5632,19 @@
       <c r="K103" t="n">
         <v>0</v>
       </c>
-      <c r="L103" t="inlineStr"/>
+      <c r="L103" t="n">
+        <v>0</v>
+      </c>
       <c r="M103" t="inlineStr"/>
       <c r="N103" t="inlineStr"/>
       <c r="O103" t="inlineStr"/>
       <c r="P103" t="inlineStr"/>
-      <c r="Q103" t="n">
+      <c r="Q103" t="inlineStr"/>
+      <c r="R103" t="inlineStr"/>
+      <c r="S103" t="n">
+        <v>1</v>
+      </c>
+      <c r="T103" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -4953,12 +5682,19 @@
       <c r="K104" t="n">
         <v>0</v>
       </c>
-      <c r="L104" t="inlineStr"/>
+      <c r="L104" t="n">
+        <v>0</v>
+      </c>
       <c r="M104" t="inlineStr"/>
       <c r="N104" t="inlineStr"/>
       <c r="O104" t="inlineStr"/>
       <c r="P104" t="inlineStr"/>
-      <c r="Q104" t="n">
+      <c r="Q104" t="inlineStr"/>
+      <c r="R104" t="inlineStr"/>
+      <c r="S104" t="n">
+        <v>1</v>
+      </c>
+      <c r="T104" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -4996,12 +5732,19 @@
       <c r="K105" t="n">
         <v>0</v>
       </c>
-      <c r="L105" t="inlineStr"/>
+      <c r="L105" t="n">
+        <v>0</v>
+      </c>
       <c r="M105" t="inlineStr"/>
       <c r="N105" t="inlineStr"/>
       <c r="O105" t="inlineStr"/>
       <c r="P105" t="inlineStr"/>
-      <c r="Q105" t="n">
+      <c r="Q105" t="inlineStr"/>
+      <c r="R105" t="inlineStr"/>
+      <c r="S105" t="n">
+        <v>2</v>
+      </c>
+      <c r="T105" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -5039,12 +5782,19 @@
       <c r="K106" t="n">
         <v>0</v>
       </c>
-      <c r="L106" t="inlineStr"/>
+      <c r="L106" t="n">
+        <v>1</v>
+      </c>
       <c r="M106" t="inlineStr"/>
       <c r="N106" t="inlineStr"/>
       <c r="O106" t="inlineStr"/>
       <c r="P106" t="inlineStr"/>
-      <c r="Q106" t="n">
+      <c r="Q106" t="inlineStr"/>
+      <c r="R106" t="inlineStr"/>
+      <c r="S106" t="n">
+        <v>9</v>
+      </c>
+      <c r="T106" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -5082,12 +5832,19 @@
       <c r="K107" t="n">
         <v>0</v>
       </c>
-      <c r="L107" t="inlineStr"/>
+      <c r="L107" t="n">
+        <v>0</v>
+      </c>
       <c r="M107" t="inlineStr"/>
       <c r="N107" t="inlineStr"/>
       <c r="O107" t="inlineStr"/>
       <c r="P107" t="inlineStr"/>
-      <c r="Q107" t="n">
+      <c r="Q107" t="inlineStr"/>
+      <c r="R107" t="inlineStr"/>
+      <c r="S107" t="n">
+        <v>3</v>
+      </c>
+      <c r="T107" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -5125,12 +5882,19 @@
       <c r="K108" t="n">
         <v>0</v>
       </c>
-      <c r="L108" t="inlineStr"/>
+      <c r="L108" t="n">
+        <v>0</v>
+      </c>
       <c r="M108" t="inlineStr"/>
       <c r="N108" t="inlineStr"/>
       <c r="O108" t="inlineStr"/>
       <c r="P108" t="inlineStr"/>
-      <c r="Q108" t="n">
+      <c r="Q108" t="inlineStr"/>
+      <c r="R108" t="inlineStr"/>
+      <c r="S108" t="n">
+        <v>1</v>
+      </c>
+      <c r="T108" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -5168,12 +5932,19 @@
       <c r="K109" t="n">
         <v>0</v>
       </c>
-      <c r="L109" t="inlineStr"/>
+      <c r="L109" t="n">
+        <v>0</v>
+      </c>
       <c r="M109" t="inlineStr"/>
       <c r="N109" t="inlineStr"/>
       <c r="O109" t="inlineStr"/>
       <c r="P109" t="inlineStr"/>
-      <c r="Q109" t="n">
+      <c r="Q109" t="inlineStr"/>
+      <c r="R109" t="inlineStr"/>
+      <c r="S109" t="n">
+        <v>4</v>
+      </c>
+      <c r="T109" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -5211,12 +5982,19 @@
       <c r="K110" t="n">
         <v>5</v>
       </c>
-      <c r="L110" t="inlineStr"/>
+      <c r="L110" t="n">
+        <v>0</v>
+      </c>
       <c r="M110" t="inlineStr"/>
       <c r="N110" t="inlineStr"/>
       <c r="O110" t="inlineStr"/>
       <c r="P110" t="inlineStr"/>
-      <c r="Q110" t="n">
+      <c r="Q110" t="inlineStr"/>
+      <c r="R110" t="inlineStr"/>
+      <c r="S110" t="n">
+        <v>11</v>
+      </c>
+      <c r="T110" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -5254,12 +6032,19 @@
       <c r="K111" t="n">
         <v>0</v>
       </c>
-      <c r="L111" t="inlineStr"/>
+      <c r="L111" t="n">
+        <v>0</v>
+      </c>
       <c r="M111" t="inlineStr"/>
       <c r="N111" t="inlineStr"/>
       <c r="O111" t="inlineStr"/>
       <c r="P111" t="inlineStr"/>
-      <c r="Q111" t="n">
+      <c r="Q111" t="inlineStr"/>
+      <c r="R111" t="inlineStr"/>
+      <c r="S111" t="n">
+        <v>1</v>
+      </c>
+      <c r="T111" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -5297,12 +6082,19 @@
       <c r="K112" t="n">
         <v>1</v>
       </c>
-      <c r="L112" t="inlineStr"/>
+      <c r="L112" t="n">
+        <v>0</v>
+      </c>
       <c r="M112" t="inlineStr"/>
       <c r="N112" t="inlineStr"/>
       <c r="O112" t="inlineStr"/>
       <c r="P112" t="inlineStr"/>
-      <c r="Q112" t="n">
+      <c r="Q112" t="inlineStr"/>
+      <c r="R112" t="inlineStr"/>
+      <c r="S112" t="n">
+        <v>2</v>
+      </c>
+      <c r="T112" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -5340,12 +6132,19 @@
       <c r="K113" t="n">
         <v>4</v>
       </c>
-      <c r="L113" t="inlineStr"/>
+      <c r="L113" t="n">
+        <v>0</v>
+      </c>
       <c r="M113" t="inlineStr"/>
       <c r="N113" t="inlineStr"/>
       <c r="O113" t="inlineStr"/>
       <c r="P113" t="inlineStr"/>
-      <c r="Q113" t="n">
+      <c r="Q113" t="inlineStr"/>
+      <c r="R113" t="inlineStr"/>
+      <c r="S113" t="n">
+        <v>10</v>
+      </c>
+      <c r="T113" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -5383,12 +6182,19 @@
       <c r="K114" t="n">
         <v>0</v>
       </c>
-      <c r="L114" t="inlineStr"/>
+      <c r="L114" t="n">
+        <v>0</v>
+      </c>
       <c r="M114" t="inlineStr"/>
       <c r="N114" t="inlineStr"/>
       <c r="O114" t="inlineStr"/>
       <c r="P114" t="inlineStr"/>
-      <c r="Q114" t="n">
+      <c r="Q114" t="inlineStr"/>
+      <c r="R114" t="inlineStr"/>
+      <c r="S114" t="n">
+        <v>4</v>
+      </c>
+      <c r="T114" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -5426,12 +6232,19 @@
       <c r="K115" t="n">
         <v>0</v>
       </c>
-      <c r="L115" t="inlineStr"/>
+      <c r="L115" t="n">
+        <v>0</v>
+      </c>
       <c r="M115" t="inlineStr"/>
       <c r="N115" t="inlineStr"/>
       <c r="O115" t="inlineStr"/>
       <c r="P115" t="inlineStr"/>
-      <c r="Q115" t="n">
+      <c r="Q115" t="inlineStr"/>
+      <c r="R115" t="inlineStr"/>
+      <c r="S115" t="n">
+        <v>3</v>
+      </c>
+      <c r="T115" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -5469,12 +6282,19 @@
       <c r="K116" t="n">
         <v>1</v>
       </c>
-      <c r="L116" t="inlineStr"/>
+      <c r="L116" t="n">
+        <v>0</v>
+      </c>
       <c r="M116" t="inlineStr"/>
       <c r="N116" t="inlineStr"/>
       <c r="O116" t="inlineStr"/>
       <c r="P116" t="inlineStr"/>
-      <c r="Q116" t="n">
+      <c r="Q116" t="inlineStr"/>
+      <c r="R116" t="inlineStr"/>
+      <c r="S116" t="n">
+        <v>0</v>
+      </c>
+      <c r="T116" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -5512,12 +6332,19 @@
       <c r="K117" t="n">
         <v>0</v>
       </c>
-      <c r="L117" t="inlineStr"/>
+      <c r="L117" t="n">
+        <v>0</v>
+      </c>
       <c r="M117" t="inlineStr"/>
       <c r="N117" t="inlineStr"/>
       <c r="O117" t="inlineStr"/>
       <c r="P117" t="inlineStr"/>
-      <c r="Q117" t="n">
+      <c r="Q117" t="inlineStr"/>
+      <c r="R117" t="inlineStr"/>
+      <c r="S117" t="n">
+        <v>0</v>
+      </c>
+      <c r="T117" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -5555,12 +6382,19 @@
       <c r="K118" t="n">
         <v>1</v>
       </c>
-      <c r="L118" t="inlineStr"/>
+      <c r="L118" t="n">
+        <v>0</v>
+      </c>
       <c r="M118" t="inlineStr"/>
       <c r="N118" t="inlineStr"/>
       <c r="O118" t="inlineStr"/>
       <c r="P118" t="inlineStr"/>
-      <c r="Q118" t="n">
+      <c r="Q118" t="inlineStr"/>
+      <c r="R118" t="inlineStr"/>
+      <c r="S118" t="n">
+        <v>9</v>
+      </c>
+      <c r="T118" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -5598,12 +6432,19 @@
       <c r="K119" t="n">
         <v>9</v>
       </c>
-      <c r="L119" t="inlineStr"/>
+      <c r="L119" t="n">
+        <v>0</v>
+      </c>
       <c r="M119" t="inlineStr"/>
       <c r="N119" t="inlineStr"/>
       <c r="O119" t="inlineStr"/>
       <c r="P119" t="inlineStr"/>
-      <c r="Q119" t="n">
+      <c r="Q119" t="inlineStr"/>
+      <c r="R119" t="inlineStr"/>
+      <c r="S119" t="n">
+        <v>18</v>
+      </c>
+      <c r="T119" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -5641,12 +6482,19 @@
       <c r="K120" t="n">
         <v>2</v>
       </c>
-      <c r="L120" t="inlineStr"/>
+      <c r="L120" t="n">
+        <v>0</v>
+      </c>
       <c r="M120" t="inlineStr"/>
       <c r="N120" t="inlineStr"/>
       <c r="O120" t="inlineStr"/>
       <c r="P120" t="inlineStr"/>
-      <c r="Q120" t="n">
+      <c r="Q120" t="inlineStr"/>
+      <c r="R120" t="inlineStr"/>
+      <c r="S120" t="n">
+        <v>2</v>
+      </c>
+      <c r="T120" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -5684,12 +6532,19 @@
       <c r="K121" t="n">
         <v>0</v>
       </c>
-      <c r="L121" t="inlineStr"/>
+      <c r="L121" t="n">
+        <v>0</v>
+      </c>
       <c r="M121" t="inlineStr"/>
       <c r="N121" t="inlineStr"/>
       <c r="O121" t="inlineStr"/>
       <c r="P121" t="inlineStr"/>
-      <c r="Q121" t="n">
+      <c r="Q121" t="inlineStr"/>
+      <c r="R121" t="inlineStr"/>
+      <c r="S121" t="n">
+        <v>1</v>
+      </c>
+      <c r="T121" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -5727,12 +6582,19 @@
       <c r="K122" t="n">
         <v>0</v>
       </c>
-      <c r="L122" t="inlineStr"/>
+      <c r="L122" t="n">
+        <v>0</v>
+      </c>
       <c r="M122" t="inlineStr"/>
       <c r="N122" t="inlineStr"/>
       <c r="O122" t="inlineStr"/>
       <c r="P122" t="inlineStr"/>
-      <c r="Q122" t="n">
+      <c r="Q122" t="inlineStr"/>
+      <c r="R122" t="inlineStr"/>
+      <c r="S122" t="n">
+        <v>5</v>
+      </c>
+      <c r="T122" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -5770,12 +6632,19 @@
       <c r="K123" t="n">
         <v>0</v>
       </c>
-      <c r="L123" t="inlineStr"/>
+      <c r="L123" t="n">
+        <v>0</v>
+      </c>
       <c r="M123" t="inlineStr"/>
       <c r="N123" t="inlineStr"/>
       <c r="O123" t="inlineStr"/>
       <c r="P123" t="inlineStr"/>
-      <c r="Q123" t="n">
+      <c r="Q123" t="inlineStr"/>
+      <c r="R123" t="inlineStr"/>
+      <c r="S123" t="n">
+        <v>4</v>
+      </c>
+      <c r="T123" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -5813,12 +6682,19 @@
       <c r="K124" t="n">
         <v>0</v>
       </c>
-      <c r="L124" t="inlineStr"/>
+      <c r="L124" t="n">
+        <v>0</v>
+      </c>
       <c r="M124" t="inlineStr"/>
       <c r="N124" t="inlineStr"/>
       <c r="O124" t="inlineStr"/>
       <c r="P124" t="inlineStr"/>
-      <c r="Q124" t="n">
+      <c r="Q124" t="inlineStr"/>
+      <c r="R124" t="inlineStr"/>
+      <c r="S124" t="n">
+        <v>2</v>
+      </c>
+      <c r="T124" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -5856,12 +6732,19 @@
       <c r="K125" t="n">
         <v>1</v>
       </c>
-      <c r="L125" t="inlineStr"/>
+      <c r="L125" t="n">
+        <v>0</v>
+      </c>
       <c r="M125" t="inlineStr"/>
       <c r="N125" t="inlineStr"/>
       <c r="O125" t="inlineStr"/>
       <c r="P125" t="inlineStr"/>
-      <c r="Q125" t="n">
+      <c r="Q125" t="inlineStr"/>
+      <c r="R125" t="inlineStr"/>
+      <c r="S125" t="n">
+        <v>1</v>
+      </c>
+      <c r="T125" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -5899,12 +6782,19 @@
       <c r="K126" t="n">
         <v>5</v>
       </c>
-      <c r="L126" t="inlineStr"/>
+      <c r="L126" t="n">
+        <v>0</v>
+      </c>
       <c r="M126" t="inlineStr"/>
       <c r="N126" t="inlineStr"/>
       <c r="O126" t="inlineStr"/>
       <c r="P126" t="inlineStr"/>
-      <c r="Q126" t="n">
+      <c r="Q126" t="inlineStr"/>
+      <c r="R126" t="inlineStr"/>
+      <c r="S126" t="n">
+        <v>18</v>
+      </c>
+      <c r="T126" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -5942,12 +6832,19 @@
       <c r="K127" t="n">
         <v>1</v>
       </c>
-      <c r="L127" t="inlineStr"/>
+      <c r="L127" t="n">
+        <v>0</v>
+      </c>
       <c r="M127" t="inlineStr"/>
       <c r="N127" t="inlineStr"/>
       <c r="O127" t="inlineStr"/>
       <c r="P127" t="inlineStr"/>
-      <c r="Q127" t="n">
+      <c r="Q127" t="inlineStr"/>
+      <c r="R127" t="inlineStr"/>
+      <c r="S127" t="n">
+        <v>9</v>
+      </c>
+      <c r="T127" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -5985,12 +6882,19 @@
       <c r="K128" t="n">
         <v>0</v>
       </c>
-      <c r="L128" t="inlineStr"/>
+      <c r="L128" t="n">
+        <v>0</v>
+      </c>
       <c r="M128" t="inlineStr"/>
       <c r="N128" t="inlineStr"/>
       <c r="O128" t="inlineStr"/>
       <c r="P128" t="inlineStr"/>
-      <c r="Q128" t="n">
+      <c r="Q128" t="inlineStr"/>
+      <c r="R128" t="inlineStr"/>
+      <c r="S128" t="n">
+        <v>3</v>
+      </c>
+      <c r="T128" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -6020,9 +6924,7 @@
       <c r="K129" t="n">
         <v>0</v>
       </c>
-      <c r="L129" t="n">
-        <v>0</v>
-      </c>
+      <c r="L129" t="inlineStr"/>
       <c r="M129" t="n">
         <v>0</v>
       </c>
@@ -6036,6 +6938,15 @@
         <v>0</v>
       </c>
       <c r="Q129" t="n">
+        <v>0</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0</v>
+      </c>
+      <c r="S129" t="n">
+        <v>3</v>
+      </c>
+      <c r="T129" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -6065,9 +6976,7 @@
       <c r="K130" t="n">
         <v>0</v>
       </c>
-      <c r="L130" t="n">
-        <v>0</v>
-      </c>
+      <c r="L130" t="inlineStr"/>
       <c r="M130" t="n">
         <v>0</v>
       </c>
@@ -6078,9 +6987,18 @@
         <v>0</v>
       </c>
       <c r="P130" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q130" t="n">
+        <v>2</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0</v>
+      </c>
+      <c r="S130" t="n">
+        <v>3</v>
+      </c>
+      <c r="T130" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -6118,12 +7036,19 @@
       <c r="K131" t="n">
         <v>0</v>
       </c>
-      <c r="L131" t="inlineStr"/>
+      <c r="L131" t="n">
+        <v>0</v>
+      </c>
       <c r="M131" t="inlineStr"/>
       <c r="N131" t="inlineStr"/>
       <c r="O131" t="inlineStr"/>
       <c r="P131" t="inlineStr"/>
-      <c r="Q131" t="n">
+      <c r="Q131" t="inlineStr"/>
+      <c r="R131" t="inlineStr"/>
+      <c r="S131" t="n">
+        <v>0</v>
+      </c>
+      <c r="T131" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -6161,12 +7086,19 @@
       <c r="K132" t="n">
         <v>0</v>
       </c>
-      <c r="L132" t="inlineStr"/>
+      <c r="L132" t="n">
+        <v>0</v>
+      </c>
       <c r="M132" t="inlineStr"/>
       <c r="N132" t="inlineStr"/>
       <c r="O132" t="inlineStr"/>
       <c r="P132" t="inlineStr"/>
-      <c r="Q132" t="n">
+      <c r="Q132" t="inlineStr"/>
+      <c r="R132" t="inlineStr"/>
+      <c r="S132" t="n">
+        <v>2</v>
+      </c>
+      <c r="T132" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -6204,12 +7136,19 @@
       <c r="K133" t="n">
         <v>0</v>
       </c>
-      <c r="L133" t="inlineStr"/>
+      <c r="L133" t="n">
+        <v>0</v>
+      </c>
       <c r="M133" t="inlineStr"/>
       <c r="N133" t="inlineStr"/>
       <c r="O133" t="inlineStr"/>
       <c r="P133" t="inlineStr"/>
-      <c r="Q133" t="n">
+      <c r="Q133" t="inlineStr"/>
+      <c r="R133" t="inlineStr"/>
+      <c r="S133" t="n">
+        <v>1</v>
+      </c>
+      <c r="T133" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -6247,12 +7186,19 @@
       <c r="K134" t="n">
         <v>0</v>
       </c>
-      <c r="L134" t="inlineStr"/>
+      <c r="L134" t="n">
+        <v>0</v>
+      </c>
       <c r="M134" t="inlineStr"/>
       <c r="N134" t="inlineStr"/>
       <c r="O134" t="inlineStr"/>
       <c r="P134" t="inlineStr"/>
-      <c r="Q134" t="n">
+      <c r="Q134" t="inlineStr"/>
+      <c r="R134" t="inlineStr"/>
+      <c r="S134" t="n">
+        <v>2</v>
+      </c>
+      <c r="T134" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -6290,12 +7236,19 @@
       <c r="K135" t="n">
         <v>0</v>
       </c>
-      <c r="L135" t="inlineStr"/>
+      <c r="L135" t="n">
+        <v>0</v>
+      </c>
       <c r="M135" t="inlineStr"/>
       <c r="N135" t="inlineStr"/>
       <c r="O135" t="inlineStr"/>
       <c r="P135" t="inlineStr"/>
-      <c r="Q135" t="n">
+      <c r="Q135" t="inlineStr"/>
+      <c r="R135" t="inlineStr"/>
+      <c r="S135" t="n">
+        <v>10</v>
+      </c>
+      <c r="T135" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -6333,12 +7286,19 @@
       <c r="K136" t="n">
         <v>0</v>
       </c>
-      <c r="L136" t="inlineStr"/>
+      <c r="L136" t="n">
+        <v>0</v>
+      </c>
       <c r="M136" t="inlineStr"/>
       <c r="N136" t="inlineStr"/>
       <c r="O136" t="inlineStr"/>
       <c r="P136" t="inlineStr"/>
-      <c r="Q136" t="n">
+      <c r="Q136" t="inlineStr"/>
+      <c r="R136" t="inlineStr"/>
+      <c r="S136" t="n">
+        <v>11</v>
+      </c>
+      <c r="T136" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -6368,9 +7328,7 @@
       <c r="K137" t="n">
         <v>0</v>
       </c>
-      <c r="L137" t="n">
-        <v>0</v>
-      </c>
+      <c r="L137" t="inlineStr"/>
       <c r="M137" t="n">
         <v>0</v>
       </c>
@@ -6381,9 +7339,18 @@
         <v>0</v>
       </c>
       <c r="P137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q137" t="n">
+        <v>1</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0</v>
+      </c>
+      <c r="S137" t="n">
+        <v>1</v>
+      </c>
+      <c r="T137" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -6413,9 +7380,7 @@
       <c r="K138" t="n">
         <v>0</v>
       </c>
-      <c r="L138" t="n">
-        <v>0</v>
-      </c>
+      <c r="L138" t="inlineStr"/>
       <c r="M138" t="n">
         <v>0</v>
       </c>
@@ -6429,6 +7394,15 @@
         <v>0</v>
       </c>
       <c r="Q138" t="n">
+        <v>0</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0</v>
+      </c>
+      <c r="S138" t="n">
+        <v>3</v>
+      </c>
+      <c r="T138" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -6466,12 +7440,19 @@
       <c r="K139" t="n">
         <v>0</v>
       </c>
-      <c r="L139" t="inlineStr"/>
+      <c r="L139" t="n">
+        <v>0</v>
+      </c>
       <c r="M139" t="inlineStr"/>
       <c r="N139" t="inlineStr"/>
       <c r="O139" t="inlineStr"/>
       <c r="P139" t="inlineStr"/>
-      <c r="Q139" t="n">
+      <c r="Q139" t="inlineStr"/>
+      <c r="R139" t="inlineStr"/>
+      <c r="S139" t="n">
+        <v>0</v>
+      </c>
+      <c r="T139" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -6509,12 +7490,19 @@
       <c r="K140" t="n">
         <v>0</v>
       </c>
-      <c r="L140" t="inlineStr"/>
+      <c r="L140" t="n">
+        <v>0</v>
+      </c>
       <c r="M140" t="inlineStr"/>
       <c r="N140" t="inlineStr"/>
       <c r="O140" t="inlineStr"/>
       <c r="P140" t="inlineStr"/>
-      <c r="Q140" t="n">
+      <c r="Q140" t="inlineStr"/>
+      <c r="R140" t="inlineStr"/>
+      <c r="S140" t="n">
+        <v>0</v>
+      </c>
+      <c r="T140" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -6552,12 +7540,19 @@
       <c r="K141" t="n">
         <v>0</v>
       </c>
-      <c r="L141" t="inlineStr"/>
+      <c r="L141" t="n">
+        <v>0</v>
+      </c>
       <c r="M141" t="inlineStr"/>
       <c r="N141" t="inlineStr"/>
       <c r="O141" t="inlineStr"/>
       <c r="P141" t="inlineStr"/>
-      <c r="Q141" t="n">
+      <c r="Q141" t="inlineStr"/>
+      <c r="R141" t="inlineStr"/>
+      <c r="S141" t="n">
+        <v>3</v>
+      </c>
+      <c r="T141" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -6595,12 +7590,19 @@
       <c r="K142" t="n">
         <v>0</v>
       </c>
-      <c r="L142" t="inlineStr"/>
+      <c r="L142" t="n">
+        <v>0</v>
+      </c>
       <c r="M142" t="inlineStr"/>
       <c r="N142" t="inlineStr"/>
       <c r="O142" t="inlineStr"/>
       <c r="P142" t="inlineStr"/>
-      <c r="Q142" t="n">
+      <c r="Q142" t="inlineStr"/>
+      <c r="R142" t="inlineStr"/>
+      <c r="S142" t="n">
+        <v>3</v>
+      </c>
+      <c r="T142" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -6638,12 +7640,19 @@
       <c r="K143" t="n">
         <v>1</v>
       </c>
-      <c r="L143" t="inlineStr"/>
+      <c r="L143" t="n">
+        <v>0</v>
+      </c>
       <c r="M143" t="inlineStr"/>
       <c r="N143" t="inlineStr"/>
       <c r="O143" t="inlineStr"/>
       <c r="P143" t="inlineStr"/>
-      <c r="Q143" t="n">
+      <c r="Q143" t="inlineStr"/>
+      <c r="R143" t="inlineStr"/>
+      <c r="S143" t="n">
+        <v>1</v>
+      </c>
+      <c r="T143" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -6673,9 +7682,7 @@
       <c r="K144" t="n">
         <v>0</v>
       </c>
-      <c r="L144" t="n">
-        <v>0</v>
-      </c>
+      <c r="L144" t="inlineStr"/>
       <c r="M144" t="n">
         <v>0</v>
       </c>
@@ -6686,9 +7693,18 @@
         <v>0</v>
       </c>
       <c r="P144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q144" t="n">
+        <v>1</v>
+      </c>
+      <c r="R144" t="n">
+        <v>0</v>
+      </c>
+      <c r="S144" t="n">
+        <v>2</v>
+      </c>
+      <c r="T144" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -6718,9 +7734,7 @@
       <c r="K145" t="n">
         <v>1</v>
       </c>
-      <c r="L145" t="n">
-        <v>0</v>
-      </c>
+      <c r="L145" t="inlineStr"/>
       <c r="M145" t="n">
         <v>0</v>
       </c>
@@ -6731,9 +7745,18 @@
         <v>0</v>
       </c>
       <c r="P145" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q145" t="n">
         <v>6</v>
       </c>
-      <c r="Q145" t="n">
+      <c r="R145" t="n">
+        <v>0</v>
+      </c>
+      <c r="S145" t="n">
+        <v>4</v>
+      </c>
+      <c r="T145" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -6763,9 +7786,7 @@
       <c r="K146" t="n">
         <v>0</v>
       </c>
-      <c r="L146" t="n">
-        <v>0</v>
-      </c>
+      <c r="L146" t="inlineStr"/>
       <c r="M146" t="n">
         <v>0</v>
       </c>
@@ -6776,9 +7797,18 @@
         <v>0</v>
       </c>
       <c r="P146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q146" t="n">
+        <v>1</v>
+      </c>
+      <c r="R146" t="n">
+        <v>0</v>
+      </c>
+      <c r="S146" t="n">
+        <v>1</v>
+      </c>
+      <c r="T146" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -6816,12 +7846,19 @@
       <c r="K147" t="n">
         <v>0</v>
       </c>
-      <c r="L147" t="inlineStr"/>
+      <c r="L147" t="n">
+        <v>0</v>
+      </c>
       <c r="M147" t="inlineStr"/>
       <c r="N147" t="inlineStr"/>
       <c r="O147" t="inlineStr"/>
       <c r="P147" t="inlineStr"/>
-      <c r="Q147" t="n">
+      <c r="Q147" t="inlineStr"/>
+      <c r="R147" t="inlineStr"/>
+      <c r="S147" t="n">
+        <v>1</v>
+      </c>
+      <c r="T147" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -6859,12 +7896,19 @@
       <c r="K148" t="n">
         <v>0</v>
       </c>
-      <c r="L148" t="inlineStr"/>
+      <c r="L148" t="n">
+        <v>0</v>
+      </c>
       <c r="M148" t="inlineStr"/>
       <c r="N148" t="inlineStr"/>
       <c r="O148" t="inlineStr"/>
       <c r="P148" t="inlineStr"/>
-      <c r="Q148" t="n">
+      <c r="Q148" t="inlineStr"/>
+      <c r="R148" t="inlineStr"/>
+      <c r="S148" t="n">
+        <v>1</v>
+      </c>
+      <c r="T148" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -6902,12 +7946,19 @@
       <c r="K149" t="n">
         <v>0</v>
       </c>
-      <c r="L149" t="inlineStr"/>
+      <c r="L149" t="n">
+        <v>0</v>
+      </c>
       <c r="M149" t="inlineStr"/>
       <c r="N149" t="inlineStr"/>
       <c r="O149" t="inlineStr"/>
       <c r="P149" t="inlineStr"/>
-      <c r="Q149" t="n">
+      <c r="Q149" t="inlineStr"/>
+      <c r="R149" t="inlineStr"/>
+      <c r="S149" t="n">
+        <v>6</v>
+      </c>
+      <c r="T149" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -6937,9 +7988,7 @@
       <c r="K150" t="n">
         <v>0</v>
       </c>
-      <c r="L150" t="n">
-        <v>0</v>
-      </c>
+      <c r="L150" t="inlineStr"/>
       <c r="M150" t="n">
         <v>0</v>
       </c>
@@ -6950,9 +7999,18 @@
         <v>0</v>
       </c>
       <c r="P150" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q150" t="n">
+        <v>2</v>
+      </c>
+      <c r="R150" t="n">
+        <v>0</v>
+      </c>
+      <c r="S150" t="n">
+        <v>4</v>
+      </c>
+      <c r="T150" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -6990,12 +8048,19 @@
       <c r="K151" t="n">
         <v>0</v>
       </c>
-      <c r="L151" t="inlineStr"/>
+      <c r="L151" t="n">
+        <v>0</v>
+      </c>
       <c r="M151" t="inlineStr"/>
       <c r="N151" t="inlineStr"/>
       <c r="O151" t="inlineStr"/>
       <c r="P151" t="inlineStr"/>
-      <c r="Q151" t="n">
+      <c r="Q151" t="inlineStr"/>
+      <c r="R151" t="inlineStr"/>
+      <c r="S151" t="n">
+        <v>4</v>
+      </c>
+      <c r="T151" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -7033,12 +8098,19 @@
       <c r="K152" t="n">
         <v>0</v>
       </c>
-      <c r="L152" t="inlineStr"/>
+      <c r="L152" t="n">
+        <v>0</v>
+      </c>
       <c r="M152" t="inlineStr"/>
       <c r="N152" t="inlineStr"/>
       <c r="O152" t="inlineStr"/>
       <c r="P152" t="inlineStr"/>
-      <c r="Q152" t="n">
+      <c r="Q152" t="inlineStr"/>
+      <c r="R152" t="inlineStr"/>
+      <c r="S152" t="n">
+        <v>3</v>
+      </c>
+      <c r="T152" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -7076,12 +8148,19 @@
       <c r="K153" t="n">
         <v>0</v>
       </c>
-      <c r="L153" t="inlineStr"/>
+      <c r="L153" t="n">
+        <v>0</v>
+      </c>
       <c r="M153" t="inlineStr"/>
       <c r="N153" t="inlineStr"/>
       <c r="O153" t="inlineStr"/>
       <c r="P153" t="inlineStr"/>
-      <c r="Q153" t="n">
+      <c r="Q153" t="inlineStr"/>
+      <c r="R153" t="inlineStr"/>
+      <c r="S153" t="n">
+        <v>1</v>
+      </c>
+      <c r="T153" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -7119,12 +8198,19 @@
       <c r="K154" t="n">
         <v>0</v>
       </c>
-      <c r="L154" t="inlineStr"/>
+      <c r="L154" t="n">
+        <v>0</v>
+      </c>
       <c r="M154" t="inlineStr"/>
       <c r="N154" t="inlineStr"/>
       <c r="O154" t="inlineStr"/>
       <c r="P154" t="inlineStr"/>
-      <c r="Q154" t="n">
+      <c r="Q154" t="inlineStr"/>
+      <c r="R154" t="inlineStr"/>
+      <c r="S154" t="n">
+        <v>2</v>
+      </c>
+      <c r="T154" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -7162,12 +8248,19 @@
       <c r="K155" t="n">
         <v>0</v>
       </c>
-      <c r="L155" t="inlineStr"/>
+      <c r="L155" t="n">
+        <v>0</v>
+      </c>
       <c r="M155" t="inlineStr"/>
       <c r="N155" t="inlineStr"/>
       <c r="O155" t="inlineStr"/>
       <c r="P155" t="inlineStr"/>
-      <c r="Q155" t="n">
+      <c r="Q155" t="inlineStr"/>
+      <c r="R155" t="inlineStr"/>
+      <c r="S155" t="n">
+        <v>1</v>
+      </c>
+      <c r="T155" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -7205,12 +8298,19 @@
       <c r="K156" t="n">
         <v>0</v>
       </c>
-      <c r="L156" t="inlineStr"/>
+      <c r="L156" t="n">
+        <v>1</v>
+      </c>
       <c r="M156" t="inlineStr"/>
       <c r="N156" t="inlineStr"/>
       <c r="O156" t="inlineStr"/>
       <c r="P156" t="inlineStr"/>
-      <c r="Q156" t="n">
+      <c r="Q156" t="inlineStr"/>
+      <c r="R156" t="inlineStr"/>
+      <c r="S156" t="n">
+        <v>0</v>
+      </c>
+      <c r="T156" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -7248,12 +8348,19 @@
       <c r="K157" t="n">
         <v>0</v>
       </c>
-      <c r="L157" t="inlineStr"/>
+      <c r="L157" t="n">
+        <v>0</v>
+      </c>
       <c r="M157" t="inlineStr"/>
       <c r="N157" t="inlineStr"/>
       <c r="O157" t="inlineStr"/>
       <c r="P157" t="inlineStr"/>
-      <c r="Q157" t="n">
+      <c r="Q157" t="inlineStr"/>
+      <c r="R157" t="inlineStr"/>
+      <c r="S157" t="n">
+        <v>1</v>
+      </c>
+      <c r="T157" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -7291,12 +8398,19 @@
       <c r="K158" t="n">
         <v>0</v>
       </c>
-      <c r="L158" t="inlineStr"/>
+      <c r="L158" t="n">
+        <v>0</v>
+      </c>
       <c r="M158" t="inlineStr"/>
       <c r="N158" t="inlineStr"/>
       <c r="O158" t="inlineStr"/>
       <c r="P158" t="inlineStr"/>
-      <c r="Q158" t="n">
+      <c r="Q158" t="inlineStr"/>
+      <c r="R158" t="inlineStr"/>
+      <c r="S158" t="n">
+        <v>5</v>
+      </c>
+      <c r="T158" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -7334,12 +8448,19 @@
       <c r="K159" t="n">
         <v>0</v>
       </c>
-      <c r="L159" t="inlineStr"/>
+      <c r="L159" t="n">
+        <v>0</v>
+      </c>
       <c r="M159" t="inlineStr"/>
       <c r="N159" t="inlineStr"/>
       <c r="O159" t="inlineStr"/>
       <c r="P159" t="inlineStr"/>
-      <c r="Q159" t="n">
+      <c r="Q159" t="inlineStr"/>
+      <c r="R159" t="inlineStr"/>
+      <c r="S159" t="n">
+        <v>5</v>
+      </c>
+      <c r="T159" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -7377,12 +8498,19 @@
       <c r="K160" t="n">
         <v>6</v>
       </c>
-      <c r="L160" t="inlineStr"/>
+      <c r="L160" t="n">
+        <v>0</v>
+      </c>
       <c r="M160" t="inlineStr"/>
       <c r="N160" t="inlineStr"/>
       <c r="O160" t="inlineStr"/>
       <c r="P160" t="inlineStr"/>
-      <c r="Q160" t="n">
+      <c r="Q160" t="inlineStr"/>
+      <c r="R160" t="inlineStr"/>
+      <c r="S160" t="n">
+        <v>1</v>
+      </c>
+      <c r="T160" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -7420,12 +8548,19 @@
       <c r="K161" t="n">
         <v>0</v>
       </c>
-      <c r="L161" t="inlineStr"/>
+      <c r="L161" t="n">
+        <v>0</v>
+      </c>
       <c r="M161" t="inlineStr"/>
       <c r="N161" t="inlineStr"/>
       <c r="O161" t="inlineStr"/>
       <c r="P161" t="inlineStr"/>
-      <c r="Q161" t="n">
+      <c r="Q161" t="inlineStr"/>
+      <c r="R161" t="inlineStr"/>
+      <c r="S161" t="n">
+        <v>0</v>
+      </c>
+      <c r="T161" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -7463,12 +8598,19 @@
       <c r="K162" t="n">
         <v>1</v>
       </c>
-      <c r="L162" t="inlineStr"/>
+      <c r="L162" t="n">
+        <v>0</v>
+      </c>
       <c r="M162" t="inlineStr"/>
       <c r="N162" t="inlineStr"/>
       <c r="O162" t="inlineStr"/>
       <c r="P162" t="inlineStr"/>
-      <c r="Q162" t="n">
+      <c r="Q162" t="inlineStr"/>
+      <c r="R162" t="inlineStr"/>
+      <c r="S162" t="n">
+        <v>0</v>
+      </c>
+      <c r="T162" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -7506,12 +8648,19 @@
       <c r="K163" t="n">
         <v>0</v>
       </c>
-      <c r="L163" t="inlineStr"/>
+      <c r="L163" t="n">
+        <v>0</v>
+      </c>
       <c r="M163" t="inlineStr"/>
       <c r="N163" t="inlineStr"/>
       <c r="O163" t="inlineStr"/>
       <c r="P163" t="inlineStr"/>
-      <c r="Q163" t="n">
+      <c r="Q163" t="inlineStr"/>
+      <c r="R163" t="inlineStr"/>
+      <c r="S163" t="n">
+        <v>0</v>
+      </c>
+      <c r="T163" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -7549,12 +8698,19 @@
       <c r="K164" t="n">
         <v>1</v>
       </c>
-      <c r="L164" t="inlineStr"/>
+      <c r="L164" t="n">
+        <v>0</v>
+      </c>
       <c r="M164" t="inlineStr"/>
       <c r="N164" t="inlineStr"/>
       <c r="O164" t="inlineStr"/>
       <c r="P164" t="inlineStr"/>
-      <c r="Q164" t="n">
+      <c r="Q164" t="inlineStr"/>
+      <c r="R164" t="inlineStr"/>
+      <c r="S164" t="n">
+        <v>1</v>
+      </c>
+      <c r="T164" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -7584,9 +8740,7 @@
       <c r="K165" t="n">
         <v>0</v>
       </c>
-      <c r="L165" t="n">
-        <v>0</v>
-      </c>
+      <c r="L165" t="inlineStr"/>
       <c r="M165" t="n">
         <v>0</v>
       </c>
@@ -7600,6 +8754,15 @@
         <v>0</v>
       </c>
       <c r="Q165" t="n">
+        <v>0</v>
+      </c>
+      <c r="R165" t="n">
+        <v>0</v>
+      </c>
+      <c r="S165" t="n">
+        <v>0</v>
+      </c>
+      <c r="T165" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -7629,9 +8792,7 @@
       <c r="K166" t="n">
         <v>0</v>
       </c>
-      <c r="L166" t="n">
-        <v>0</v>
-      </c>
+      <c r="L166" t="inlineStr"/>
       <c r="M166" t="n">
         <v>0</v>
       </c>
@@ -7642,9 +8803,18 @@
         <v>0</v>
       </c>
       <c r="P166" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q166" t="n">
+        <v>1</v>
+      </c>
+      <c r="R166" t="n">
+        <v>0</v>
+      </c>
+      <c r="S166" t="n">
+        <v>0</v>
+      </c>
+      <c r="T166" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -7674,9 +8844,7 @@
       <c r="K167" t="n">
         <v>0</v>
       </c>
-      <c r="L167" t="n">
-        <v>0</v>
-      </c>
+      <c r="L167" t="inlineStr"/>
       <c r="M167" t="n">
         <v>0</v>
       </c>
@@ -7687,9 +8855,18 @@
         <v>0</v>
       </c>
       <c r="P167" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q167" t="n">
+        <v>1</v>
+      </c>
+      <c r="R167" t="n">
+        <v>0</v>
+      </c>
+      <c r="S167" t="n">
+        <v>0</v>
+      </c>
+      <c r="T167" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -7727,12 +8904,19 @@
       <c r="K168" t="n">
         <v>0</v>
       </c>
-      <c r="L168" t="inlineStr"/>
+      <c r="L168" t="n">
+        <v>0</v>
+      </c>
       <c r="M168" t="inlineStr"/>
       <c r="N168" t="inlineStr"/>
       <c r="O168" t="inlineStr"/>
       <c r="P168" t="inlineStr"/>
-      <c r="Q168" t="n">
+      <c r="Q168" t="inlineStr"/>
+      <c r="R168" t="inlineStr"/>
+      <c r="S168" t="n">
+        <v>1</v>
+      </c>
+      <c r="T168" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -7770,12 +8954,19 @@
       <c r="K169" t="n">
         <v>0</v>
       </c>
-      <c r="L169" t="inlineStr"/>
+      <c r="L169" t="n">
+        <v>0</v>
+      </c>
       <c r="M169" t="inlineStr"/>
       <c r="N169" t="inlineStr"/>
       <c r="O169" t="inlineStr"/>
       <c r="P169" t="inlineStr"/>
-      <c r="Q169" t="n">
+      <c r="Q169" t="inlineStr"/>
+      <c r="R169" t="inlineStr"/>
+      <c r="S169" t="n">
+        <v>2</v>
+      </c>
+      <c r="T169" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -7813,12 +9004,19 @@
       <c r="K170" t="n">
         <v>1</v>
       </c>
-      <c r="L170" t="inlineStr"/>
+      <c r="L170" t="n">
+        <v>0</v>
+      </c>
       <c r="M170" t="inlineStr"/>
       <c r="N170" t="inlineStr"/>
       <c r="O170" t="inlineStr"/>
       <c r="P170" t="inlineStr"/>
-      <c r="Q170" t="n">
+      <c r="Q170" t="inlineStr"/>
+      <c r="R170" t="inlineStr"/>
+      <c r="S170" t="n">
+        <v>2</v>
+      </c>
+      <c r="T170" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -7848,9 +9046,7 @@
       <c r="K171" t="n">
         <v>0</v>
       </c>
-      <c r="L171" t="n">
-        <v>0</v>
-      </c>
+      <c r="L171" t="inlineStr"/>
       <c r="M171" t="n">
         <v>0</v>
       </c>
@@ -7858,12 +9054,21 @@
         <v>0</v>
       </c>
       <c r="O171" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P171" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q171" t="n">
+        <v>3</v>
+      </c>
+      <c r="R171" t="n">
+        <v>0</v>
+      </c>
+      <c r="S171" t="n">
+        <v>1</v>
+      </c>
+      <c r="T171" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -7901,12 +9106,19 @@
       <c r="K172" t="n">
         <v>0</v>
       </c>
-      <c r="L172" t="inlineStr"/>
+      <c r="L172" t="n">
+        <v>0</v>
+      </c>
       <c r="M172" t="inlineStr"/>
       <c r="N172" t="inlineStr"/>
       <c r="O172" t="inlineStr"/>
       <c r="P172" t="inlineStr"/>
-      <c r="Q172" t="n">
+      <c r="Q172" t="inlineStr"/>
+      <c r="R172" t="inlineStr"/>
+      <c r="S172" t="n">
+        <v>0</v>
+      </c>
+      <c r="T172" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -7944,12 +9156,19 @@
       <c r="K173" t="n">
         <v>0</v>
       </c>
-      <c r="L173" t="inlineStr"/>
+      <c r="L173" t="n">
+        <v>0</v>
+      </c>
       <c r="M173" t="inlineStr"/>
       <c r="N173" t="inlineStr"/>
       <c r="O173" t="inlineStr"/>
       <c r="P173" t="inlineStr"/>
-      <c r="Q173" t="n">
+      <c r="Q173" t="inlineStr"/>
+      <c r="R173" t="inlineStr"/>
+      <c r="S173" t="n">
+        <v>6</v>
+      </c>
+      <c r="T173" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -7987,12 +9206,19 @@
       <c r="K174" t="n">
         <v>0</v>
       </c>
-      <c r="L174" t="inlineStr"/>
+      <c r="L174" t="n">
+        <v>0</v>
+      </c>
       <c r="M174" t="inlineStr"/>
       <c r="N174" t="inlineStr"/>
       <c r="O174" t="inlineStr"/>
       <c r="P174" t="inlineStr"/>
-      <c r="Q174" t="n">
+      <c r="Q174" t="inlineStr"/>
+      <c r="R174" t="inlineStr"/>
+      <c r="S174" t="n">
+        <v>5</v>
+      </c>
+      <c r="T174" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -8030,12 +9256,19 @@
       <c r="K175" t="n">
         <v>0</v>
       </c>
-      <c r="L175" t="inlineStr"/>
+      <c r="L175" t="n">
+        <v>0</v>
+      </c>
       <c r="M175" t="inlineStr"/>
       <c r="N175" t="inlineStr"/>
       <c r="O175" t="inlineStr"/>
       <c r="P175" t="inlineStr"/>
-      <c r="Q175" t="n">
+      <c r="Q175" t="inlineStr"/>
+      <c r="R175" t="inlineStr"/>
+      <c r="S175" t="n">
+        <v>4</v>
+      </c>
+      <c r="T175" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -8073,12 +9306,19 @@
       <c r="K176" t="n">
         <v>0</v>
       </c>
-      <c r="L176" t="inlineStr"/>
+      <c r="L176" t="n">
+        <v>0</v>
+      </c>
       <c r="M176" t="inlineStr"/>
       <c r="N176" t="inlineStr"/>
       <c r="O176" t="inlineStr"/>
       <c r="P176" t="inlineStr"/>
-      <c r="Q176" t="n">
+      <c r="Q176" t="inlineStr"/>
+      <c r="R176" t="inlineStr"/>
+      <c r="S176" t="n">
+        <v>0</v>
+      </c>
+      <c r="T176" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -8116,12 +9356,19 @@
       <c r="K177" t="n">
         <v>0</v>
       </c>
-      <c r="L177" t="inlineStr"/>
+      <c r="L177" t="n">
+        <v>0</v>
+      </c>
       <c r="M177" t="inlineStr"/>
       <c r="N177" t="inlineStr"/>
       <c r="O177" t="inlineStr"/>
       <c r="P177" t="inlineStr"/>
-      <c r="Q177" t="n">
+      <c r="Q177" t="inlineStr"/>
+      <c r="R177" t="inlineStr"/>
+      <c r="S177" t="n">
+        <v>1</v>
+      </c>
+      <c r="T177" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -8159,12 +9406,19 @@
       <c r="K178" t="n">
         <v>0</v>
       </c>
-      <c r="L178" t="inlineStr"/>
+      <c r="L178" t="n">
+        <v>0</v>
+      </c>
       <c r="M178" t="inlineStr"/>
       <c r="N178" t="inlineStr"/>
       <c r="O178" t="inlineStr"/>
       <c r="P178" t="inlineStr"/>
-      <c r="Q178" t="n">
+      <c r="Q178" t="inlineStr"/>
+      <c r="R178" t="inlineStr"/>
+      <c r="S178" t="n">
+        <v>1</v>
+      </c>
+      <c r="T178" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -8202,12 +9456,19 @@
       <c r="K179" t="n">
         <v>1</v>
       </c>
-      <c r="L179" t="inlineStr"/>
+      <c r="L179" t="n">
+        <v>0</v>
+      </c>
       <c r="M179" t="inlineStr"/>
       <c r="N179" t="inlineStr"/>
       <c r="O179" t="inlineStr"/>
       <c r="P179" t="inlineStr"/>
-      <c r="Q179" t="n">
+      <c r="Q179" t="inlineStr"/>
+      <c r="R179" t="inlineStr"/>
+      <c r="S179" t="n">
+        <v>13</v>
+      </c>
+      <c r="T179" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -8245,12 +9506,19 @@
       <c r="K180" t="n">
         <v>0</v>
       </c>
-      <c r="L180" t="inlineStr"/>
+      <c r="L180" t="n">
+        <v>0</v>
+      </c>
       <c r="M180" t="inlineStr"/>
       <c r="N180" t="inlineStr"/>
       <c r="O180" t="inlineStr"/>
       <c r="P180" t="inlineStr"/>
-      <c r="Q180" t="n">
+      <c r="Q180" t="inlineStr"/>
+      <c r="R180" t="inlineStr"/>
+      <c r="S180" t="n">
+        <v>1</v>
+      </c>
+      <c r="T180" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -8288,12 +9556,19 @@
       <c r="K181" t="n">
         <v>0</v>
       </c>
-      <c r="L181" t="inlineStr"/>
+      <c r="L181" t="n">
+        <v>0</v>
+      </c>
       <c r="M181" t="inlineStr"/>
       <c r="N181" t="inlineStr"/>
       <c r="O181" t="inlineStr"/>
       <c r="P181" t="inlineStr"/>
-      <c r="Q181" t="n">
+      <c r="Q181" t="inlineStr"/>
+      <c r="R181" t="inlineStr"/>
+      <c r="S181" t="n">
+        <v>1</v>
+      </c>
+      <c r="T181" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -8331,12 +9606,19 @@
       <c r="K182" t="n">
         <v>0</v>
       </c>
-      <c r="L182" t="inlineStr"/>
+      <c r="L182" t="n">
+        <v>0</v>
+      </c>
       <c r="M182" t="inlineStr"/>
       <c r="N182" t="inlineStr"/>
       <c r="O182" t="inlineStr"/>
       <c r="P182" t="inlineStr"/>
-      <c r="Q182" t="n">
+      <c r="Q182" t="inlineStr"/>
+      <c r="R182" t="inlineStr"/>
+      <c r="S182" t="n">
+        <v>0</v>
+      </c>
+      <c r="T182" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -8374,12 +9656,19 @@
       <c r="K183" t="n">
         <v>0</v>
       </c>
-      <c r="L183" t="inlineStr"/>
+      <c r="L183" t="n">
+        <v>0</v>
+      </c>
       <c r="M183" t="inlineStr"/>
       <c r="N183" t="inlineStr"/>
       <c r="O183" t="inlineStr"/>
       <c r="P183" t="inlineStr"/>
-      <c r="Q183" t="n">
+      <c r="Q183" t="inlineStr"/>
+      <c r="R183" t="inlineStr"/>
+      <c r="S183" t="n">
+        <v>4</v>
+      </c>
+      <c r="T183" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -8417,12 +9706,19 @@
       <c r="K184" t="n">
         <v>0</v>
       </c>
-      <c r="L184" t="inlineStr"/>
+      <c r="L184" t="n">
+        <v>0</v>
+      </c>
       <c r="M184" t="inlineStr"/>
       <c r="N184" t="inlineStr"/>
       <c r="O184" t="inlineStr"/>
       <c r="P184" t="inlineStr"/>
-      <c r="Q184" t="n">
+      <c r="Q184" t="inlineStr"/>
+      <c r="R184" t="inlineStr"/>
+      <c r="S184" t="n">
+        <v>5</v>
+      </c>
+      <c r="T184" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -8460,12 +9756,19 @@
       <c r="K185" t="n">
         <v>1</v>
       </c>
-      <c r="L185" t="inlineStr"/>
+      <c r="L185" t="n">
+        <v>0</v>
+      </c>
       <c r="M185" t="inlineStr"/>
       <c r="N185" t="inlineStr"/>
       <c r="O185" t="inlineStr"/>
       <c r="P185" t="inlineStr"/>
-      <c r="Q185" t="n">
+      <c r="Q185" t="inlineStr"/>
+      <c r="R185" t="inlineStr"/>
+      <c r="S185" t="n">
+        <v>4</v>
+      </c>
+      <c r="T185" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -8503,12 +9806,19 @@
       <c r="K186" t="n">
         <v>1</v>
       </c>
-      <c r="L186" t="inlineStr"/>
+      <c r="L186" t="n">
+        <v>0</v>
+      </c>
       <c r="M186" t="inlineStr"/>
       <c r="N186" t="inlineStr"/>
       <c r="O186" t="inlineStr"/>
       <c r="P186" t="inlineStr"/>
-      <c r="Q186" t="n">
+      <c r="Q186" t="inlineStr"/>
+      <c r="R186" t="inlineStr"/>
+      <c r="S186" t="n">
+        <v>8</v>
+      </c>
+      <c r="T186" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -8546,12 +9856,19 @@
       <c r="K187" t="n">
         <v>0</v>
       </c>
-      <c r="L187" t="inlineStr"/>
+      <c r="L187" t="n">
+        <v>0</v>
+      </c>
       <c r="M187" t="inlineStr"/>
       <c r="N187" t="inlineStr"/>
       <c r="O187" t="inlineStr"/>
       <c r="P187" t="inlineStr"/>
-      <c r="Q187" t="n">
+      <c r="Q187" t="inlineStr"/>
+      <c r="R187" t="inlineStr"/>
+      <c r="S187" t="n">
+        <v>0</v>
+      </c>
+      <c r="T187" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -8589,12 +9906,19 @@
       <c r="K188" t="n">
         <v>2</v>
       </c>
-      <c r="L188" t="inlineStr"/>
+      <c r="L188" t="n">
+        <v>0</v>
+      </c>
       <c r="M188" t="inlineStr"/>
       <c r="N188" t="inlineStr"/>
       <c r="O188" t="inlineStr"/>
       <c r="P188" t="inlineStr"/>
-      <c r="Q188" t="n">
+      <c r="Q188" t="inlineStr"/>
+      <c r="R188" t="inlineStr"/>
+      <c r="S188" t="n">
+        <v>3</v>
+      </c>
+      <c r="T188" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -8632,12 +9956,19 @@
       <c r="K189" t="n">
         <v>0</v>
       </c>
-      <c r="L189" t="inlineStr"/>
+      <c r="L189" t="n">
+        <v>0</v>
+      </c>
       <c r="M189" t="inlineStr"/>
       <c r="N189" t="inlineStr"/>
       <c r="O189" t="inlineStr"/>
       <c r="P189" t="inlineStr"/>
-      <c r="Q189" t="n">
+      <c r="Q189" t="inlineStr"/>
+      <c r="R189" t="inlineStr"/>
+      <c r="S189" t="n">
+        <v>0</v>
+      </c>
+      <c r="T189" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -8675,12 +10006,19 @@
       <c r="K190" t="n">
         <v>1</v>
       </c>
-      <c r="L190" t="inlineStr"/>
+      <c r="L190" t="n">
+        <v>0</v>
+      </c>
       <c r="M190" t="inlineStr"/>
       <c r="N190" t="inlineStr"/>
       <c r="O190" t="inlineStr"/>
       <c r="P190" t="inlineStr"/>
-      <c r="Q190" t="n">
+      <c r="Q190" t="inlineStr"/>
+      <c r="R190" t="inlineStr"/>
+      <c r="S190" t="n">
+        <v>7</v>
+      </c>
+      <c r="T190" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -8718,12 +10056,19 @@
       <c r="K191" t="n">
         <v>0</v>
       </c>
-      <c r="L191" t="inlineStr"/>
+      <c r="L191" t="n">
+        <v>0</v>
+      </c>
       <c r="M191" t="inlineStr"/>
       <c r="N191" t="inlineStr"/>
       <c r="O191" t="inlineStr"/>
       <c r="P191" t="inlineStr"/>
-      <c r="Q191" t="n">
+      <c r="Q191" t="inlineStr"/>
+      <c r="R191" t="inlineStr"/>
+      <c r="S191" t="n">
+        <v>8</v>
+      </c>
+      <c r="T191" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -8753,11 +10098,9 @@
       <c r="K192" t="n">
         <v>0</v>
       </c>
-      <c r="L192" t="n">
-        <v>1</v>
-      </c>
+      <c r="L192" t="inlineStr"/>
       <c r="M192" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N192" t="n">
         <v>0</v>
@@ -8766,9 +10109,18 @@
         <v>0</v>
       </c>
       <c r="P192" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q192" t="n">
+        <v>3</v>
+      </c>
+      <c r="R192" t="n">
+        <v>0</v>
+      </c>
+      <c r="S192" t="n">
+        <v>3</v>
+      </c>
+      <c r="T192" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -8798,9 +10150,7 @@
       <c r="K193" t="n">
         <v>0</v>
       </c>
-      <c r="L193" t="n">
-        <v>0</v>
-      </c>
+      <c r="L193" t="inlineStr"/>
       <c r="M193" t="n">
         <v>0</v>
       </c>
@@ -8814,6 +10164,15 @@
         <v>0</v>
       </c>
       <c r="Q193" t="n">
+        <v>0</v>
+      </c>
+      <c r="R193" t="n">
+        <v>0</v>
+      </c>
+      <c r="S193" t="n">
+        <v>8</v>
+      </c>
+      <c r="T193" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -8851,12 +10210,19 @@
       <c r="K194" t="n">
         <v>0</v>
       </c>
-      <c r="L194" t="inlineStr"/>
+      <c r="L194" t="n">
+        <v>0</v>
+      </c>
       <c r="M194" t="inlineStr"/>
       <c r="N194" t="inlineStr"/>
       <c r="O194" t="inlineStr"/>
       <c r="P194" t="inlineStr"/>
-      <c r="Q194" t="n">
+      <c r="Q194" t="inlineStr"/>
+      <c r="R194" t="inlineStr"/>
+      <c r="S194" t="n">
+        <v>0</v>
+      </c>
+      <c r="T194" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -8894,12 +10260,19 @@
       <c r="K195" t="n">
         <v>0</v>
       </c>
-      <c r="L195" t="inlineStr"/>
+      <c r="L195" t="n">
+        <v>0</v>
+      </c>
       <c r="M195" t="inlineStr"/>
       <c r="N195" t="inlineStr"/>
       <c r="O195" t="inlineStr"/>
       <c r="P195" t="inlineStr"/>
-      <c r="Q195" t="n">
+      <c r="Q195" t="inlineStr"/>
+      <c r="R195" t="inlineStr"/>
+      <c r="S195" t="n">
+        <v>0</v>
+      </c>
+      <c r="T195" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -8937,12 +10310,19 @@
       <c r="K196" t="n">
         <v>2</v>
       </c>
-      <c r="L196" t="inlineStr"/>
+      <c r="L196" t="n">
+        <v>0</v>
+      </c>
       <c r="M196" t="inlineStr"/>
       <c r="N196" t="inlineStr"/>
       <c r="O196" t="inlineStr"/>
       <c r="P196" t="inlineStr"/>
-      <c r="Q196" t="n">
+      <c r="Q196" t="inlineStr"/>
+      <c r="R196" t="inlineStr"/>
+      <c r="S196" t="n">
+        <v>2</v>
+      </c>
+      <c r="T196" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -8980,12 +10360,19 @@
       <c r="K197" t="n">
         <v>0</v>
       </c>
-      <c r="L197" t="inlineStr"/>
+      <c r="L197" t="n">
+        <v>1</v>
+      </c>
       <c r="M197" t="inlineStr"/>
       <c r="N197" t="inlineStr"/>
       <c r="O197" t="inlineStr"/>
       <c r="P197" t="inlineStr"/>
-      <c r="Q197" t="n">
+      <c r="Q197" t="inlineStr"/>
+      <c r="R197" t="inlineStr"/>
+      <c r="S197" t="n">
+        <v>0</v>
+      </c>
+      <c r="T197" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -9023,12 +10410,19 @@
       <c r="K198" t="n">
         <v>1</v>
       </c>
-      <c r="L198" t="inlineStr"/>
+      <c r="L198" t="n">
+        <v>0</v>
+      </c>
       <c r="M198" t="inlineStr"/>
       <c r="N198" t="inlineStr"/>
       <c r="O198" t="inlineStr"/>
       <c r="P198" t="inlineStr"/>
-      <c r="Q198" t="n">
+      <c r="Q198" t="inlineStr"/>
+      <c r="R198" t="inlineStr"/>
+      <c r="S198" t="n">
+        <v>0</v>
+      </c>
+      <c r="T198" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -9066,12 +10460,19 @@
       <c r="K199" t="n">
         <v>0</v>
       </c>
-      <c r="L199" t="inlineStr"/>
+      <c r="L199" t="n">
+        <v>0</v>
+      </c>
       <c r="M199" t="inlineStr"/>
       <c r="N199" t="inlineStr"/>
       <c r="O199" t="inlineStr"/>
       <c r="P199" t="inlineStr"/>
-      <c r="Q199" t="n">
+      <c r="Q199" t="inlineStr"/>
+      <c r="R199" t="inlineStr"/>
+      <c r="S199" t="n">
+        <v>1</v>
+      </c>
+      <c r="T199" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -9109,12 +10510,19 @@
       <c r="K200" t="n">
         <v>0</v>
       </c>
-      <c r="L200" t="inlineStr"/>
+      <c r="L200" t="n">
+        <v>0</v>
+      </c>
       <c r="M200" t="inlineStr"/>
       <c r="N200" t="inlineStr"/>
       <c r="O200" t="inlineStr"/>
       <c r="P200" t="inlineStr"/>
-      <c r="Q200" t="n">
+      <c r="Q200" t="inlineStr"/>
+      <c r="R200" t="inlineStr"/>
+      <c r="S200" t="n">
+        <v>0</v>
+      </c>
+      <c r="T200" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -9152,12 +10560,19 @@
       <c r="K201" t="n">
         <v>0</v>
       </c>
-      <c r="L201" t="inlineStr"/>
+      <c r="L201" t="n">
+        <v>0</v>
+      </c>
       <c r="M201" t="inlineStr"/>
       <c r="N201" t="inlineStr"/>
       <c r="O201" t="inlineStr"/>
       <c r="P201" t="inlineStr"/>
-      <c r="Q201" t="n">
+      <c r="Q201" t="inlineStr"/>
+      <c r="R201" t="inlineStr"/>
+      <c r="S201" t="n">
+        <v>1</v>
+      </c>
+      <c r="T201" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -9195,12 +10610,19 @@
       <c r="K202" t="n">
         <v>0</v>
       </c>
-      <c r="L202" t="inlineStr"/>
+      <c r="L202" t="n">
+        <v>0</v>
+      </c>
       <c r="M202" t="inlineStr"/>
       <c r="N202" t="inlineStr"/>
       <c r="O202" t="inlineStr"/>
       <c r="P202" t="inlineStr"/>
-      <c r="Q202" t="n">
+      <c r="Q202" t="inlineStr"/>
+      <c r="R202" t="inlineStr"/>
+      <c r="S202" t="n">
+        <v>0</v>
+      </c>
+      <c r="T202" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -9238,12 +10660,19 @@
       <c r="K203" t="n">
         <v>0</v>
       </c>
-      <c r="L203" t="inlineStr"/>
+      <c r="L203" t="n">
+        <v>0</v>
+      </c>
       <c r="M203" t="inlineStr"/>
       <c r="N203" t="inlineStr"/>
       <c r="O203" t="inlineStr"/>
       <c r="P203" t="inlineStr"/>
-      <c r="Q203" t="n">
+      <c r="Q203" t="inlineStr"/>
+      <c r="R203" t="inlineStr"/>
+      <c r="S203" t="n">
+        <v>0</v>
+      </c>
+      <c r="T203" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -9281,12 +10710,19 @@
       <c r="K204" t="n">
         <v>1</v>
       </c>
-      <c r="L204" t="inlineStr"/>
+      <c r="L204" t="n">
+        <v>0</v>
+      </c>
       <c r="M204" t="inlineStr"/>
       <c r="N204" t="inlineStr"/>
       <c r="O204" t="inlineStr"/>
       <c r="P204" t="inlineStr"/>
-      <c r="Q204" t="n">
+      <c r="Q204" t="inlineStr"/>
+      <c r="R204" t="inlineStr"/>
+      <c r="S204" t="n">
+        <v>1</v>
+      </c>
+      <c r="T204" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -9324,12 +10760,19 @@
       <c r="K205" t="n">
         <v>0</v>
       </c>
-      <c r="L205" t="inlineStr"/>
+      <c r="L205" t="n">
+        <v>0</v>
+      </c>
       <c r="M205" t="inlineStr"/>
       <c r="N205" t="inlineStr"/>
       <c r="O205" t="inlineStr"/>
       <c r="P205" t="inlineStr"/>
-      <c r="Q205" t="n">
+      <c r="Q205" t="inlineStr"/>
+      <c r="R205" t="inlineStr"/>
+      <c r="S205" t="n">
+        <v>4</v>
+      </c>
+      <c r="T205" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -9367,12 +10810,19 @@
       <c r="K206" t="n">
         <v>0</v>
       </c>
-      <c r="L206" t="inlineStr"/>
+      <c r="L206" t="n">
+        <v>0</v>
+      </c>
       <c r="M206" t="inlineStr"/>
       <c r="N206" t="inlineStr"/>
       <c r="O206" t="inlineStr"/>
       <c r="P206" t="inlineStr"/>
-      <c r="Q206" t="n">
+      <c r="Q206" t="inlineStr"/>
+      <c r="R206" t="inlineStr"/>
+      <c r="S206" t="n">
+        <v>1</v>
+      </c>
+      <c r="T206" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -9410,12 +10860,19 @@
       <c r="K207" t="n">
         <v>0</v>
       </c>
-      <c r="L207" t="inlineStr"/>
+      <c r="L207" t="n">
+        <v>0</v>
+      </c>
       <c r="M207" t="inlineStr"/>
       <c r="N207" t="inlineStr"/>
       <c r="O207" t="inlineStr"/>
       <c r="P207" t="inlineStr"/>
-      <c r="Q207" t="n">
+      <c r="Q207" t="inlineStr"/>
+      <c r="R207" t="inlineStr"/>
+      <c r="S207" t="n">
+        <v>5</v>
+      </c>
+      <c r="T207" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -9453,12 +10910,19 @@
       <c r="K208" t="n">
         <v>0</v>
       </c>
-      <c r="L208" t="inlineStr"/>
+      <c r="L208" t="n">
+        <v>0</v>
+      </c>
       <c r="M208" t="inlineStr"/>
       <c r="N208" t="inlineStr"/>
       <c r="O208" t="inlineStr"/>
       <c r="P208" t="inlineStr"/>
-      <c r="Q208" t="n">
+      <c r="Q208" t="inlineStr"/>
+      <c r="R208" t="inlineStr"/>
+      <c r="S208" t="n">
+        <v>0</v>
+      </c>
+      <c r="T208" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -9496,12 +10960,19 @@
       <c r="K209" t="n">
         <v>0</v>
       </c>
-      <c r="L209" t="inlineStr"/>
+      <c r="L209" t="n">
+        <v>0</v>
+      </c>
       <c r="M209" t="inlineStr"/>
       <c r="N209" t="inlineStr"/>
       <c r="O209" t="inlineStr"/>
       <c r="P209" t="inlineStr"/>
-      <c r="Q209" t="n">
+      <c r="Q209" t="inlineStr"/>
+      <c r="R209" t="inlineStr"/>
+      <c r="S209" t="n">
+        <v>0</v>
+      </c>
+      <c r="T209" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -9539,12 +11010,19 @@
       <c r="K210" t="n">
         <v>2</v>
       </c>
-      <c r="L210" t="inlineStr"/>
+      <c r="L210" t="n">
+        <v>0</v>
+      </c>
       <c r="M210" t="inlineStr"/>
       <c r="N210" t="inlineStr"/>
       <c r="O210" t="inlineStr"/>
       <c r="P210" t="inlineStr"/>
-      <c r="Q210" t="n">
+      <c r="Q210" t="inlineStr"/>
+      <c r="R210" t="inlineStr"/>
+      <c r="S210" t="n">
+        <v>1</v>
+      </c>
+      <c r="T210" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -9582,12 +11060,19 @@
       <c r="K211" t="n">
         <v>0</v>
       </c>
-      <c r="L211" t="inlineStr"/>
+      <c r="L211" t="n">
+        <v>0</v>
+      </c>
       <c r="M211" t="inlineStr"/>
       <c r="N211" t="inlineStr"/>
       <c r="O211" t="inlineStr"/>
       <c r="P211" t="inlineStr"/>
-      <c r="Q211" t="n">
+      <c r="Q211" t="inlineStr"/>
+      <c r="R211" t="inlineStr"/>
+      <c r="S211" t="n">
+        <v>5</v>
+      </c>
+      <c r="T211" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -9625,12 +11110,19 @@
       <c r="K212" t="n">
         <v>7</v>
       </c>
-      <c r="L212" t="inlineStr"/>
+      <c r="L212" t="n">
+        <v>1</v>
+      </c>
       <c r="M212" t="inlineStr"/>
       <c r="N212" t="inlineStr"/>
       <c r="O212" t="inlineStr"/>
       <c r="P212" t="inlineStr"/>
-      <c r="Q212" t="n">
+      <c r="Q212" t="inlineStr"/>
+      <c r="R212" t="inlineStr"/>
+      <c r="S212" t="n">
+        <v>3</v>
+      </c>
+      <c r="T212" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -9668,12 +11160,19 @@
       <c r="K213" t="n">
         <v>1</v>
       </c>
-      <c r="L213" t="inlineStr"/>
+      <c r="L213" t="n">
+        <v>0</v>
+      </c>
       <c r="M213" t="inlineStr"/>
       <c r="N213" t="inlineStr"/>
       <c r="O213" t="inlineStr"/>
       <c r="P213" t="inlineStr"/>
-      <c r="Q213" t="n">
+      <c r="Q213" t="inlineStr"/>
+      <c r="R213" t="inlineStr"/>
+      <c r="S213" t="n">
+        <v>11</v>
+      </c>
+      <c r="T213" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -9711,12 +11210,19 @@
       <c r="K214" t="n">
         <v>0</v>
       </c>
-      <c r="L214" t="inlineStr"/>
+      <c r="L214" t="n">
+        <v>0</v>
+      </c>
       <c r="M214" t="inlineStr"/>
       <c r="N214" t="inlineStr"/>
       <c r="O214" t="inlineStr"/>
       <c r="P214" t="inlineStr"/>
-      <c r="Q214" t="n">
+      <c r="Q214" t="inlineStr"/>
+      <c r="R214" t="inlineStr"/>
+      <c r="S214" t="n">
+        <v>0</v>
+      </c>
+      <c r="T214" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -9754,12 +11260,19 @@
       <c r="K215" t="n">
         <v>0</v>
       </c>
-      <c r="L215" t="inlineStr"/>
+      <c r="L215" t="n">
+        <v>0</v>
+      </c>
       <c r="M215" t="inlineStr"/>
       <c r="N215" t="inlineStr"/>
       <c r="O215" t="inlineStr"/>
       <c r="P215" t="inlineStr"/>
-      <c r="Q215" t="n">
+      <c r="Q215" t="inlineStr"/>
+      <c r="R215" t="inlineStr"/>
+      <c r="S215" t="n">
+        <v>5</v>
+      </c>
+      <c r="T215" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -9797,12 +11310,19 @@
       <c r="K216" t="n">
         <v>0</v>
       </c>
-      <c r="L216" t="inlineStr"/>
+      <c r="L216" t="n">
+        <v>0</v>
+      </c>
       <c r="M216" t="inlineStr"/>
       <c r="N216" t="inlineStr"/>
       <c r="O216" t="inlineStr"/>
       <c r="P216" t="inlineStr"/>
-      <c r="Q216" t="n">
+      <c r="Q216" t="inlineStr"/>
+      <c r="R216" t="inlineStr"/>
+      <c r="S216" t="n">
+        <v>0</v>
+      </c>
+      <c r="T216" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -9840,12 +11360,19 @@
       <c r="K217" t="n">
         <v>0</v>
       </c>
-      <c r="L217" t="inlineStr"/>
+      <c r="L217" t="n">
+        <v>0</v>
+      </c>
       <c r="M217" t="inlineStr"/>
       <c r="N217" t="inlineStr"/>
       <c r="O217" t="inlineStr"/>
       <c r="P217" t="inlineStr"/>
-      <c r="Q217" t="n">
+      <c r="Q217" t="inlineStr"/>
+      <c r="R217" t="inlineStr"/>
+      <c r="S217" t="n">
+        <v>0</v>
+      </c>
+      <c r="T217" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -9883,12 +11410,19 @@
       <c r="K218" t="n">
         <v>0</v>
       </c>
-      <c r="L218" t="inlineStr"/>
+      <c r="L218" t="n">
+        <v>0</v>
+      </c>
       <c r="M218" t="inlineStr"/>
       <c r="N218" t="inlineStr"/>
       <c r="O218" t="inlineStr"/>
       <c r="P218" t="inlineStr"/>
-      <c r="Q218" t="n">
+      <c r="Q218" t="inlineStr"/>
+      <c r="R218" t="inlineStr"/>
+      <c r="S218" t="n">
+        <v>0</v>
+      </c>
+      <c r="T218" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -9942,6 +11476,15 @@
         <v>0</v>
       </c>
       <c r="Q219" t="n">
+        <v>0</v>
+      </c>
+      <c r="R219" t="n">
+        <v>0</v>
+      </c>
+      <c r="S219" t="n">
+        <v>1</v>
+      </c>
+      <c r="T219" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -9979,12 +11522,19 @@
       <c r="K220" t="n">
         <v>0</v>
       </c>
-      <c r="L220" t="inlineStr"/>
+      <c r="L220" t="n">
+        <v>0</v>
+      </c>
       <c r="M220" t="inlineStr"/>
       <c r="N220" t="inlineStr"/>
       <c r="O220" t="inlineStr"/>
       <c r="P220" t="inlineStr"/>
-      <c r="Q220" t="n">
+      <c r="Q220" t="inlineStr"/>
+      <c r="R220" t="inlineStr"/>
+      <c r="S220" t="n">
+        <v>1</v>
+      </c>
+      <c r="T220" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -10022,12 +11572,19 @@
       <c r="K221" t="n">
         <v>0</v>
       </c>
-      <c r="L221" t="inlineStr"/>
+      <c r="L221" t="n">
+        <v>0</v>
+      </c>
       <c r="M221" t="inlineStr"/>
       <c r="N221" t="inlineStr"/>
       <c r="O221" t="inlineStr"/>
       <c r="P221" t="inlineStr"/>
-      <c r="Q221" t="n">
+      <c r="Q221" t="inlineStr"/>
+      <c r="R221" t="inlineStr"/>
+      <c r="S221" t="n">
+        <v>0</v>
+      </c>
+      <c r="T221" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -10065,12 +11622,19 @@
       <c r="K222" t="n">
         <v>0</v>
       </c>
-      <c r="L222" t="inlineStr"/>
+      <c r="L222" t="n">
+        <v>0</v>
+      </c>
       <c r="M222" t="inlineStr"/>
       <c r="N222" t="inlineStr"/>
       <c r="O222" t="inlineStr"/>
       <c r="P222" t="inlineStr"/>
-      <c r="Q222" t="n">
+      <c r="Q222" t="inlineStr"/>
+      <c r="R222" t="inlineStr"/>
+      <c r="S222" t="n">
+        <v>0</v>
+      </c>
+      <c r="T222" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -10108,12 +11672,19 @@
       <c r="K223" t="n">
         <v>1</v>
       </c>
-      <c r="L223" t="inlineStr"/>
+      <c r="L223" t="n">
+        <v>0</v>
+      </c>
       <c r="M223" t="inlineStr"/>
       <c r="N223" t="inlineStr"/>
       <c r="O223" t="inlineStr"/>
       <c r="P223" t="inlineStr"/>
-      <c r="Q223" t="n">
+      <c r="Q223" t="inlineStr"/>
+      <c r="R223" t="inlineStr"/>
+      <c r="S223" t="n">
+        <v>3</v>
+      </c>
+      <c r="T223" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -10151,12 +11722,19 @@
       <c r="K224" t="n">
         <v>0</v>
       </c>
-      <c r="L224" t="inlineStr"/>
+      <c r="L224" t="n">
+        <v>0</v>
+      </c>
       <c r="M224" t="inlineStr"/>
       <c r="N224" t="inlineStr"/>
       <c r="O224" t="inlineStr"/>
       <c r="P224" t="inlineStr"/>
-      <c r="Q224" t="n">
+      <c r="Q224" t="inlineStr"/>
+      <c r="R224" t="inlineStr"/>
+      <c r="S224" t="n">
+        <v>8</v>
+      </c>
+      <c r="T224" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -10194,12 +11772,19 @@
       <c r="K225" t="n">
         <v>0</v>
       </c>
-      <c r="L225" t="inlineStr"/>
+      <c r="L225" t="n">
+        <v>0</v>
+      </c>
       <c r="M225" t="inlineStr"/>
       <c r="N225" t="inlineStr"/>
       <c r="O225" t="inlineStr"/>
       <c r="P225" t="inlineStr"/>
-      <c r="Q225" t="n">
+      <c r="Q225" t="inlineStr"/>
+      <c r="R225" t="inlineStr"/>
+      <c r="S225" t="n">
+        <v>3</v>
+      </c>
+      <c r="T225" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -10237,12 +11822,19 @@
       <c r="K226" t="n">
         <v>0</v>
       </c>
-      <c r="L226" t="inlineStr"/>
+      <c r="L226" t="n">
+        <v>0</v>
+      </c>
       <c r="M226" t="inlineStr"/>
       <c r="N226" t="inlineStr"/>
       <c r="O226" t="inlineStr"/>
       <c r="P226" t="inlineStr"/>
-      <c r="Q226" t="n">
+      <c r="Q226" t="inlineStr"/>
+      <c r="R226" t="inlineStr"/>
+      <c r="S226" t="n">
+        <v>0</v>
+      </c>
+      <c r="T226" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -10280,12 +11872,19 @@
       <c r="K227" t="n">
         <v>0</v>
       </c>
-      <c r="L227" t="inlineStr"/>
+      <c r="L227" t="n">
+        <v>0</v>
+      </c>
       <c r="M227" t="inlineStr"/>
       <c r="N227" t="inlineStr"/>
       <c r="O227" t="inlineStr"/>
       <c r="P227" t="inlineStr"/>
-      <c r="Q227" t="n">
+      <c r="Q227" t="inlineStr"/>
+      <c r="R227" t="inlineStr"/>
+      <c r="S227" t="n">
+        <v>0</v>
+      </c>
+      <c r="T227" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -10323,12 +11922,19 @@
       <c r="K228" t="n">
         <v>3</v>
       </c>
-      <c r="L228" t="inlineStr"/>
+      <c r="L228" t="n">
+        <v>0</v>
+      </c>
       <c r="M228" t="inlineStr"/>
       <c r="N228" t="inlineStr"/>
       <c r="O228" t="inlineStr"/>
       <c r="P228" t="inlineStr"/>
-      <c r="Q228" t="n">
+      <c r="Q228" t="inlineStr"/>
+      <c r="R228" t="inlineStr"/>
+      <c r="S228" t="n">
+        <v>6</v>
+      </c>
+      <c r="T228" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -10366,12 +11972,19 @@
       <c r="K229" t="n">
         <v>0</v>
       </c>
-      <c r="L229" t="inlineStr"/>
+      <c r="L229" t="n">
+        <v>0</v>
+      </c>
       <c r="M229" t="inlineStr"/>
       <c r="N229" t="inlineStr"/>
       <c r="O229" t="inlineStr"/>
       <c r="P229" t="inlineStr"/>
-      <c r="Q229" t="n">
+      <c r="Q229" t="inlineStr"/>
+      <c r="R229" t="inlineStr"/>
+      <c r="S229" t="n">
+        <v>2</v>
+      </c>
+      <c r="T229" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -10409,12 +12022,19 @@
       <c r="K230" t="n">
         <v>0</v>
       </c>
-      <c r="L230" t="inlineStr"/>
+      <c r="L230" t="n">
+        <v>0</v>
+      </c>
       <c r="M230" t="inlineStr"/>
       <c r="N230" t="inlineStr"/>
       <c r="O230" t="inlineStr"/>
       <c r="P230" t="inlineStr"/>
-      <c r="Q230" t="n">
+      <c r="Q230" t="inlineStr"/>
+      <c r="R230" t="inlineStr"/>
+      <c r="S230" t="n">
+        <v>0</v>
+      </c>
+      <c r="T230" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -10452,12 +12072,19 @@
       <c r="K231" t="n">
         <v>2</v>
       </c>
-      <c r="L231" t="inlineStr"/>
+      <c r="L231" t="n">
+        <v>0</v>
+      </c>
       <c r="M231" t="inlineStr"/>
       <c r="N231" t="inlineStr"/>
       <c r="O231" t="inlineStr"/>
       <c r="P231" t="inlineStr"/>
-      <c r="Q231" t="n">
+      <c r="Q231" t="inlineStr"/>
+      <c r="R231" t="inlineStr"/>
+      <c r="S231" t="n">
+        <v>3</v>
+      </c>
+      <c r="T231" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -10495,12 +12122,19 @@
       <c r="K232" t="n">
         <v>0</v>
       </c>
-      <c r="L232" t="inlineStr"/>
+      <c r="L232" t="n">
+        <v>0</v>
+      </c>
       <c r="M232" t="inlineStr"/>
       <c r="N232" t="inlineStr"/>
       <c r="O232" t="inlineStr"/>
       <c r="P232" t="inlineStr"/>
-      <c r="Q232" t="n">
+      <c r="Q232" t="inlineStr"/>
+      <c r="R232" t="inlineStr"/>
+      <c r="S232" t="n">
+        <v>2</v>
+      </c>
+      <c r="T232" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -10538,12 +12172,19 @@
       <c r="K233" t="n">
         <v>0</v>
       </c>
-      <c r="L233" t="inlineStr"/>
+      <c r="L233" t="n">
+        <v>0</v>
+      </c>
       <c r="M233" t="inlineStr"/>
       <c r="N233" t="inlineStr"/>
       <c r="O233" t="inlineStr"/>
       <c r="P233" t="inlineStr"/>
-      <c r="Q233" t="n">
+      <c r="Q233" t="inlineStr"/>
+      <c r="R233" t="inlineStr"/>
+      <c r="S233" t="n">
+        <v>16</v>
+      </c>
+      <c r="T233" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -10581,12 +12222,19 @@
       <c r="K234" t="n">
         <v>0</v>
       </c>
-      <c r="L234" t="inlineStr"/>
+      <c r="L234" t="n">
+        <v>0</v>
+      </c>
       <c r="M234" t="inlineStr"/>
       <c r="N234" t="inlineStr"/>
       <c r="O234" t="inlineStr"/>
       <c r="P234" t="inlineStr"/>
-      <c r="Q234" t="n">
+      <c r="Q234" t="inlineStr"/>
+      <c r="R234" t="inlineStr"/>
+      <c r="S234" t="n">
+        <v>1</v>
+      </c>
+      <c r="T234" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -10616,9 +12264,7 @@
       <c r="K235" t="n">
         <v>0</v>
       </c>
-      <c r="L235" t="n">
-        <v>0</v>
-      </c>
+      <c r="L235" t="inlineStr"/>
       <c r="M235" t="n">
         <v>0</v>
       </c>
@@ -10629,9 +12275,18 @@
         <v>0</v>
       </c>
       <c r="P235" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q235" t="n">
+        <v>3</v>
+      </c>
+      <c r="R235" t="n">
+        <v>0</v>
+      </c>
+      <c r="S235" t="n">
+        <v>3</v>
+      </c>
+      <c r="T235" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -10661,9 +12316,7 @@
       <c r="K236" t="n">
         <v>0</v>
       </c>
-      <c r="L236" t="n">
-        <v>0</v>
-      </c>
+      <c r="L236" t="inlineStr"/>
       <c r="M236" t="n">
         <v>0</v>
       </c>
@@ -10674,9 +12327,18 @@
         <v>0</v>
       </c>
       <c r="P236" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q236" t="n">
+        <v>3</v>
+      </c>
+      <c r="R236" t="n">
+        <v>0</v>
+      </c>
+      <c r="S236" t="n">
+        <v>8</v>
+      </c>
+      <c r="T236" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -10714,12 +12376,19 @@
       <c r="K237" t="n">
         <v>0</v>
       </c>
-      <c r="L237" t="inlineStr"/>
+      <c r="L237" t="n">
+        <v>0</v>
+      </c>
       <c r="M237" t="inlineStr"/>
       <c r="N237" t="inlineStr"/>
       <c r="O237" t="inlineStr"/>
       <c r="P237" t="inlineStr"/>
-      <c r="Q237" t="n">
+      <c r="Q237" t="inlineStr"/>
+      <c r="R237" t="inlineStr"/>
+      <c r="S237" t="n">
+        <v>2</v>
+      </c>
+      <c r="T237" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -10749,22 +12418,29 @@
       <c r="K238" t="n">
         <v>1</v>
       </c>
-      <c r="L238" t="n">
-        <v>0</v>
-      </c>
+      <c r="L238" t="inlineStr"/>
       <c r="M238" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N238" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O238" t="n">
         <v>0</v>
       </c>
       <c r="P238" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q238" t="n">
+        <v>3</v>
+      </c>
+      <c r="R238" t="n">
+        <v>0</v>
+      </c>
+      <c r="S238" t="n">
+        <v>6</v>
+      </c>
+      <c r="T238" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -10794,22 +12470,29 @@
       <c r="K239" t="n">
         <v>0</v>
       </c>
-      <c r="L239" t="n">
-        <v>0</v>
-      </c>
+      <c r="L239" t="inlineStr"/>
       <c r="M239" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N239" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O239" t="n">
         <v>0</v>
       </c>
       <c r="P239" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q239" t="n">
+        <v>1</v>
+      </c>
+      <c r="R239" t="n">
+        <v>0</v>
+      </c>
+      <c r="S239" t="n">
+        <v>16</v>
+      </c>
+      <c r="T239" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -10847,12 +12530,19 @@
       <c r="K240" t="n">
         <v>0</v>
       </c>
-      <c r="L240" t="inlineStr"/>
+      <c r="L240" t="n">
+        <v>0</v>
+      </c>
       <c r="M240" t="inlineStr"/>
       <c r="N240" t="inlineStr"/>
       <c r="O240" t="inlineStr"/>
       <c r="P240" t="inlineStr"/>
-      <c r="Q240" t="n">
+      <c r="Q240" t="inlineStr"/>
+      <c r="R240" t="inlineStr"/>
+      <c r="S240" t="n">
+        <v>0</v>
+      </c>
+      <c r="T240" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -10890,12 +12580,19 @@
       <c r="K241" t="n">
         <v>1</v>
       </c>
-      <c r="L241" t="inlineStr"/>
+      <c r="L241" t="n">
+        <v>0</v>
+      </c>
       <c r="M241" t="inlineStr"/>
       <c r="N241" t="inlineStr"/>
       <c r="O241" t="inlineStr"/>
       <c r="P241" t="inlineStr"/>
-      <c r="Q241" t="n">
+      <c r="Q241" t="inlineStr"/>
+      <c r="R241" t="inlineStr"/>
+      <c r="S241" t="n">
+        <v>1</v>
+      </c>
+      <c r="T241" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -10925,9 +12622,7 @@
       <c r="K242" t="n">
         <v>0</v>
       </c>
-      <c r="L242" t="n">
-        <v>0</v>
-      </c>
+      <c r="L242" t="inlineStr"/>
       <c r="M242" t="n">
         <v>0</v>
       </c>
@@ -10938,9 +12633,18 @@
         <v>0</v>
       </c>
       <c r="P242" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q242" t="n">
+        <v>2</v>
+      </c>
+      <c r="R242" t="n">
+        <v>0</v>
+      </c>
+      <c r="S242" t="n">
+        <v>4</v>
+      </c>
+      <c r="T242" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -10970,12 +12674,10 @@
       <c r="K243" t="n">
         <v>0</v>
       </c>
-      <c r="L243" t="n">
+      <c r="L243" t="inlineStr"/>
+      <c r="M243" t="n">
         <v>6</v>
       </c>
-      <c r="M243" t="n">
-        <v>0</v>
-      </c>
       <c r="N243" t="n">
         <v>0</v>
       </c>
@@ -10986,6 +12688,15 @@
         <v>0</v>
       </c>
       <c r="Q243" t="n">
+        <v>0</v>
+      </c>
+      <c r="R243" t="n">
+        <v>0</v>
+      </c>
+      <c r="S243" t="n">
+        <v>0</v>
+      </c>
+      <c r="T243" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -11023,12 +12734,19 @@
       <c r="K244" t="n">
         <v>0</v>
       </c>
-      <c r="L244" t="inlineStr"/>
+      <c r="L244" t="n">
+        <v>0</v>
+      </c>
       <c r="M244" t="inlineStr"/>
       <c r="N244" t="inlineStr"/>
       <c r="O244" t="inlineStr"/>
       <c r="P244" t="inlineStr"/>
-      <c r="Q244" t="n">
+      <c r="Q244" t="inlineStr"/>
+      <c r="R244" t="inlineStr"/>
+      <c r="S244" t="n">
+        <v>2</v>
+      </c>
+      <c r="T244" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -11066,12 +12784,19 @@
       <c r="K245" t="n">
         <v>1</v>
       </c>
-      <c r="L245" t="inlineStr"/>
+      <c r="L245" t="n">
+        <v>0</v>
+      </c>
       <c r="M245" t="inlineStr"/>
       <c r="N245" t="inlineStr"/>
       <c r="O245" t="inlineStr"/>
       <c r="P245" t="inlineStr"/>
-      <c r="Q245" t="n">
+      <c r="Q245" t="inlineStr"/>
+      <c r="R245" t="inlineStr"/>
+      <c r="S245" t="n">
+        <v>2</v>
+      </c>
+      <c r="T245" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -11109,12 +12834,19 @@
       <c r="K246" t="n">
         <v>1</v>
       </c>
-      <c r="L246" t="inlineStr"/>
+      <c r="L246" t="n">
+        <v>0</v>
+      </c>
       <c r="M246" t="inlineStr"/>
       <c r="N246" t="inlineStr"/>
       <c r="O246" t="inlineStr"/>
       <c r="P246" t="inlineStr"/>
-      <c r="Q246" t="n">
+      <c r="Q246" t="inlineStr"/>
+      <c r="R246" t="inlineStr"/>
+      <c r="S246" t="n">
+        <v>8</v>
+      </c>
+      <c r="T246" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -11152,12 +12884,19 @@
       <c r="K247" t="n">
         <v>2</v>
       </c>
-      <c r="L247" t="inlineStr"/>
+      <c r="L247" t="n">
+        <v>0</v>
+      </c>
       <c r="M247" t="inlineStr"/>
       <c r="N247" t="inlineStr"/>
       <c r="O247" t="inlineStr"/>
       <c r="P247" t="inlineStr"/>
-      <c r="Q247" t="n">
+      <c r="Q247" t="inlineStr"/>
+      <c r="R247" t="inlineStr"/>
+      <c r="S247" t="n">
+        <v>2</v>
+      </c>
+      <c r="T247" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -11195,12 +12934,19 @@
       <c r="K248" t="n">
         <v>1</v>
       </c>
-      <c r="L248" t="inlineStr"/>
+      <c r="L248" t="n">
+        <v>0</v>
+      </c>
       <c r="M248" t="inlineStr"/>
       <c r="N248" t="inlineStr"/>
       <c r="O248" t="inlineStr"/>
       <c r="P248" t="inlineStr"/>
-      <c r="Q248" t="n">
+      <c r="Q248" t="inlineStr"/>
+      <c r="R248" t="inlineStr"/>
+      <c r="S248" t="n">
+        <v>8</v>
+      </c>
+      <c r="T248" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -11238,12 +12984,19 @@
       <c r="K249" t="n">
         <v>0</v>
       </c>
-      <c r="L249" t="inlineStr"/>
+      <c r="L249" t="n">
+        <v>0</v>
+      </c>
       <c r="M249" t="inlineStr"/>
       <c r="N249" t="inlineStr"/>
       <c r="O249" t="inlineStr"/>
       <c r="P249" t="inlineStr"/>
-      <c r="Q249" t="n">
+      <c r="Q249" t="inlineStr"/>
+      <c r="R249" t="inlineStr"/>
+      <c r="S249" t="n">
+        <v>0</v>
+      </c>
+      <c r="T249" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -11281,12 +13034,19 @@
       <c r="K250" t="n">
         <v>0</v>
       </c>
-      <c r="L250" t="inlineStr"/>
+      <c r="L250" t="n">
+        <v>0</v>
+      </c>
       <c r="M250" t="inlineStr"/>
       <c r="N250" t="inlineStr"/>
       <c r="O250" t="inlineStr"/>
       <c r="P250" t="inlineStr"/>
-      <c r="Q250" t="n">
+      <c r="Q250" t="inlineStr"/>
+      <c r="R250" t="inlineStr"/>
+      <c r="S250" t="n">
+        <v>0</v>
+      </c>
+      <c r="T250" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -11324,12 +13084,19 @@
       <c r="K251" t="n">
         <v>0</v>
       </c>
-      <c r="L251" t="inlineStr"/>
+      <c r="L251" t="n">
+        <v>0</v>
+      </c>
       <c r="M251" t="inlineStr"/>
       <c r="N251" t="inlineStr"/>
       <c r="O251" t="inlineStr"/>
       <c r="P251" t="inlineStr"/>
-      <c r="Q251" t="n">
+      <c r="Q251" t="inlineStr"/>
+      <c r="R251" t="inlineStr"/>
+      <c r="S251" t="n">
+        <v>1</v>
+      </c>
+      <c r="T251" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -11367,12 +13134,19 @@
       <c r="K252" t="n">
         <v>0</v>
       </c>
-      <c r="L252" t="inlineStr"/>
+      <c r="L252" t="n">
+        <v>0</v>
+      </c>
       <c r="M252" t="inlineStr"/>
       <c r="N252" t="inlineStr"/>
       <c r="O252" t="inlineStr"/>
       <c r="P252" t="inlineStr"/>
-      <c r="Q252" t="n">
+      <c r="Q252" t="inlineStr"/>
+      <c r="R252" t="inlineStr"/>
+      <c r="S252" t="n">
+        <v>0</v>
+      </c>
+      <c r="T252" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -11410,12 +13184,19 @@
       <c r="K253" t="n">
         <v>0</v>
       </c>
-      <c r="L253" t="inlineStr"/>
+      <c r="L253" t="n">
+        <v>0</v>
+      </c>
       <c r="M253" t="inlineStr"/>
       <c r="N253" t="inlineStr"/>
       <c r="O253" t="inlineStr"/>
       <c r="P253" t="inlineStr"/>
-      <c r="Q253" t="n">
+      <c r="Q253" t="inlineStr"/>
+      <c r="R253" t="inlineStr"/>
+      <c r="S253" t="n">
+        <v>0</v>
+      </c>
+      <c r="T253" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -11453,12 +13234,19 @@
       <c r="K254" t="n">
         <v>0</v>
       </c>
-      <c r="L254" t="inlineStr"/>
+      <c r="L254" t="n">
+        <v>0</v>
+      </c>
       <c r="M254" t="inlineStr"/>
       <c r="N254" t="inlineStr"/>
       <c r="O254" t="inlineStr"/>
       <c r="P254" t="inlineStr"/>
-      <c r="Q254" t="n">
+      <c r="Q254" t="inlineStr"/>
+      <c r="R254" t="inlineStr"/>
+      <c r="S254" t="n">
+        <v>6</v>
+      </c>
+      <c r="T254" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -11496,12 +13284,19 @@
       <c r="K255" t="n">
         <v>0</v>
       </c>
-      <c r="L255" t="inlineStr"/>
+      <c r="L255" t="n">
+        <v>0</v>
+      </c>
       <c r="M255" t="inlineStr"/>
       <c r="N255" t="inlineStr"/>
       <c r="O255" t="inlineStr"/>
       <c r="P255" t="inlineStr"/>
-      <c r="Q255" t="n">
+      <c r="Q255" t="inlineStr"/>
+      <c r="R255" t="inlineStr"/>
+      <c r="S255" t="n">
+        <v>0</v>
+      </c>
+      <c r="T255" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -11539,12 +13334,19 @@
       <c r="K256" t="n">
         <v>0</v>
       </c>
-      <c r="L256" t="inlineStr"/>
+      <c r="L256" t="n">
+        <v>0</v>
+      </c>
       <c r="M256" t="inlineStr"/>
       <c r="N256" t="inlineStr"/>
       <c r="O256" t="inlineStr"/>
       <c r="P256" t="inlineStr"/>
-      <c r="Q256" t="n">
+      <c r="Q256" t="inlineStr"/>
+      <c r="R256" t="inlineStr"/>
+      <c r="S256" t="n">
+        <v>3</v>
+      </c>
+      <c r="T256" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -11582,12 +13384,19 @@
       <c r="K257" t="n">
         <v>0</v>
       </c>
-      <c r="L257" t="inlineStr"/>
+      <c r="L257" t="n">
+        <v>0</v>
+      </c>
       <c r="M257" t="inlineStr"/>
       <c r="N257" t="inlineStr"/>
       <c r="O257" t="inlineStr"/>
       <c r="P257" t="inlineStr"/>
-      <c r="Q257" t="n">
+      <c r="Q257" t="inlineStr"/>
+      <c r="R257" t="inlineStr"/>
+      <c r="S257" t="n">
+        <v>8</v>
+      </c>
+      <c r="T257" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -11625,12 +13434,19 @@
       <c r="K258" t="n">
         <v>0</v>
       </c>
-      <c r="L258" t="inlineStr"/>
+      <c r="L258" t="n">
+        <v>0</v>
+      </c>
       <c r="M258" t="inlineStr"/>
       <c r="N258" t="inlineStr"/>
       <c r="O258" t="inlineStr"/>
       <c r="P258" t="inlineStr"/>
-      <c r="Q258" t="n">
+      <c r="Q258" t="inlineStr"/>
+      <c r="R258" t="inlineStr"/>
+      <c r="S258" t="n">
+        <v>0</v>
+      </c>
+      <c r="T258" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -11668,12 +13484,19 @@
       <c r="K259" t="n">
         <v>0</v>
       </c>
-      <c r="L259" t="inlineStr"/>
+      <c r="L259" t="n">
+        <v>0</v>
+      </c>
       <c r="M259" t="inlineStr"/>
       <c r="N259" t="inlineStr"/>
       <c r="O259" t="inlineStr"/>
       <c r="P259" t="inlineStr"/>
-      <c r="Q259" t="n">
+      <c r="Q259" t="inlineStr"/>
+      <c r="R259" t="inlineStr"/>
+      <c r="S259" t="n">
+        <v>0</v>
+      </c>
+      <c r="T259" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -11711,12 +13534,19 @@
       <c r="K260" t="n">
         <v>0</v>
       </c>
-      <c r="L260" t="inlineStr"/>
+      <c r="L260" t="n">
+        <v>0</v>
+      </c>
       <c r="M260" t="inlineStr"/>
       <c r="N260" t="inlineStr"/>
       <c r="O260" t="inlineStr"/>
       <c r="P260" t="inlineStr"/>
-      <c r="Q260" t="n">
+      <c r="Q260" t="inlineStr"/>
+      <c r="R260" t="inlineStr"/>
+      <c r="S260" t="n">
+        <v>1</v>
+      </c>
+      <c r="T260" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -11754,12 +13584,19 @@
       <c r="K261" t="n">
         <v>0</v>
       </c>
-      <c r="L261" t="inlineStr"/>
+      <c r="L261" t="n">
+        <v>0</v>
+      </c>
       <c r="M261" t="inlineStr"/>
       <c r="N261" t="inlineStr"/>
       <c r="O261" t="inlineStr"/>
       <c r="P261" t="inlineStr"/>
-      <c r="Q261" t="n">
+      <c r="Q261" t="inlineStr"/>
+      <c r="R261" t="inlineStr"/>
+      <c r="S261" t="n">
+        <v>3</v>
+      </c>
+      <c r="T261" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -11797,12 +13634,19 @@
       <c r="K262" t="n">
         <v>0</v>
       </c>
-      <c r="L262" t="inlineStr"/>
+      <c r="L262" t="n">
+        <v>0</v>
+      </c>
       <c r="M262" t="inlineStr"/>
       <c r="N262" t="inlineStr"/>
       <c r="O262" t="inlineStr"/>
       <c r="P262" t="inlineStr"/>
-      <c r="Q262" t="n">
+      <c r="Q262" t="inlineStr"/>
+      <c r="R262" t="inlineStr"/>
+      <c r="S262" t="n">
+        <v>14</v>
+      </c>
+      <c r="T262" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -11840,12 +13684,19 @@
       <c r="K263" t="n">
         <v>0</v>
       </c>
-      <c r="L263" t="inlineStr"/>
+      <c r="L263" t="n">
+        <v>0</v>
+      </c>
       <c r="M263" t="inlineStr"/>
       <c r="N263" t="inlineStr"/>
       <c r="O263" t="inlineStr"/>
       <c r="P263" t="inlineStr"/>
-      <c r="Q263" t="n">
+      <c r="Q263" t="inlineStr"/>
+      <c r="R263" t="inlineStr"/>
+      <c r="S263" t="n">
+        <v>3</v>
+      </c>
+      <c r="T263" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -11883,12 +13734,19 @@
       <c r="K264" t="n">
         <v>0</v>
       </c>
-      <c r="L264" t="inlineStr"/>
+      <c r="L264" t="n">
+        <v>0</v>
+      </c>
       <c r="M264" t="inlineStr"/>
       <c r="N264" t="inlineStr"/>
       <c r="O264" t="inlineStr"/>
       <c r="P264" t="inlineStr"/>
-      <c r="Q264" t="n">
+      <c r="Q264" t="inlineStr"/>
+      <c r="R264" t="inlineStr"/>
+      <c r="S264" t="n">
+        <v>3</v>
+      </c>
+      <c r="T264" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -11926,12 +13784,19 @@
       <c r="K265" t="n">
         <v>0</v>
       </c>
-      <c r="L265" t="inlineStr"/>
+      <c r="L265" t="n">
+        <v>0</v>
+      </c>
       <c r="M265" t="inlineStr"/>
       <c r="N265" t="inlineStr"/>
       <c r="O265" t="inlineStr"/>
       <c r="P265" t="inlineStr"/>
-      <c r="Q265" t="n">
+      <c r="Q265" t="inlineStr"/>
+      <c r="R265" t="inlineStr"/>
+      <c r="S265" t="n">
+        <v>10</v>
+      </c>
+      <c r="T265" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -11969,12 +13834,19 @@
       <c r="K266" t="n">
         <v>1</v>
       </c>
-      <c r="L266" t="inlineStr"/>
+      <c r="L266" t="n">
+        <v>0</v>
+      </c>
       <c r="M266" t="inlineStr"/>
       <c r="N266" t="inlineStr"/>
       <c r="O266" t="inlineStr"/>
       <c r="P266" t="inlineStr"/>
-      <c r="Q266" t="n">
+      <c r="Q266" t="inlineStr"/>
+      <c r="R266" t="inlineStr"/>
+      <c r="S266" t="n">
+        <v>28</v>
+      </c>
+      <c r="T266" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -12012,12 +13884,19 @@
       <c r="K267" t="n">
         <v>0</v>
       </c>
-      <c r="L267" t="inlineStr"/>
+      <c r="L267" t="n">
+        <v>0</v>
+      </c>
       <c r="M267" t="inlineStr"/>
       <c r="N267" t="inlineStr"/>
       <c r="O267" t="inlineStr"/>
       <c r="P267" t="inlineStr"/>
-      <c r="Q267" t="n">
+      <c r="Q267" t="inlineStr"/>
+      <c r="R267" t="inlineStr"/>
+      <c r="S267" t="n">
+        <v>7</v>
+      </c>
+      <c r="T267" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -12055,12 +13934,19 @@
       <c r="K268" t="n">
         <v>0</v>
       </c>
-      <c r="L268" t="inlineStr"/>
+      <c r="L268" t="n">
+        <v>0</v>
+      </c>
       <c r="M268" t="inlineStr"/>
       <c r="N268" t="inlineStr"/>
       <c r="O268" t="inlineStr"/>
       <c r="P268" t="inlineStr"/>
-      <c r="Q268" t="n">
+      <c r="Q268" t="inlineStr"/>
+      <c r="R268" t="inlineStr"/>
+      <c r="S268" t="n">
+        <v>5</v>
+      </c>
+      <c r="T268" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -12098,12 +13984,19 @@
       <c r="K269" t="n">
         <v>0</v>
       </c>
-      <c r="L269" t="inlineStr"/>
+      <c r="L269" t="n">
+        <v>0</v>
+      </c>
       <c r="M269" t="inlineStr"/>
       <c r="N269" t="inlineStr"/>
       <c r="O269" t="inlineStr"/>
       <c r="P269" t="inlineStr"/>
-      <c r="Q269" t="n">
+      <c r="Q269" t="inlineStr"/>
+      <c r="R269" t="inlineStr"/>
+      <c r="S269" t="n">
+        <v>1</v>
+      </c>
+      <c r="T269" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -12141,12 +14034,19 @@
       <c r="K270" t="n">
         <v>0</v>
       </c>
-      <c r="L270" t="inlineStr"/>
+      <c r="L270" t="n">
+        <v>0</v>
+      </c>
       <c r="M270" t="inlineStr"/>
       <c r="N270" t="inlineStr"/>
       <c r="O270" t="inlineStr"/>
       <c r="P270" t="inlineStr"/>
-      <c r="Q270" t="n">
+      <c r="Q270" t="inlineStr"/>
+      <c r="R270" t="inlineStr"/>
+      <c r="S270" t="n">
+        <v>0</v>
+      </c>
+      <c r="T270" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -12184,12 +14084,19 @@
       <c r="K271" t="n">
         <v>1</v>
       </c>
-      <c r="L271" t="inlineStr"/>
+      <c r="L271" t="n">
+        <v>0</v>
+      </c>
       <c r="M271" t="inlineStr"/>
       <c r="N271" t="inlineStr"/>
       <c r="O271" t="inlineStr"/>
       <c r="P271" t="inlineStr"/>
-      <c r="Q271" t="n">
+      <c r="Q271" t="inlineStr"/>
+      <c r="R271" t="inlineStr"/>
+      <c r="S271" t="n">
+        <v>1</v>
+      </c>
+      <c r="T271" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -12227,12 +14134,19 @@
       <c r="K272" t="n">
         <v>0</v>
       </c>
-      <c r="L272" t="inlineStr"/>
+      <c r="L272" t="n">
+        <v>0</v>
+      </c>
       <c r="M272" t="inlineStr"/>
       <c r="N272" t="inlineStr"/>
       <c r="O272" t="inlineStr"/>
       <c r="P272" t="inlineStr"/>
-      <c r="Q272" t="n">
+      <c r="Q272" t="inlineStr"/>
+      <c r="R272" t="inlineStr"/>
+      <c r="S272" t="n">
+        <v>0</v>
+      </c>
+      <c r="T272" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -12270,12 +14184,19 @@
       <c r="K273" t="n">
         <v>0</v>
       </c>
-      <c r="L273" t="inlineStr"/>
+      <c r="L273" t="n">
+        <v>0</v>
+      </c>
       <c r="M273" t="inlineStr"/>
       <c r="N273" t="inlineStr"/>
       <c r="O273" t="inlineStr"/>
       <c r="P273" t="inlineStr"/>
-      <c r="Q273" t="n">
+      <c r="Q273" t="inlineStr"/>
+      <c r="R273" t="inlineStr"/>
+      <c r="S273" t="n">
+        <v>0</v>
+      </c>
+      <c r="T273" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -12313,12 +14234,19 @@
       <c r="K274" t="n">
         <v>0</v>
       </c>
-      <c r="L274" t="inlineStr"/>
+      <c r="L274" t="n">
+        <v>0</v>
+      </c>
       <c r="M274" t="inlineStr"/>
       <c r="N274" t="inlineStr"/>
       <c r="O274" t="inlineStr"/>
       <c r="P274" t="inlineStr"/>
-      <c r="Q274" t="n">
+      <c r="Q274" t="inlineStr"/>
+      <c r="R274" t="inlineStr"/>
+      <c r="S274" t="n">
+        <v>2</v>
+      </c>
+      <c r="T274" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -12356,12 +14284,19 @@
       <c r="K275" t="n">
         <v>1</v>
       </c>
-      <c r="L275" t="inlineStr"/>
+      <c r="L275" t="n">
+        <v>0</v>
+      </c>
       <c r="M275" t="inlineStr"/>
       <c r="N275" t="inlineStr"/>
       <c r="O275" t="inlineStr"/>
       <c r="P275" t="inlineStr"/>
-      <c r="Q275" t="n">
+      <c r="Q275" t="inlineStr"/>
+      <c r="R275" t="inlineStr"/>
+      <c r="S275" t="n">
+        <v>5</v>
+      </c>
+      <c r="T275" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -12399,12 +14334,19 @@
       <c r="K276" t="n">
         <v>0</v>
       </c>
-      <c r="L276" t="inlineStr"/>
+      <c r="L276" t="n">
+        <v>0</v>
+      </c>
       <c r="M276" t="inlineStr"/>
       <c r="N276" t="inlineStr"/>
       <c r="O276" t="inlineStr"/>
       <c r="P276" t="inlineStr"/>
-      <c r="Q276" t="n">
+      <c r="Q276" t="inlineStr"/>
+      <c r="R276" t="inlineStr"/>
+      <c r="S276" t="n">
+        <v>0</v>
+      </c>
+      <c r="T276" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -12442,12 +14384,19 @@
       <c r="K277" t="n">
         <v>0</v>
       </c>
-      <c r="L277" t="inlineStr"/>
+      <c r="L277" t="n">
+        <v>0</v>
+      </c>
       <c r="M277" t="inlineStr"/>
       <c r="N277" t="inlineStr"/>
       <c r="O277" t="inlineStr"/>
       <c r="P277" t="inlineStr"/>
-      <c r="Q277" t="n">
+      <c r="Q277" t="inlineStr"/>
+      <c r="R277" t="inlineStr"/>
+      <c r="S277" t="n">
+        <v>5</v>
+      </c>
+      <c r="T277" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -12485,12 +14434,19 @@
       <c r="K278" t="n">
         <v>0</v>
       </c>
-      <c r="L278" t="inlineStr"/>
+      <c r="L278" t="n">
+        <v>0</v>
+      </c>
       <c r="M278" t="inlineStr"/>
       <c r="N278" t="inlineStr"/>
       <c r="O278" t="inlineStr"/>
       <c r="P278" t="inlineStr"/>
-      <c r="Q278" t="n">
+      <c r="Q278" t="inlineStr"/>
+      <c r="R278" t="inlineStr"/>
+      <c r="S278" t="n">
+        <v>0</v>
+      </c>
+      <c r="T278" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -12528,12 +14484,19 @@
       <c r="K279" t="n">
         <v>0</v>
       </c>
-      <c r="L279" t="inlineStr"/>
+      <c r="L279" t="n">
+        <v>0</v>
+      </c>
       <c r="M279" t="inlineStr"/>
       <c r="N279" t="inlineStr"/>
       <c r="O279" t="inlineStr"/>
       <c r="P279" t="inlineStr"/>
-      <c r="Q279" t="n">
+      <c r="Q279" t="inlineStr"/>
+      <c r="R279" t="inlineStr"/>
+      <c r="S279" t="n">
+        <v>4</v>
+      </c>
+      <c r="T279" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -12571,12 +14534,19 @@
       <c r="K280" t="n">
         <v>0</v>
       </c>
-      <c r="L280" t="inlineStr"/>
+      <c r="L280" t="n">
+        <v>0</v>
+      </c>
       <c r="M280" t="inlineStr"/>
       <c r="N280" t="inlineStr"/>
       <c r="O280" t="inlineStr"/>
       <c r="P280" t="inlineStr"/>
-      <c r="Q280" t="n">
+      <c r="Q280" t="inlineStr"/>
+      <c r="R280" t="inlineStr"/>
+      <c r="S280" t="n">
+        <v>0</v>
+      </c>
+      <c r="T280" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -12614,12 +14584,19 @@
       <c r="K281" t="n">
         <v>0</v>
       </c>
-      <c r="L281" t="inlineStr"/>
+      <c r="L281" t="n">
+        <v>0</v>
+      </c>
       <c r="M281" t="inlineStr"/>
       <c r="N281" t="inlineStr"/>
       <c r="O281" t="inlineStr"/>
       <c r="P281" t="inlineStr"/>
-      <c r="Q281" t="n">
+      <c r="Q281" t="inlineStr"/>
+      <c r="R281" t="inlineStr"/>
+      <c r="S281" t="n">
+        <v>2</v>
+      </c>
+      <c r="T281" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -12657,12 +14634,19 @@
       <c r="K282" t="n">
         <v>0</v>
       </c>
-      <c r="L282" t="inlineStr"/>
+      <c r="L282" t="n">
+        <v>0</v>
+      </c>
       <c r="M282" t="inlineStr"/>
       <c r="N282" t="inlineStr"/>
       <c r="O282" t="inlineStr"/>
       <c r="P282" t="inlineStr"/>
-      <c r="Q282" t="n">
+      <c r="Q282" t="inlineStr"/>
+      <c r="R282" t="inlineStr"/>
+      <c r="S282" t="n">
+        <v>3</v>
+      </c>
+      <c r="T282" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -12700,12 +14684,19 @@
       <c r="K283" t="n">
         <v>0</v>
       </c>
-      <c r="L283" t="inlineStr"/>
+      <c r="L283" t="n">
+        <v>0</v>
+      </c>
       <c r="M283" t="inlineStr"/>
       <c r="N283" t="inlineStr"/>
       <c r="O283" t="inlineStr"/>
       <c r="P283" t="inlineStr"/>
-      <c r="Q283" t="n">
+      <c r="Q283" t="inlineStr"/>
+      <c r="R283" t="inlineStr"/>
+      <c r="S283" t="n">
+        <v>0</v>
+      </c>
+      <c r="T283" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -12743,12 +14734,19 @@
       <c r="K284" t="n">
         <v>0</v>
       </c>
-      <c r="L284" t="inlineStr"/>
+      <c r="L284" t="n">
+        <v>0</v>
+      </c>
       <c r="M284" t="inlineStr"/>
       <c r="N284" t="inlineStr"/>
       <c r="O284" t="inlineStr"/>
       <c r="P284" t="inlineStr"/>
-      <c r="Q284" t="n">
+      <c r="Q284" t="inlineStr"/>
+      <c r="R284" t="inlineStr"/>
+      <c r="S284" t="n">
+        <v>2</v>
+      </c>
+      <c r="T284" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -12786,12 +14784,19 @@
       <c r="K285" t="n">
         <v>0</v>
       </c>
-      <c r="L285" t="inlineStr"/>
+      <c r="L285" t="n">
+        <v>0</v>
+      </c>
       <c r="M285" t="inlineStr"/>
       <c r="N285" t="inlineStr"/>
       <c r="O285" t="inlineStr"/>
       <c r="P285" t="inlineStr"/>
-      <c r="Q285" t="n">
+      <c r="Q285" t="inlineStr"/>
+      <c r="R285" t="inlineStr"/>
+      <c r="S285" t="n">
+        <v>0</v>
+      </c>
+      <c r="T285" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -12821,9 +14826,7 @@
       <c r="K286" t="n">
         <v>0</v>
       </c>
-      <c r="L286" t="n">
-        <v>0</v>
-      </c>
+      <c r="L286" t="inlineStr"/>
       <c r="M286" t="n">
         <v>0</v>
       </c>
@@ -12837,6 +14840,15 @@
         <v>0</v>
       </c>
       <c r="Q286" t="n">
+        <v>0</v>
+      </c>
+      <c r="R286" t="n">
+        <v>0</v>
+      </c>
+      <c r="S286" t="n">
+        <v>5</v>
+      </c>
+      <c r="T286" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -12874,12 +14886,19 @@
       <c r="K287" t="n">
         <v>6</v>
       </c>
-      <c r="L287" t="inlineStr"/>
+      <c r="L287" t="n">
+        <v>1</v>
+      </c>
       <c r="M287" t="inlineStr"/>
       <c r="N287" t="inlineStr"/>
       <c r="O287" t="inlineStr"/>
       <c r="P287" t="inlineStr"/>
-      <c r="Q287" t="n">
+      <c r="Q287" t="inlineStr"/>
+      <c r="R287" t="inlineStr"/>
+      <c r="S287" t="n">
+        <v>1</v>
+      </c>
+      <c r="T287" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -12917,12 +14936,19 @@
       <c r="K288" t="n">
         <v>0</v>
       </c>
-      <c r="L288" t="inlineStr"/>
+      <c r="L288" t="n">
+        <v>0</v>
+      </c>
       <c r="M288" t="inlineStr"/>
       <c r="N288" t="inlineStr"/>
       <c r="O288" t="inlineStr"/>
       <c r="P288" t="inlineStr"/>
-      <c r="Q288" t="n">
+      <c r="Q288" t="inlineStr"/>
+      <c r="R288" t="inlineStr"/>
+      <c r="S288" t="n">
+        <v>3</v>
+      </c>
+      <c r="T288" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -12952,9 +14978,7 @@
       <c r="K289" t="n">
         <v>0</v>
       </c>
-      <c r="L289" t="n">
-        <v>0</v>
-      </c>
+      <c r="L289" t="inlineStr"/>
       <c r="M289" t="n">
         <v>0</v>
       </c>
@@ -12965,9 +14989,18 @@
         <v>0</v>
       </c>
       <c r="P289" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q289" t="n">
         <v>11</v>
       </c>
-      <c r="Q289" t="n">
+      <c r="R289" t="n">
+        <v>0</v>
+      </c>
+      <c r="S289" t="n">
+        <v>4</v>
+      </c>
+      <c r="T289" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -12997,9 +15030,7 @@
       <c r="K290" t="n">
         <v>0</v>
       </c>
-      <c r="L290" t="n">
-        <v>0</v>
-      </c>
+      <c r="L290" t="inlineStr"/>
       <c r="M290" t="n">
         <v>0</v>
       </c>
@@ -13010,9 +15041,18 @@
         <v>0</v>
       </c>
       <c r="P290" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q290" t="n">
         <v>11</v>
       </c>
-      <c r="Q290" t="n">
+      <c r="R290" t="n">
+        <v>0</v>
+      </c>
+      <c r="S290" t="n">
+        <v>6</v>
+      </c>
+      <c r="T290" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -13042,9 +15082,7 @@
       <c r="K291" t="n">
         <v>0</v>
       </c>
-      <c r="L291" t="n">
-        <v>0</v>
-      </c>
+      <c r="L291" t="inlineStr"/>
       <c r="M291" t="n">
         <v>0</v>
       </c>
@@ -13058,6 +15096,15 @@
         <v>0</v>
       </c>
       <c r="Q291" t="n">
+        <v>0</v>
+      </c>
+      <c r="R291" t="n">
+        <v>0</v>
+      </c>
+      <c r="S291" t="n">
+        <v>2</v>
+      </c>
+      <c r="T291" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -13087,9 +15134,7 @@
       <c r="K292" t="n">
         <v>0</v>
       </c>
-      <c r="L292" t="n">
-        <v>0</v>
-      </c>
+      <c r="L292" t="inlineStr"/>
       <c r="M292" t="n">
         <v>0</v>
       </c>
@@ -13100,9 +15145,18 @@
         <v>0</v>
       </c>
       <c r="P292" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q292" t="n">
+        <v>2</v>
+      </c>
+      <c r="R292" t="n">
+        <v>0</v>
+      </c>
+      <c r="S292" t="n">
+        <v>2</v>
+      </c>
+      <c r="T292" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -13140,12 +15194,19 @@
       <c r="K293" t="n">
         <v>0</v>
       </c>
-      <c r="L293" t="inlineStr"/>
+      <c r="L293" t="n">
+        <v>0</v>
+      </c>
       <c r="M293" t="inlineStr"/>
       <c r="N293" t="inlineStr"/>
       <c r="O293" t="inlineStr"/>
       <c r="P293" t="inlineStr"/>
-      <c r="Q293" t="n">
+      <c r="Q293" t="inlineStr"/>
+      <c r="R293" t="inlineStr"/>
+      <c r="S293" t="n">
+        <v>0</v>
+      </c>
+      <c r="T293" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -13183,12 +15244,19 @@
       <c r="K294" t="n">
         <v>1</v>
       </c>
-      <c r="L294" t="inlineStr"/>
+      <c r="L294" t="n">
+        <v>0</v>
+      </c>
       <c r="M294" t="inlineStr"/>
       <c r="N294" t="inlineStr"/>
       <c r="O294" t="inlineStr"/>
       <c r="P294" t="inlineStr"/>
-      <c r="Q294" t="n">
+      <c r="Q294" t="inlineStr"/>
+      <c r="R294" t="inlineStr"/>
+      <c r="S294" t="n">
+        <v>0</v>
+      </c>
+      <c r="T294" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -13218,9 +15286,7 @@
       <c r="K295" t="n">
         <v>0</v>
       </c>
-      <c r="L295" t="n">
-        <v>0</v>
-      </c>
+      <c r="L295" t="inlineStr"/>
       <c r="M295" t="n">
         <v>0</v>
       </c>
@@ -13228,12 +15294,21 @@
         <v>0</v>
       </c>
       <c r="O295" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P295" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q295" t="n">
+        <v>0</v>
+      </c>
+      <c r="R295" t="n">
+        <v>0</v>
+      </c>
+      <c r="S295" t="n">
+        <v>2</v>
+      </c>
+      <c r="T295" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -13271,12 +15346,19 @@
       <c r="K296" t="n">
         <v>0</v>
       </c>
-      <c r="L296" t="inlineStr"/>
+      <c r="L296" t="n">
+        <v>0</v>
+      </c>
       <c r="M296" t="inlineStr"/>
       <c r="N296" t="inlineStr"/>
       <c r="O296" t="inlineStr"/>
       <c r="P296" t="inlineStr"/>
-      <c r="Q296" t="n">
+      <c r="Q296" t="inlineStr"/>
+      <c r="R296" t="inlineStr"/>
+      <c r="S296" t="n">
+        <v>0</v>
+      </c>
+      <c r="T296" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -13314,12 +15396,19 @@
       <c r="K297" t="n">
         <v>0</v>
       </c>
-      <c r="L297" t="inlineStr"/>
+      <c r="L297" t="n">
+        <v>0</v>
+      </c>
       <c r="M297" t="inlineStr"/>
       <c r="N297" t="inlineStr"/>
       <c r="O297" t="inlineStr"/>
       <c r="P297" t="inlineStr"/>
-      <c r="Q297" t="n">
+      <c r="Q297" t="inlineStr"/>
+      <c r="R297" t="inlineStr"/>
+      <c r="S297" t="n">
+        <v>1</v>
+      </c>
+      <c r="T297" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -13357,12 +15446,19 @@
       <c r="K298" t="n">
         <v>0</v>
       </c>
-      <c r="L298" t="inlineStr"/>
+      <c r="L298" t="n">
+        <v>0</v>
+      </c>
       <c r="M298" t="inlineStr"/>
       <c r="N298" t="inlineStr"/>
       <c r="O298" t="inlineStr"/>
       <c r="P298" t="inlineStr"/>
-      <c r="Q298" t="n">
+      <c r="Q298" t="inlineStr"/>
+      <c r="R298" t="inlineStr"/>
+      <c r="S298" t="n">
+        <v>3</v>
+      </c>
+      <c r="T298" t="n">
         <v>2009</v>
       </c>
     </row>
@@ -13400,12 +15496,19 @@
       <c r="K299" t="n">
         <v>1</v>
       </c>
-      <c r="L299" t="inlineStr"/>
+      <c r="L299" t="n">
+        <v>0</v>
+      </c>
       <c r="M299" t="inlineStr"/>
       <c r="N299" t="inlineStr"/>
       <c r="O299" t="inlineStr"/>
       <c r="P299" t="inlineStr"/>
-      <c r="Q299" t="n">
+      <c r="Q299" t="inlineStr"/>
+      <c r="R299" t="inlineStr"/>
+      <c r="S299" t="n">
+        <v>14</v>
+      </c>
+      <c r="T299" t="n">
         <v>2009</v>
       </c>
     </row>
